--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K260"/>
+  <dimension ref="A1:K275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -667,10 +667,10 @@
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="I6" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I7" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -741,10 +741,10 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="I8" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -778,13 +778,13 @@
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -932,10 +932,10 @@
         <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I13" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -969,10 +969,10 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="I14" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="I15" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="I16" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1080,13 +1080,13 @@
         <v>6.5</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.11</v>
+        <v>0.06</v>
       </c>
       <c r="I22" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.44</v>
+        <v>0.22</v>
       </c>
       <c r="I23" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>0.89</v>
+        <v>0.44</v>
       </c>
       <c r="I24" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1382,13 +1382,13 @@
         <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I25" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1610,10 +1610,10 @@
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.71</v>
+        <v>0.36</v>
       </c>
       <c r="I31" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1684,13 +1684,13 @@
         <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I33" t="n">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         <v>1.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="I42" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="I43" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I44" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I45" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I46" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I47" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2245,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I48" t="n">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>0.43</v>
+        <v>0.21</v>
       </c>
       <c r="I52" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="I53" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2473,13 +2473,13 @@
         <v>7</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I54" t="n">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I57" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I58" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         <v>5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="I59" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I60" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="I63" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="I64" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2892,10 +2892,10 @@
         <v>4</v>
       </c>
       <c r="H65" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I65" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         <v>6</v>
       </c>
       <c r="H66" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="I66" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         <v>7</v>
       </c>
       <c r="H67" t="n">
-        <v>0.88</v>
+        <v>0.44</v>
       </c>
       <c r="I67" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3003,13 +3003,13 @@
         <v>8</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I68" t="n">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I71" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I72" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         <v>3</v>
       </c>
       <c r="H73" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I73" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         <v>5</v>
       </c>
       <c r="H74" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="I74" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I75" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3305,13 +3305,13 @@
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I76" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="I82" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
         <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>0.33</v>
+        <v>0.17</v>
       </c>
       <c r="I83" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="I84" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         <v>5</v>
       </c>
       <c r="H85" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="I85" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -3681,10 +3681,10 @@
         <v>5</v>
       </c>
       <c r="H86" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
       <c r="I86" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -3718,13 +3718,13 @@
         <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I87" t="n">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I93" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I94" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I95" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4057,10 +4057,10 @@
         <v>3</v>
       </c>
       <c r="H96" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I96" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4094,10 +4094,10 @@
         <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I97" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         <v>4</v>
       </c>
       <c r="H98" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="I98" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         <v>5</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I99" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I103" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I104" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="I105" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
       <c r="I106" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -4470,10 +4470,10 @@
         <v>5</v>
       </c>
       <c r="H107" t="n">
-        <v>0.71</v>
+        <v>0.24</v>
       </c>
       <c r="I107" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>0.86</v>
+        <v>0.28</v>
       </c>
       <c r="I108" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         <v>6.5</v>
       </c>
       <c r="H109" t="n">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="I109" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         <v>7</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I110" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -4618,13 +4618,13 @@
         <v>7</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I111" t="n">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -4809,10 +4809,10 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I116" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         <v>4</v>
       </c>
       <c r="H117" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="I117" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I118" t="n">
-        <v>275</v>
+        <v>304</v>
       </c>
       <c r="J118" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5037,10 +5037,10 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I122" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         <v>2</v>
       </c>
       <c r="H123" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="I123" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         <v>4</v>
       </c>
       <c r="H124" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="I124" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         <v>6</v>
       </c>
       <c r="H125" t="n">
-        <v>0.86</v>
+        <v>0.43</v>
       </c>
       <c r="I125" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         <v>7</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I126" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -5222,13 +5222,13 @@
         <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I127" t="n">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5413,10 +5413,10 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I132" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I133" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="I134" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         <v>4</v>
       </c>
       <c r="H135" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="I135" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
         <v>5</v>
       </c>
       <c r="H136" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I136" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         <v>5</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I137" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         <v>5</v>
       </c>
       <c r="H138" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I138" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -5672,13 +5672,13 @@
         <v>5</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I139" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I143" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I144" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -5900,10 +5900,10 @@
         <v>2</v>
       </c>
       <c r="H145" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I145" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         <v>3.5</v>
       </c>
       <c r="H146" t="n">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="I146" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -5974,13 +5974,13 @@
         <v>5</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I147" t="n">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
@@ -6168,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -6313,10 +6313,10 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="I156" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
@@ -6350,10 +6350,10 @@
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="I157" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -6387,10 +6387,10 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
       <c r="I158" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         <v>2</v>
       </c>
       <c r="H159" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="I159" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -6461,10 +6461,10 @@
         <v>3</v>
       </c>
       <c r="H160" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I160" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         <v>3</v>
       </c>
       <c r="H161" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I161" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -6535,10 +6535,10 @@
         <v>3</v>
       </c>
       <c r="H162" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I162" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
@@ -6572,13 +6572,13 @@
         <v>4</v>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I163" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
@@ -6800,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I169" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I170" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
@@ -6874,10 +6874,10 @@
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I171" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -6911,10 +6911,10 @@
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I172" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I173" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         <v>1</v>
       </c>
       <c r="H174" t="n">
-        <v>0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I174" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
@@ -7022,10 +7022,10 @@
         <v>2</v>
       </c>
       <c r="H175" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="I175" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         <v>2</v>
       </c>
       <c r="H176" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="I176" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
@@ -7096,10 +7096,10 @@
         <v>4</v>
       </c>
       <c r="H177" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="I177" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         <v>4</v>
       </c>
       <c r="H178" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="I178" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>0.71</v>
+        <v>0.24</v>
       </c>
       <c r="I179" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
@@ -7207,10 +7207,10 @@
         <v>6</v>
       </c>
       <c r="H180" t="n">
-        <v>0.86</v>
+        <v>0.28</v>
       </c>
       <c r="I180" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         <v>6</v>
       </c>
       <c r="H181" t="n">
-        <v>0.86</v>
+        <v>0.28</v>
       </c>
       <c r="I181" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         <v>7</v>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I182" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
@@ -7318,13 +7318,13 @@
         <v>7</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I183" t="n">
-        <v>261</v>
+        <v>294</v>
       </c>
       <c r="J183" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
@@ -7586,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
@@ -7694,10 +7694,10 @@
         <v>0.5</v>
       </c>
       <c r="H193" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="I193" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="I194" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
@@ -7768,10 +7768,10 @@
         <v>2</v>
       </c>
       <c r="H195" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="I195" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -7805,10 +7805,10 @@
         <v>2.5</v>
       </c>
       <c r="H196" t="n">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
@@ -7842,10 +7842,10 @@
         <v>3</v>
       </c>
       <c r="H197" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I197" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -7879,10 +7879,10 @@
         <v>3</v>
       </c>
       <c r="H198" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I198" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         <v>3</v>
       </c>
       <c r="H199" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I199" t="n">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="J199" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         <v>0.5</v>
       </c>
       <c r="H206" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="I206" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         <v>1.5</v>
       </c>
       <c r="H207" t="n">
-        <v>0.5</v>
+        <v>0.16</v>
       </c>
       <c r="I207" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         <v>2</v>
       </c>
       <c r="H208" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="I208" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         <v>2.5</v>
       </c>
       <c r="H209" t="n">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="I209" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
@@ -8329,10 +8329,10 @@
         <v>2.5</v>
       </c>
       <c r="H210" t="n">
-        <v>0.83</v>
+        <v>0.28</v>
       </c>
       <c r="I210" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
@@ -8366,13 +8366,13 @@
         <v>3</v>
       </c>
       <c r="H211" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I211" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="J211" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
@@ -8420,7 +8420,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -8486,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
@@ -8494,7 +8494,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
@@ -8531,7 +8531,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
@@ -8568,7 +8568,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8634,7 +8634,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8705,10 +8705,10 @@
         <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
@@ -8716,7 +8716,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8742,10 +8742,10 @@
         <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I221" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
@@ -8753,7 +8753,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8779,10 +8779,10 @@
         <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>0.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I222" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8816,10 +8816,10 @@
         <v>2</v>
       </c>
       <c r="H223" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="I223" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
@@ -8827,7 +8827,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8853,10 +8853,10 @@
         <v>2</v>
       </c>
       <c r="H224" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="I224" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
@@ -8864,7 +8864,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8890,10 +8890,10 @@
         <v>3</v>
       </c>
       <c r="H225" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="I225" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
@@ -8901,7 +8901,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8927,10 +8927,10 @@
         <v>4</v>
       </c>
       <c r="H226" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="I226" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8964,10 +8964,10 @@
         <v>4</v>
       </c>
       <c r="H227" t="n">
-        <v>0.8</v>
+        <v>0.26</v>
       </c>
       <c r="I227" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
@@ -8975,7 +8975,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9001,10 +9001,10 @@
         <v>5</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I228" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
@@ -9012,7 +9012,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9038,10 +9038,10 @@
         <v>5</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I229" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9075,10 +9075,10 @@
         <v>5</v>
       </c>
       <c r="H230" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I230" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9112,13 +9112,13 @@
         <v>5</v>
       </c>
       <c r="H231" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I231" t="n">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="J231" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
@@ -9166,7 +9166,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9232,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
@@ -9240,7 +9240,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
@@ -9314,7 +9314,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="I237" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
@@ -9351,7 +9351,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
@@ -9425,7 +9425,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -9451,10 +9451,10 @@
         <v>2</v>
       </c>
       <c r="H240" t="n">
-        <v>0.29</v>
+        <v>0.09</v>
       </c>
       <c r="I240" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
@@ -9462,7 +9462,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9488,10 +9488,10 @@
         <v>3</v>
       </c>
       <c r="H241" t="n">
-        <v>0.43</v>
+        <v>0.14</v>
       </c>
       <c r="I241" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
@@ -9499,7 +9499,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -9525,10 +9525,10 @@
         <v>5</v>
       </c>
       <c r="H242" t="n">
-        <v>0.71</v>
+        <v>0.24</v>
       </c>
       <c r="I242" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9562,10 +9562,10 @@
         <v>6</v>
       </c>
       <c r="H243" t="n">
-        <v>0.86</v>
+        <v>0.28</v>
       </c>
       <c r="I243" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
@@ -9573,7 +9573,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -9599,10 +9599,10 @@
         <v>6.5</v>
       </c>
       <c r="H244" t="n">
-        <v>0.93</v>
+        <v>0.31</v>
       </c>
       <c r="I244" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
@@ -9610,7 +9610,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9636,10 +9636,10 @@
         <v>7</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I245" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
@@ -9647,7 +9647,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9673,13 +9673,13 @@
         <v>7</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I246" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -9690,21 +9690,21 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>44088</v>
+        <v>44817</v>
       </c>
       <c r="C247" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D247" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
@@ -9727,21 +9727,21 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>44092</v>
+        <v>44823</v>
       </c>
       <c r="C248" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D248" t="n">
         <v>262</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9756,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
@@ -9764,21 +9764,21 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>44095</v>
+        <v>44827</v>
       </c>
       <c r="C249" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D249" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
@@ -9801,21 +9801,21 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>44098</v>
+        <v>44832</v>
       </c>
       <c r="C250" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D250" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
@@ -9838,21 +9838,21 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>44102</v>
+        <v>44834</v>
       </c>
       <c r="C251" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D251" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9861,13 +9861,13 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
@@ -9875,21 +9875,21 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>44104</v>
+        <v>44841</v>
       </c>
       <c r="C252" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D252" t="n">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9898,13 +9898,13 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
@@ -9912,21 +9912,21 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>44106</v>
+        <v>44844</v>
       </c>
       <c r="C253" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D253" t="n">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9935,13 +9935,13 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H253" t="n">
-        <v>0.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I253" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
@@ -9949,21 +9949,21 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>44109</v>
+        <v>44848</v>
       </c>
       <c r="C254" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D254" t="n">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9972,13 +9972,13 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H254" t="n">
-        <v>0.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I254" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
@@ -9986,21 +9986,21 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>44022</v>
+        <v>44851</v>
       </c>
       <c r="C255" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D255" t="n">
-        <v>192</v>
+        <v>290</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10009,13 +10009,13 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H255" t="n">
-        <v>0.83</v>
+        <v>0.13</v>
       </c>
       <c r="I255" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10023,21 +10023,21 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>44175</v>
+        <v>44854</v>
       </c>
       <c r="C256" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D256" t="n">
-        <v>345</v>
+        <v>293</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H256" t="n">
-        <v>0.83</v>
+        <v>0.2</v>
       </c>
       <c r="I256" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
@@ -10060,21 +10060,21 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>44118</v>
+        <v>44859</v>
       </c>
       <c r="C257" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D257" t="n">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10083,13 +10083,13 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H257" t="n">
-        <v>0.83</v>
+        <v>0.26</v>
       </c>
       <c r="I257" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
@@ -10097,36 +10097,36 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>44120</v>
+        <v>44862</v>
       </c>
       <c r="C258" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D258" t="n">
+        <v>301</v>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>4</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I258" t="n">
         <v>290</v>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Te Puke</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G258" t="n">
-        <v>6</v>
-      </c>
-      <c r="H258" t="n">
-        <v>1</v>
-      </c>
-      <c r="I258" t="n">
-        <v>264</v>
       </c>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
@@ -10134,21 +10134,21 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>44123</v>
+        <v>44866</v>
       </c>
       <c r="C259" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D259" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10157,13 +10157,13 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H259" t="n">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I259" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
@@ -10171,41 +10171,602 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
+        <v>44869</v>
+      </c>
+      <c r="C260" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D260" t="n">
+        <v>308</v>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>5</v>
+      </c>
+      <c r="H260" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I260" t="n">
+        <v>290</v>
+      </c>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>44872</v>
+      </c>
+      <c r="C261" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D261" t="n">
+        <v>311</v>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>5</v>
+      </c>
+      <c r="H261" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I261" t="n">
+        <v>290</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>StartFlowering</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>44088</v>
+      </c>
+      <c r="C262" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D262" t="n">
+        <v>258</v>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>274</v>
+      </c>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>44092</v>
+      </c>
+      <c r="C263" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D263" t="n">
+        <v>262</v>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="n">
+        <v>0</v>
+      </c>
+      <c r="I263" t="n">
+        <v>274</v>
+      </c>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>44095</v>
+      </c>
+      <c r="C264" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D264" t="n">
+        <v>265</v>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" t="n">
+        <v>274</v>
+      </c>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>44098</v>
+      </c>
+      <c r="C265" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D265" t="n">
+        <v>268</v>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="n">
+        <v>0</v>
+      </c>
+      <c r="I265" t="n">
+        <v>274</v>
+      </c>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>44102</v>
+      </c>
+      <c r="C266" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D266" t="n">
+        <v>272</v>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>1</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I266" t="n">
+        <v>274</v>
+      </c>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>44104</v>
+      </c>
+      <c r="C267" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D267" t="n">
+        <v>274</v>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>2</v>
+      </c>
+      <c r="H267" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I267" t="n">
+        <v>274</v>
+      </c>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>44106</v>
+      </c>
+      <c r="C268" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D268" t="n">
+        <v>276</v>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>2</v>
+      </c>
+      <c r="H268" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I268" t="n">
+        <v>274</v>
+      </c>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>44109</v>
+      </c>
+      <c r="C269" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D269" t="n">
+        <v>279</v>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>4</v>
+      </c>
+      <c r="H269" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="I269" t="n">
+        <v>274</v>
+      </c>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>44022</v>
+      </c>
+      <c r="C270" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D270" t="n">
+        <v>192</v>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>5</v>
+      </c>
+      <c r="H270" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I270" t="n">
+        <v>274</v>
+      </c>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>44175</v>
+      </c>
+      <c r="C271" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D271" t="n">
+        <v>345</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>5</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I271" t="n">
+        <v>274</v>
+      </c>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>44118</v>
+      </c>
+      <c r="C272" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D272" t="n">
+        <v>288</v>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>5</v>
+      </c>
+      <c r="H272" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I272" t="n">
+        <v>274</v>
+      </c>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>44120</v>
+      </c>
+      <c r="C273" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D273" t="n">
+        <v>290</v>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>6</v>
+      </c>
+      <c r="H273" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I273" t="n">
+        <v>274</v>
+      </c>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>44123</v>
+      </c>
+      <c r="C274" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D274" t="n">
+        <v>293</v>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>6</v>
+      </c>
+      <c r="H274" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I274" t="n">
+        <v>274</v>
+      </c>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="n">
         <v>44127</v>
       </c>
-      <c r="C260" t="n">
+      <c r="C275" t="n">
         <v>2020</v>
       </c>
-      <c r="D260" t="n">
+      <c r="D275" t="n">
         <v>297</v>
       </c>
-      <c r="E260" t="inlineStr">
-        <is>
-          <t>Te Puke</t>
-        </is>
-      </c>
-      <c r="F260" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G260" t="n">
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
         <v>6</v>
       </c>
-      <c r="H260" t="n">
-        <v>1</v>
-      </c>
-      <c r="I260" t="n">
-        <v>264</v>
-      </c>
-      <c r="J260" t="n">
-        <v>1</v>
-      </c>
-      <c r="K260" t="inlineStr">
+      <c r="H275" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I275" t="n">
+        <v>274</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K275" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -10222,7 +10783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I191"/>
+  <dimension ref="A1:H204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10258,15 +10819,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>KiwiFruit.Phenology.Flowers</t>
+          <t>KiwiFruit.Phenology.FloweringDOY</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>KiwiFruit.Phenology.FloweringDOY</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>KiwiFruit.Phenology.CurrentStageName</t>
         </is>
@@ -10298,12 +10854,9 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>327</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10331,12 +10884,9 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.2105263157894737</v>
-      </c>
-      <c r="H3" t="n">
-        <v>327</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10364,12 +10914,9 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2.421052631578947</v>
-      </c>
-      <c r="H4" t="n">
-        <v>327</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10397,12 +10944,9 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8.157894736842104</v>
-      </c>
-      <c r="H5" t="n">
-        <v>327</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10430,12 +10974,9 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17.94736842105263</v>
-      </c>
-      <c r="H6" t="n">
-        <v>327</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>335</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10463,12 +11004,9 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18.52631578947368</v>
-      </c>
-      <c r="H7" t="n">
-        <v>327</v>
-      </c>
-      <c r="I7" t="inlineStr">
+        <v>335</v>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -10500,12 +11038,9 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
         <v>330</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10533,12 +11068,9 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
         <v>330</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -10566,12 +11098,9 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H10" t="n">
         <v>330</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10599,12 +11128,9 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="H11" t="n">
         <v>330</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10632,12 +11158,9 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="H12" t="n">
         <v>330</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10665,12 +11188,9 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>16.25</v>
-      </c>
-      <c r="H13" t="n">
         <v>330</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -10702,12 +11222,9 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>323</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10735,12 +11252,9 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>323</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10768,12 +11282,9 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>323</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10801,12 +11312,9 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H17" t="n">
-        <v>323</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10834,12 +11342,9 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H18" t="n">
-        <v>323</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10867,12 +11372,9 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="H19" t="n">
-        <v>323</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10900,12 +11402,9 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="H20" t="n">
-        <v>323</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10933,12 +11432,9 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="H21" t="n">
-        <v>323</v>
-      </c>
-      <c r="I21" t="inlineStr">
+        <v>327</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -10970,12 +11466,9 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>323</v>
-      </c>
-      <c r="I22" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11003,12 +11496,9 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>323</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11036,12 +11526,9 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>323</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11069,12 +11556,9 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.636363636363636</v>
-      </c>
-      <c r="H25" t="n">
-        <v>323</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11102,12 +11586,9 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7.818181818181818</v>
-      </c>
-      <c r="H26" t="n">
-        <v>323</v>
-      </c>
-      <c r="I26" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11135,12 +11616,9 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>18.81818181818182</v>
-      </c>
-      <c r="H27" t="n">
-        <v>323</v>
-      </c>
-      <c r="I27" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11168,12 +11646,9 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>31.18181818181818</v>
-      </c>
-      <c r="H28" t="n">
-        <v>323</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11201,12 +11676,9 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>32</v>
-      </c>
-      <c r="H29" t="n">
-        <v>323</v>
-      </c>
-      <c r="I29" t="inlineStr">
+        <v>327</v>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11238,12 +11710,9 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>323</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11271,12 +11740,9 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H31" t="n">
-        <v>323</v>
-      </c>
-      <c r="I31" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11304,12 +11770,9 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="H32" t="n">
-        <v>323</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11337,12 +11800,9 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="H33" t="n">
-        <v>323</v>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11370,12 +11830,9 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>6.066666666666666</v>
-      </c>
-      <c r="H34" t="n">
-        <v>323</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11403,12 +11860,9 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="H35" t="n">
-        <v>323</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11436,12 +11890,9 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>19.76666666666667</v>
-      </c>
-      <c r="H36" t="n">
-        <v>323</v>
-      </c>
-      <c r="I36" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11469,12 +11920,9 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>20.73333333333333</v>
-      </c>
-      <c r="H37" t="n">
-        <v>323</v>
-      </c>
-      <c r="I37" t="inlineStr">
+        <v>327</v>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11506,12 +11954,9 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.59375</v>
-      </c>
-      <c r="H38" t="n">
-        <v>323</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11539,12 +11984,9 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H39" t="n">
-        <v>323</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -11572,12 +12014,9 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>13.96875</v>
-      </c>
-      <c r="H40" t="n">
-        <v>323</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -11605,12 +12044,9 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>29.671875</v>
-      </c>
-      <c r="H41" t="n">
-        <v>323</v>
-      </c>
-      <c r="I41" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11642,12 +12078,9 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.078125</v>
-      </c>
-      <c r="H42" t="n">
-        <v>324</v>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11675,12 +12108,9 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4.234375</v>
-      </c>
-      <c r="H43" t="n">
-        <v>324</v>
-      </c>
-      <c r="I43" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11708,12 +12138,9 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>16.9375</v>
-      </c>
-      <c r="H44" t="n">
-        <v>324</v>
-      </c>
-      <c r="I44" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11741,12 +12168,9 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>19.71875</v>
-      </c>
-      <c r="H45" t="n">
-        <v>324</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -11774,12 +12198,9 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>20.171875</v>
-      </c>
-      <c r="H46" t="n">
-        <v>324</v>
-      </c>
-      <c r="I46" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11811,12 +12232,9 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2.53968253968254</v>
-      </c>
-      <c r="H47" t="n">
         <v>320</v>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -11844,12 +12262,9 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>11.28571428571429</v>
-      </c>
-      <c r="H48" t="n">
         <v>320</v>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -11877,12 +12292,9 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>21.73015873015873</v>
-      </c>
-      <c r="H49" t="n">
         <v>320</v>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -11910,12 +12322,9 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>23.09523809523809</v>
-      </c>
-      <c r="H50" t="n">
         <v>320</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11947,12 +12356,9 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.703125</v>
-      </c>
-      <c r="H51" t="n">
-        <v>320</v>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -11980,12 +12386,9 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>11.1875</v>
-      </c>
-      <c r="H52" t="n">
-        <v>320</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12013,12 +12416,9 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>21.40625</v>
-      </c>
-      <c r="H53" t="n">
-        <v>320</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12046,12 +12446,9 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>23.390625</v>
-      </c>
-      <c r="H54" t="n">
-        <v>320</v>
-      </c>
-      <c r="I54" t="inlineStr">
+        <v>324</v>
+      </c>
+      <c r="H54" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12083,12 +12480,9 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2.640625</v>
-      </c>
-      <c r="H55" t="n">
         <v>320</v>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12116,12 +12510,9 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>11.484375</v>
-      </c>
-      <c r="H56" t="n">
         <v>320</v>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12149,12 +12540,9 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>21.765625</v>
-      </c>
-      <c r="H57" t="n">
         <v>320</v>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12182,12 +12570,9 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>23.109375</v>
-      </c>
-      <c r="H58" t="n">
         <v>320</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12219,12 +12604,9 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>0.234375</v>
-      </c>
-      <c r="H59" t="n">
-        <v>325</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12252,12 +12634,9 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.15625</v>
-      </c>
-      <c r="H60" t="n">
-        <v>325</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12285,12 +12664,9 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>2.84375</v>
-      </c>
-      <c r="H61" t="n">
-        <v>325</v>
-      </c>
-      <c r="I61" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12318,12 +12694,9 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>14.734375</v>
-      </c>
-      <c r="H62" t="n">
-        <v>325</v>
-      </c>
-      <c r="I62" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12351,12 +12724,9 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H63" t="n">
-        <v>325</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12384,12 +12754,9 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>20.28125</v>
-      </c>
-      <c r="H64" t="n">
-        <v>325</v>
-      </c>
-      <c r="I64" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H64" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12421,12 +12788,9 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>0.90625</v>
-      </c>
-      <c r="H65" t="n">
-        <v>329</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
+        <v>334</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12454,12 +12818,9 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>4.890625</v>
-      </c>
-      <c r="H66" t="n">
-        <v>329</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
+        <v>334</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12487,12 +12848,9 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>12.125</v>
-      </c>
-      <c r="H67" t="n">
-        <v>329</v>
-      </c>
-      <c r="I67" t="inlineStr"/>
+        <v>334</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -12520,12 +12878,9 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>13.421875</v>
-      </c>
-      <c r="H68" t="n">
-        <v>329</v>
-      </c>
-      <c r="I68" t="inlineStr">
+        <v>334</v>
+      </c>
+      <c r="H68" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12557,12 +12912,9 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0.015625</v>
-      </c>
-      <c r="H69" t="n">
-        <v>320</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
+        <v>342</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12590,12 +12942,9 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.09375</v>
-      </c>
-      <c r="H70" t="n">
-        <v>320</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
+        <v>342</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -12623,12 +12972,9 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="H71" t="n">
-        <v>320</v>
-      </c>
-      <c r="I71" t="inlineStr"/>
+        <v>342</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -12656,12 +13002,9 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>2.828125</v>
-      </c>
-      <c r="H72" t="n">
-        <v>320</v>
-      </c>
-      <c r="I72" t="inlineStr"/>
+        <v>342</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -12689,12 +13032,9 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>10.28125</v>
-      </c>
-      <c r="H73" t="n">
-        <v>320</v>
-      </c>
-      <c r="I73" t="inlineStr"/>
+        <v>342</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -12722,12 +13062,9 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>12.5625</v>
-      </c>
-      <c r="H74" t="n">
-        <v>320</v>
-      </c>
-      <c r="I74" t="inlineStr">
+        <v>342</v>
+      </c>
+      <c r="H74" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12759,12 +13096,9 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>324</v>
-      </c>
-      <c r="I75" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -12792,12 +13126,9 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.3191489361702128</v>
-      </c>
-      <c r="H76" t="n">
-        <v>324</v>
-      </c>
-      <c r="I76" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -12825,12 +13156,9 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1.276595744680851</v>
-      </c>
-      <c r="H77" t="n">
-        <v>324</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -12858,12 +13186,9 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>5.978723404255319</v>
-      </c>
-      <c r="H78" t="n">
-        <v>324</v>
-      </c>
-      <c r="I78" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -12891,12 +13216,9 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>17.19148936170213</v>
-      </c>
-      <c r="H79" t="n">
-        <v>324</v>
-      </c>
-      <c r="I79" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -12924,12 +13246,9 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>22.17021276595745</v>
-      </c>
-      <c r="H80" t="n">
-        <v>324</v>
-      </c>
-      <c r="I80" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -12957,12 +13276,9 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>23.31914893617021</v>
-      </c>
-      <c r="H81" t="n">
-        <v>324</v>
-      </c>
-      <c r="I81" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12994,12 +13310,9 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="H82" t="n">
-        <v>318</v>
-      </c>
-      <c r="I82" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13027,12 +13340,9 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H83" t="n">
-        <v>318</v>
-      </c>
-      <c r="I83" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13060,12 +13370,9 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H84" t="n">
-        <v>318</v>
-      </c>
-      <c r="I84" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13093,12 +13400,9 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="H85" t="n">
-        <v>318</v>
-      </c>
-      <c r="I85" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13126,12 +13430,9 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1.075</v>
-      </c>
-      <c r="H86" t="n">
-        <v>318</v>
-      </c>
-      <c r="I86" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13159,12 +13460,9 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="H87" t="n">
-        <v>318</v>
-      </c>
-      <c r="I87" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13192,12 +13490,9 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>8</v>
-      </c>
-      <c r="H88" t="n">
-        <v>318</v>
-      </c>
-      <c r="I88" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13225,12 +13520,9 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>11.275</v>
-      </c>
-      <c r="H89" t="n">
-        <v>318</v>
-      </c>
-      <c r="I89" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13258,12 +13550,9 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>13.725</v>
-      </c>
-      <c r="H90" t="n">
-        <v>318</v>
-      </c>
-      <c r="I90" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13291,12 +13580,9 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>13.875</v>
-      </c>
-      <c r="H91" t="n">
-        <v>318</v>
-      </c>
-      <c r="I91" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H91" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13328,12 +13614,9 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>317</v>
-      </c>
-      <c r="I92" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13361,12 +13644,9 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H93" t="n">
-        <v>317</v>
-      </c>
-      <c r="I93" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13394,12 +13674,9 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="H94" t="n">
-        <v>317</v>
-      </c>
-      <c r="I94" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13427,12 +13704,9 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H95" t="n">
-        <v>317</v>
-      </c>
-      <c r="I95" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13460,12 +13734,9 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>7.725</v>
-      </c>
-      <c r="H96" t="n">
-        <v>317</v>
-      </c>
-      <c r="I96" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13493,12 +13764,9 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>10.025</v>
-      </c>
-      <c r="H97" t="n">
-        <v>317</v>
-      </c>
-      <c r="I97" t="inlineStr"/>
+        <v>324</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13526,12 +13794,9 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>10.025</v>
-      </c>
-      <c r="H98" t="n">
-        <v>317</v>
-      </c>
-      <c r="I98" t="inlineStr">
+        <v>324</v>
+      </c>
+      <c r="H98" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13563,12 +13828,9 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" t="n">
-        <v>319</v>
-      </c>
-      <c r="I99" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13596,12 +13858,9 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" t="n">
-        <v>319</v>
-      </c>
-      <c r="I100" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13629,12 +13888,9 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>319</v>
-      </c>
-      <c r="I101" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13662,12 +13918,9 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>319</v>
-      </c>
-      <c r="I102" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13695,12 +13948,9 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>319</v>
-      </c>
-      <c r="I103" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13728,12 +13978,9 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>319</v>
-      </c>
-      <c r="I104" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13761,12 +14008,9 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" t="n">
-        <v>319</v>
-      </c>
-      <c r="I105" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13794,12 +14038,9 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H106" t="n">
-        <v>319</v>
-      </c>
-      <c r="I106" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13827,12 +14068,9 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H107" t="n">
-        <v>319</v>
-      </c>
-      <c r="I107" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13860,12 +14098,9 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H108" t="n">
-        <v>319</v>
-      </c>
-      <c r="I108" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13893,12 +14128,9 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="H109" t="n">
-        <v>319</v>
-      </c>
-      <c r="I109" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13926,12 +14158,9 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="H110" t="n">
-        <v>319</v>
-      </c>
-      <c r="I110" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13959,12 +14188,9 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H111" t="n">
-        <v>319</v>
-      </c>
-      <c r="I111" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13992,12 +14218,9 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H112" t="n">
-        <v>319</v>
-      </c>
-      <c r="I112" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14025,12 +14248,9 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H113" t="n">
-        <v>319</v>
-      </c>
-      <c r="I113" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14058,12 +14278,9 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H114" t="n">
-        <v>319</v>
-      </c>
-      <c r="I114" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14091,12 +14308,9 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H115" t="n">
-        <v>319</v>
-      </c>
-      <c r="I115" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14124,12 +14338,9 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H116" t="n">
-        <v>319</v>
-      </c>
-      <c r="I116" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14157,12 +14368,9 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="H117" t="n">
-        <v>319</v>
-      </c>
-      <c r="I117" t="inlineStr"/>
+        <v>330</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14190,12 +14398,9 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>6.85</v>
-      </c>
-      <c r="H118" t="n">
-        <v>319</v>
-      </c>
-      <c r="I118" t="inlineStr">
+        <v>330</v>
+      </c>
+      <c r="H118" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -14227,12 +14432,9 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0.02564102564102564</v>
-      </c>
-      <c r="H119" t="n">
-        <v>317</v>
-      </c>
-      <c r="I119" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14260,12 +14462,9 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.02564102564102564</v>
-      </c>
-      <c r="H120" t="n">
-        <v>317</v>
-      </c>
-      <c r="I120" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14293,12 +14492,9 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="H121" t="n">
-        <v>317</v>
-      </c>
-      <c r="I121" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14326,12 +14522,9 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="H122" t="n">
-        <v>317</v>
-      </c>
-      <c r="I122" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14359,12 +14552,9 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="H123" t="n">
-        <v>317</v>
-      </c>
-      <c r="I123" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14392,12 +14582,9 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1.512820512820513</v>
-      </c>
-      <c r="H124" t="n">
-        <v>317</v>
-      </c>
-      <c r="I124" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14425,12 +14612,9 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2.102564102564103</v>
-      </c>
-      <c r="H125" t="n">
-        <v>317</v>
-      </c>
-      <c r="I125" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14458,12 +14642,9 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2.538461538461538</v>
-      </c>
-      <c r="H126" t="n">
-        <v>317</v>
-      </c>
-      <c r="I126" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14491,12 +14672,9 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2.974358974358974</v>
-      </c>
-      <c r="H127" t="n">
-        <v>317</v>
-      </c>
-      <c r="I127" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14524,12 +14702,9 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>3.256410256410256</v>
-      </c>
-      <c r="H128" t="n">
-        <v>317</v>
-      </c>
-      <c r="I128" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14557,12 +14732,9 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3.358974358974359</v>
-      </c>
-      <c r="H129" t="n">
-        <v>317</v>
-      </c>
-      <c r="I129" t="inlineStr"/>
+        <v>329</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14590,12 +14762,9 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>3.358974358974359</v>
-      </c>
-      <c r="H130" t="n">
-        <v>317</v>
-      </c>
-      <c r="I130" t="inlineStr">
+        <v>329</v>
+      </c>
+      <c r="H130" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -14627,12 +14796,9 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>318</v>
-      </c>
-      <c r="I131" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14660,12 +14826,9 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>318</v>
-      </c>
-      <c r="I132" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14693,12 +14856,9 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>318</v>
-      </c>
-      <c r="I133" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14726,12 +14886,9 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>0.06779661016949153</v>
-      </c>
-      <c r="H134" t="n">
-        <v>318</v>
-      </c>
-      <c r="I134" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14759,12 +14916,9 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0.1694915254237288</v>
-      </c>
-      <c r="H135" t="n">
-        <v>318</v>
-      </c>
-      <c r="I135" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14792,12 +14946,9 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>0.1864406779661017</v>
-      </c>
-      <c r="H136" t="n">
-        <v>318</v>
-      </c>
-      <c r="I136" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14825,12 +14976,9 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>0.3728813559322034</v>
-      </c>
-      <c r="H137" t="n">
-        <v>318</v>
-      </c>
-      <c r="I137" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14858,12 +15006,9 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0.5084745762711864</v>
-      </c>
-      <c r="H138" t="n">
-        <v>318</v>
-      </c>
-      <c r="I138" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14891,12 +15036,9 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0.8135593220338984</v>
-      </c>
-      <c r="H139" t="n">
-        <v>318</v>
-      </c>
-      <c r="I139" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14924,12 +15066,9 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1.169491525423729</v>
-      </c>
-      <c r="H140" t="n">
-        <v>318</v>
-      </c>
-      <c r="I140" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14957,12 +15096,9 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1.491525423728814</v>
-      </c>
-      <c r="H141" t="n">
-        <v>318</v>
-      </c>
-      <c r="I141" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14990,12 +15126,9 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1.88135593220339</v>
-      </c>
-      <c r="H142" t="n">
-        <v>318</v>
-      </c>
-      <c r="I142" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15023,12 +15156,9 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>2.203389830508474</v>
-      </c>
-      <c r="H143" t="n">
-        <v>318</v>
-      </c>
-      <c r="I143" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15056,12 +15186,9 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>2.372881355932203</v>
-      </c>
-      <c r="H144" t="n">
-        <v>318</v>
-      </c>
-      <c r="I144" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15089,12 +15216,9 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2.559322033898305</v>
-      </c>
-      <c r="H145" t="n">
-        <v>318</v>
-      </c>
-      <c r="I145" t="inlineStr"/>
+        <v>337</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15122,12 +15246,9 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>2.76271186440678</v>
-      </c>
-      <c r="H146" t="n">
-        <v>318</v>
-      </c>
-      <c r="I146" t="inlineStr">
+        <v>337</v>
+      </c>
+      <c r="H146" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -15159,12 +15280,9 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="H147" t="n">
-        <v>315</v>
-      </c>
-      <c r="I147" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15192,12 +15310,9 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>0.1025641025641026</v>
-      </c>
-      <c r="H148" t="n">
-        <v>315</v>
-      </c>
-      <c r="I148" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15225,12 +15340,9 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>0.1282051282051282</v>
-      </c>
-      <c r="H149" t="n">
-        <v>315</v>
-      </c>
-      <c r="I149" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15258,12 +15370,9 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="H150" t="n">
-        <v>315</v>
-      </c>
-      <c r="I150" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15291,12 +15400,9 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.9743589743589743</v>
-      </c>
-      <c r="H151" t="n">
-        <v>315</v>
-      </c>
-      <c r="I151" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15324,12 +15430,9 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1.41025641025641</v>
-      </c>
-      <c r="H152" t="n">
-        <v>315</v>
-      </c>
-      <c r="I152" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15357,12 +15460,9 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1.897435897435897</v>
-      </c>
-      <c r="H153" t="n">
-        <v>315</v>
-      </c>
-      <c r="I153" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15390,12 +15490,9 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>2.153846153846154</v>
-      </c>
-      <c r="H154" t="n">
-        <v>315</v>
-      </c>
-      <c r="I154" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15423,12 +15520,9 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>2.512820512820513</v>
-      </c>
-      <c r="H155" t="n">
-        <v>315</v>
-      </c>
-      <c r="I155" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15456,12 +15550,9 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>2.794871794871795</v>
-      </c>
-      <c r="H156" t="n">
-        <v>315</v>
-      </c>
-      <c r="I156" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15489,12 +15580,9 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>2.974358974358974</v>
-      </c>
-      <c r="H157" t="n">
-        <v>315</v>
-      </c>
-      <c r="I157" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15522,12 +15610,9 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>3.205128205128205</v>
-      </c>
-      <c r="H158" t="n">
-        <v>315</v>
-      </c>
-      <c r="I158" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15555,12 +15640,9 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>3.333333333333333</v>
-      </c>
-      <c r="H159" t="n">
-        <v>315</v>
-      </c>
-      <c r="I159" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15588,12 +15670,9 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>3.41025641025641</v>
-      </c>
-      <c r="H160" t="n">
-        <v>315</v>
-      </c>
-      <c r="I160" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15621,12 +15700,9 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>3.41025641025641</v>
-      </c>
-      <c r="H161" t="n">
-        <v>315</v>
-      </c>
-      <c r="I161" t="inlineStr"/>
+        <v>314</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15654,12 +15730,9 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>3.41025641025641</v>
-      </c>
-      <c r="H162" t="n">
-        <v>315</v>
-      </c>
-      <c r="I162" t="inlineStr">
+        <v>314</v>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -15668,7 +15741,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -15682,7 +15755,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -15691,17 +15764,14 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
-      </c>
-      <c r="H163" t="n">
-        <v>314</v>
-      </c>
-      <c r="I163" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
@@ -15715,7 +15785,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -15724,17 +15794,14 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="H164" t="n">
-        <v>314</v>
-      </c>
-      <c r="I164" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -15748,7 +15815,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -15757,17 +15824,14 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H165" t="n">
-        <v>314</v>
-      </c>
-      <c r="I165" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -15781,7 +15845,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -15790,17 +15854,14 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="H166" t="n">
-        <v>314</v>
-      </c>
-      <c r="I166" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -15814,7 +15875,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -15823,17 +15884,14 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.3666666666666666</v>
-      </c>
-      <c r="H167" t="n">
-        <v>314</v>
-      </c>
-      <c r="I167" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
@@ -15847,7 +15905,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -15856,17 +15914,14 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1.066666666666667</v>
-      </c>
-      <c r="H168" t="n">
-        <v>314</v>
-      </c>
-      <c r="I168" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
@@ -15880,7 +15935,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -15889,17 +15944,14 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H169" t="n">
-        <v>314</v>
-      </c>
-      <c r="I169" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
@@ -15913,7 +15965,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -15922,17 +15974,14 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>7.933333333333334</v>
-      </c>
-      <c r="H170" t="n">
-        <v>314</v>
-      </c>
-      <c r="I170" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
@@ -15946,7 +15995,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -15955,17 +16004,14 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>11.38333333333333</v>
-      </c>
-      <c r="H171" t="n">
-        <v>314</v>
-      </c>
-      <c r="I171" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -15979,7 +16025,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -15988,17 +16034,14 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>11.85</v>
-      </c>
-      <c r="H172" t="n">
-        <v>314</v>
-      </c>
-      <c r="I172" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -16012,7 +16055,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -16021,17 +16064,14 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>12</v>
-      </c>
-      <c r="H173" t="n">
-        <v>314</v>
-      </c>
-      <c r="I173" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -16045,7 +16085,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -16054,17 +16094,14 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="H174" t="n">
-        <v>314</v>
-      </c>
-      <c r="I174" t="inlineStr"/>
+        <v>328</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HW-BudbreakTP2020Control</t>
+          <t>HW-Budbreak2020Control</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -16078,7 +16115,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -16087,12 +16124,9 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="H175" t="n">
-        <v>314</v>
-      </c>
-      <c r="I175" t="inlineStr">
+        <v>328</v>
+      </c>
+      <c r="H175" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -16101,7 +16135,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -16115,7 +16149,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -16124,17 +16158,14 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
-      </c>
-      <c r="H176" t="n">
-        <v>320</v>
-      </c>
-      <c r="I176" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -16148,7 +16179,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -16157,17 +16188,14 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
-      </c>
-      <c r="H177" t="n">
-        <v>320</v>
-      </c>
-      <c r="I177" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -16181,7 +16209,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -16190,17 +16218,14 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
-      </c>
-      <c r="H178" t="n">
-        <v>320</v>
-      </c>
-      <c r="I178" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -16214,7 +16239,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -16223,17 +16248,14 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H179" t="n">
-        <v>320</v>
-      </c>
-      <c r="I179" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -16247,7 +16269,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -16256,17 +16278,14 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H180" t="n">
-        <v>320</v>
-      </c>
-      <c r="I180" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -16280,7 +16299,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -16289,17 +16308,14 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="H181" t="n">
-        <v>320</v>
-      </c>
-      <c r="I181" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -16313,7 +16329,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -16322,17 +16338,14 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>15.42</v>
-      </c>
-      <c r="H182" t="n">
-        <v>320</v>
-      </c>
-      <c r="I182" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -16346,7 +16359,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -16355,17 +16368,14 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="H183" t="n">
-        <v>320</v>
-      </c>
-      <c r="I183" t="inlineStr"/>
+        <v>327</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HWBBRawTP2021Control</t>
+          <t>HWBBRawKK2021Control</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -16379,7 +16389,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -16388,12 +16398,9 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>20.32</v>
-      </c>
-      <c r="H184" t="n">
-        <v>320</v>
-      </c>
-      <c r="I184" t="inlineStr">
+        <v>327</v>
+      </c>
+      <c r="H184" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -16402,21 +16409,21 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>44147</v>
+        <v>44879</v>
       </c>
       <c r="C185" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D185" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -16425,31 +16432,28 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0</v>
-      </c>
-      <c r="H185" t="n">
-        <v>322</v>
-      </c>
-      <c r="I185" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>44151</v>
+        <v>44881</v>
       </c>
       <c r="C186" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D186" t="n">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -16458,31 +16462,28 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>0.1180555555555556</v>
-      </c>
-      <c r="H186" t="n">
-        <v>322</v>
-      </c>
-      <c r="I186" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>44154</v>
+        <v>44883</v>
       </c>
       <c r="C187" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D187" t="n">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -16491,31 +16492,28 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.7916666666666666</v>
-      </c>
-      <c r="H187" t="n">
-        <v>322</v>
-      </c>
-      <c r="I187" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>44159</v>
+        <v>44886</v>
       </c>
       <c r="C188" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D188" t="n">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -16524,64 +16522,58 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>3.604166666666667</v>
-      </c>
-      <c r="H188" t="n">
-        <v>322</v>
-      </c>
-      <c r="I188" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>44162</v>
+        <v>44888</v>
       </c>
       <c r="C189" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D189" t="n">
+        <v>327</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
         <v>332</v>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Te Puke</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G189" t="n">
-        <v>5.847222222222222</v>
-      </c>
-      <c r="H189" t="n">
-        <v>322</v>
-      </c>
-      <c r="I189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>44166</v>
+        <v>44890</v>
       </c>
       <c r="C190" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D190" t="n">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Te Puke</t>
+          <t>Kerikeri</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -16590,45 +16582,433 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>6.958333333333333</v>
-      </c>
-      <c r="H190" t="n">
-        <v>322</v>
-      </c>
-      <c r="I190" t="inlineStr"/>
+        <v>332</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HW-Budbreak-TP2020Control</t>
+          <t>HWBBRawKK2022Control</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
+        <v>44893</v>
+      </c>
+      <c r="C191" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D191" t="n">
+        <v>332</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>332</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>44896</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D192" t="n">
+        <v>335</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>332</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>44900</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D193" t="n">
+        <v>339</v>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>332</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>44902</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D194" t="n">
+        <v>341</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>332</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>44904</v>
+      </c>
+      <c r="C195" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D195" t="n">
+        <v>343</v>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>332</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>44907</v>
+      </c>
+      <c r="C196" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D196" t="n">
+        <v>346</v>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>332</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>HWBBRawKK2022Control</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>44909</v>
+      </c>
+      <c r="C197" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D197" t="n">
+        <v>348</v>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>332</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>StartFlowering</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>44147</v>
+      </c>
+      <c r="C198" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D198" t="n">
+        <v>317</v>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>321</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>44151</v>
+      </c>
+      <c r="C199" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D199" t="n">
+        <v>321</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>321</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>44154</v>
+      </c>
+      <c r="C200" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D200" t="n">
+        <v>324</v>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G200" t="n">
+        <v>321</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>44159</v>
+      </c>
+      <c r="C201" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D201" t="n">
+        <v>329</v>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G201" t="n">
+        <v>321</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>44162</v>
+      </c>
+      <c r="C202" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D202" t="n">
+        <v>332</v>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G202" t="n">
+        <v>321</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>44166</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2020</v>
+      </c>
+      <c r="D203" t="n">
+        <v>336</v>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G203" t="n">
+        <v>321</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>HW-Budbreak-KK2020Control</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="n">
         <v>44169</v>
       </c>
-      <c r="C191" t="n">
+      <c r="C204" t="n">
         <v>2020</v>
       </c>
-      <c r="D191" t="n">
+      <c r="D204" t="n">
         <v>339</v>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Te Puke</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G191" t="n">
-        <v>6.645833333333333</v>
-      </c>
-      <c r="H191" t="n">
-        <v>322</v>
-      </c>
-      <c r="I191" t="inlineStr">
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Kerikeri</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G204" t="n">
+        <v>321</v>
+      </c>
+      <c r="H204" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>

--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K275"/>
+  <dimension ref="A1:K260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -596,7 +596,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -633,7 +633,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -667,10 +667,10 @@
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="I6" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -704,10 +704,10 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I7" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -741,10 +741,10 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="I8" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -778,13 +778,13 @@
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -932,10 +932,10 @@
         <v>0.5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -969,10 +969,10 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="I14" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>0.31</v>
+        <v>0.62</v>
       </c>
       <c r="I15" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -1043,10 +1043,10 @@
         <v>4.5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1080,13 +1080,13 @@
         <v>6.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="I22" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
       <c r="I23" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         <v>8</v>
       </c>
       <c r="H24" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="I24" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -1382,13 +1382,13 @@
         <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -1465,7 +1465,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -1502,7 +1502,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -1539,7 +1539,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -1573,10 +1573,10 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="I30" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -1610,10 +1610,10 @@
         <v>5</v>
       </c>
       <c r="H31" t="n">
-        <v>0.36</v>
+        <v>0.71</v>
       </c>
       <c r="I31" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1647,10 +1647,10 @@
         <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -1684,13 +1684,13 @@
         <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
@@ -1949,10 +1949,10 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I40" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         <v>1.5</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I41" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -2023,10 +2023,10 @@
         <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I42" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
@@ -2060,10 +2060,10 @@
         <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I43" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
@@ -2097,10 +2097,10 @@
         <v>5</v>
       </c>
       <c r="H44" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
@@ -2134,10 +2134,10 @@
         <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
@@ -2171,10 +2171,10 @@
         <v>5</v>
       </c>
       <c r="H46" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
@@ -2208,10 +2208,10 @@
         <v>5</v>
       </c>
       <c r="H47" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -2245,13 +2245,13 @@
         <v>5</v>
       </c>
       <c r="H48" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="J48" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -2362,10 +2362,10 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="I51" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         <v>3</v>
       </c>
       <c r="H52" t="n">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="I52" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         <v>6</v>
       </c>
       <c r="H53" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="I53" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
@@ -2473,13 +2473,13 @@
         <v>7</v>
       </c>
       <c r="H54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2590,10 +2590,10 @@
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="I57" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         <v>3</v>
       </c>
       <c r="H58" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         <v>5</v>
       </c>
       <c r="H59" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I59" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
@@ -2701,13 +2701,13 @@
         <v>6</v>
       </c>
       <c r="H60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I60" t="n">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
@@ -2818,10 +2818,10 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="I63" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         <v>2</v>
       </c>
       <c r="H64" t="n">
-        <v>0.12</v>
+        <v>0.25</v>
       </c>
       <c r="I64" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
@@ -2892,10 +2892,10 @@
         <v>4</v>
       </c>
       <c r="H65" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I65" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
@@ -2929,10 +2929,10 @@
         <v>6</v>
       </c>
       <c r="H66" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="I66" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
@@ -2966,10 +2966,10 @@
         <v>7</v>
       </c>
       <c r="H67" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="I67" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
@@ -3003,13 +3003,13 @@
         <v>8</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="J68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="I69" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
@@ -3120,10 +3120,10 @@
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="I71" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
@@ -3157,10 +3157,10 @@
         <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="I72" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
@@ -3194,10 +3194,10 @@
         <v>3</v>
       </c>
       <c r="H73" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="I73" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
@@ -3231,10 +3231,10 @@
         <v>5</v>
       </c>
       <c r="H74" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I74" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         <v>6</v>
       </c>
       <c r="H75" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3305,13 +3305,13 @@
         <v>6</v>
       </c>
       <c r="H76" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
@@ -3388,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
@@ -3462,7 +3462,7 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
@@ -3499,7 +3499,7 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
@@ -3533,10 +3533,10 @@
         <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.08</v>
+        <v>0.17</v>
       </c>
       <c r="I82" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
         <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="I83" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
@@ -3607,10 +3607,10 @@
         <v>4</v>
       </c>
       <c r="H84" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I84" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
@@ -3644,10 +3644,10 @@
         <v>5</v>
       </c>
       <c r="H85" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I85" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
@@ -3681,10 +3681,10 @@
         <v>5</v>
       </c>
       <c r="H86" t="n">
-        <v>0.42</v>
+        <v>0.83</v>
       </c>
       <c r="I86" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
@@ -3718,13 +3718,13 @@
         <v>6</v>
       </c>
       <c r="H87" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="J87" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
@@ -3838,7 +3838,7 @@
         <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
@@ -3875,7 +3875,7 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
@@ -3912,7 +3912,7 @@
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I93" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I94" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
@@ -4020,10 +4020,10 @@
         <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I95" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
@@ -4057,10 +4057,10 @@
         <v>3</v>
       </c>
       <c r="H96" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="I96" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
@@ -4094,10 +4094,10 @@
         <v>4</v>
       </c>
       <c r="H97" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I97" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
@@ -4131,10 +4131,10 @@
         <v>4</v>
       </c>
       <c r="H98" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I98" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         <v>5</v>
       </c>
       <c r="H99" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J99" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="I100" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4288,7 +4288,7 @@
         <v>0</v>
       </c>
       <c r="I102" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
@@ -4322,10 +4322,10 @@
         <v>1</v>
       </c>
       <c r="H103" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I103" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr"/>
@@ -4359,10 +4359,10 @@
         <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I104" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
@@ -4396,10 +4396,10 @@
         <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I105" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
@@ -4433,10 +4433,10 @@
         <v>3</v>
       </c>
       <c r="H106" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
@@ -4470,10 +4470,10 @@
         <v>5</v>
       </c>
       <c r="H107" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="I107" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         <v>6</v>
       </c>
       <c r="H108" t="n">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="I108" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
@@ -4544,10 +4544,10 @@
         <v>6.5</v>
       </c>
       <c r="H109" t="n">
-        <v>0.31</v>
+        <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
@@ -4581,10 +4581,10 @@
         <v>7</v>
       </c>
       <c r="H110" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
@@ -4618,13 +4618,13 @@
         <v>7</v>
       </c>
       <c r="H111" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="J111" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr"/>
@@ -4738,7 +4738,7 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
@@ -4809,10 +4809,10 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I116" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         <v>4</v>
       </c>
       <c r="H117" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I117" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -4883,13 +4883,13 @@
         <v>5</v>
       </c>
       <c r="H118" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="J118" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
@@ -4966,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
@@ -5003,7 +5003,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5037,10 +5037,10 @@
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="I122" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
@@ -5074,10 +5074,10 @@
         <v>2</v>
       </c>
       <c r="H123" t="n">
-        <v>0.14</v>
+        <v>0.29</v>
       </c>
       <c r="I123" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
@@ -5111,10 +5111,10 @@
         <v>4</v>
       </c>
       <c r="H124" t="n">
-        <v>0.29</v>
+        <v>0.57</v>
       </c>
       <c r="I124" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
@@ -5148,10 +5148,10 @@
         <v>6</v>
       </c>
       <c r="H125" t="n">
-        <v>0.43</v>
+        <v>0.86</v>
       </c>
       <c r="I125" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
         <v>7</v>
       </c>
       <c r="H126" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
@@ -5222,13 +5222,13 @@
         <v>7</v>
       </c>
       <c r="H127" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="J127" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
@@ -5305,7 +5305,7 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
@@ -5342,7 +5342,7 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
@@ -5379,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
@@ -5413,10 +5413,10 @@
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I132" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
@@ -5450,10 +5450,10 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I133" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
@@ -5487,10 +5487,10 @@
         <v>2</v>
       </c>
       <c r="H134" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I134" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
@@ -5524,10 +5524,10 @@
         <v>4</v>
       </c>
       <c r="H135" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I135" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
@@ -5561,10 +5561,10 @@
         <v>5</v>
       </c>
       <c r="H136" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I136" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         <v>5</v>
       </c>
       <c r="H137" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
@@ -5635,10 +5635,10 @@
         <v>5</v>
       </c>
       <c r="H138" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
@@ -5672,13 +5672,13 @@
         <v>5</v>
       </c>
       <c r="H139" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="J139" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
@@ -5755,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
@@ -5792,7 +5792,7 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
@@ -5826,10 +5826,10 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I143" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
@@ -5863,10 +5863,10 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="I144" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
@@ -5900,10 +5900,10 @@
         <v>2</v>
       </c>
       <c r="H145" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="I145" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
@@ -5937,10 +5937,10 @@
         <v>3.5</v>
       </c>
       <c r="H146" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="I146" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr"/>
@@ -5974,13 +5974,13 @@
         <v>5</v>
       </c>
       <c r="H147" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="J147" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
@@ -6057,7 +6057,7 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
@@ -6094,7 +6094,7 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
@@ -6168,7 +6168,7 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="I155" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
@@ -6313,10 +6313,10 @@
         <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="I156" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
@@ -6350,10 +6350,10 @@
         <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="I157" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
@@ -6387,10 +6387,10 @@
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="I158" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
@@ -6424,10 +6424,10 @@
         <v>2</v>
       </c>
       <c r="H159" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="I159" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
@@ -6461,10 +6461,10 @@
         <v>3</v>
       </c>
       <c r="H160" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I160" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
@@ -6498,10 +6498,10 @@
         <v>3</v>
       </c>
       <c r="H161" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I161" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
@@ -6535,10 +6535,10 @@
         <v>3</v>
       </c>
       <c r="H162" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I162" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
@@ -6572,13 +6572,13 @@
         <v>4</v>
       </c>
       <c r="H163" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>292</v>
+        <v>267</v>
       </c>
       <c r="J163" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
@@ -6692,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr"/>
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr"/>
@@ -6800,10 +6800,10 @@
         <v>1</v>
       </c>
       <c r="H169" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I169" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         <v>1</v>
       </c>
       <c r="H170" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I170" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J170" t="inlineStr"/>
       <c r="K170" t="inlineStr"/>
@@ -6874,10 +6874,10 @@
         <v>1</v>
       </c>
       <c r="H171" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I171" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr"/>
@@ -6911,10 +6911,10 @@
         <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I172" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr"/>
@@ -6948,10 +6948,10 @@
         <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I173" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr"/>
@@ -6985,10 +6985,10 @@
         <v>1</v>
       </c>
       <c r="H174" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I174" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr"/>
@@ -7022,10 +7022,10 @@
         <v>2</v>
       </c>
       <c r="H175" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I175" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         <v>2</v>
       </c>
       <c r="H176" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I176" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr"/>
@@ -7096,10 +7096,10 @@
         <v>4</v>
       </c>
       <c r="H177" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="I177" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr"/>
@@ -7133,10 +7133,10 @@
         <v>4</v>
       </c>
       <c r="H178" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="I178" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr"/>
@@ -7170,10 +7170,10 @@
         <v>5</v>
       </c>
       <c r="H179" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="I179" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr"/>
@@ -7207,10 +7207,10 @@
         <v>6</v>
       </c>
       <c r="H180" t="n">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="I180" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
         <v>6</v>
       </c>
       <c r="H181" t="n">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="I181" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr"/>
@@ -7281,10 +7281,10 @@
         <v>7</v>
       </c>
       <c r="H182" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I182" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr"/>
@@ -7318,13 +7318,13 @@
         <v>7</v>
       </c>
       <c r="H183" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="J183" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
@@ -7364,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr"/>
@@ -7401,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="I185" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr"/>
@@ -7475,7 +7475,7 @@
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr"/>
@@ -7512,7 +7512,7 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr"/>
@@ -7586,7 +7586,7 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr"/>
@@ -7623,7 +7623,7 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr"/>
@@ -7660,7 +7660,7 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr"/>
@@ -7694,10 +7694,10 @@
         <v>0.5</v>
       </c>
       <c r="H193" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="I193" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr"/>
@@ -7731,10 +7731,10 @@
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>0.11</v>
+        <v>0.33</v>
       </c>
       <c r="I194" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr"/>
@@ -7768,10 +7768,10 @@
         <v>2</v>
       </c>
       <c r="H195" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="I195" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
@@ -7805,10 +7805,10 @@
         <v>2.5</v>
       </c>
       <c r="H196" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="I196" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr"/>
@@ -7842,10 +7842,10 @@
         <v>3</v>
       </c>
       <c r="H197" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I197" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr"/>
@@ -7879,10 +7879,10 @@
         <v>3</v>
       </c>
       <c r="H198" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr"/>
@@ -7916,13 +7916,13 @@
         <v>3</v>
       </c>
       <c r="H199" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I199" t="n">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="J199" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr"/>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr"/>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr"/>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr"/>
@@ -8110,7 +8110,7 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr"/>
@@ -8147,7 +8147,7 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
@@ -8181,10 +8181,10 @@
         <v>0.5</v>
       </c>
       <c r="H206" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="I206" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr"/>
@@ -8218,10 +8218,10 @@
         <v>1.5</v>
       </c>
       <c r="H207" t="n">
-        <v>0.16</v>
+        <v>0.5</v>
       </c>
       <c r="I207" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr"/>
@@ -8255,10 +8255,10 @@
         <v>2</v>
       </c>
       <c r="H208" t="n">
-        <v>0.22</v>
+        <v>0.67</v>
       </c>
       <c r="I208" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr"/>
@@ -8292,10 +8292,10 @@
         <v>2.5</v>
       </c>
       <c r="H209" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="I209" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr"/>
@@ -8329,10 +8329,10 @@
         <v>2.5</v>
       </c>
       <c r="H210" t="n">
-        <v>0.28</v>
+        <v>0.83</v>
       </c>
       <c r="I210" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr"/>
@@ -8366,13 +8366,13 @@
         <v>3</v>
       </c>
       <c r="H211" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I211" t="n">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="J211" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B212" s="2" t="n">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8412,7 +8412,7 @@
         <v>0</v>
       </c>
       <c r="I212" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr"/>
@@ -8420,7 +8420,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B213" s="2" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -8449,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="I213" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr"/>
@@ -8457,7 +8457,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B214" s="2" t="n">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -8486,7 +8486,7 @@
         <v>0</v>
       </c>
       <c r="I214" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
@@ -8494,7 +8494,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B215" s="2" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -8523,7 +8523,7 @@
         <v>0</v>
       </c>
       <c r="I215" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr"/>
@@ -8531,7 +8531,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B216" s="2" t="n">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -8560,7 +8560,7 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr"/>
@@ -8568,7 +8568,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B217" s="2" t="n">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8597,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
@@ -8605,7 +8605,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B218" s="2" t="n">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8634,7 +8634,7 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr"/>
@@ -8642,7 +8642,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B219" s="2" t="n">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8671,7 +8671,7 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr"/>
@@ -8679,7 +8679,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B220" s="2" t="n">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8705,10 +8705,10 @@
         <v>1</v>
       </c>
       <c r="H220" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I220" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr"/>
@@ -8716,7 +8716,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B221" s="2" t="n">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8742,10 +8742,10 @@
         <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I221" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr"/>
@@ -8753,7 +8753,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B222" s="2" t="n">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8779,10 +8779,10 @@
         <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="I222" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B223" s="2" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8816,10 +8816,10 @@
         <v>2</v>
       </c>
       <c r="H223" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I223" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr"/>
@@ -8827,7 +8827,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B224" s="2" t="n">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8853,10 +8853,10 @@
         <v>2</v>
       </c>
       <c r="H224" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="I224" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr"/>
@@ -8864,7 +8864,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B225" s="2" t="n">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8890,10 +8890,10 @@
         <v>3</v>
       </c>
       <c r="H225" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="I225" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J225" t="inlineStr"/>
       <c r="K225" t="inlineStr"/>
@@ -8901,7 +8901,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B226" s="2" t="n">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8927,10 +8927,10 @@
         <v>4</v>
       </c>
       <c r="H226" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I226" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr"/>
@@ -8938,7 +8938,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B227" s="2" t="n">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -8964,10 +8964,10 @@
         <v>4</v>
       </c>
       <c r="H227" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="I227" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr"/>
@@ -8975,7 +8975,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B228" s="2" t="n">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -9001,10 +9001,10 @@
         <v>5</v>
       </c>
       <c r="H228" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr"/>
@@ -9012,7 +9012,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B229" s="2" t="n">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -9038,10 +9038,10 @@
         <v>5</v>
       </c>
       <c r="H229" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr"/>
@@ -9049,7 +9049,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B230" s="2" t="n">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -9075,10 +9075,10 @@
         <v>5</v>
       </c>
       <c r="H230" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr"/>
@@ -9086,7 +9086,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B231" s="2" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -9112,13 +9112,13 @@
         <v>5</v>
       </c>
       <c r="H231" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="J231" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B232" s="2" t="n">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr"/>
@@ -9166,7 +9166,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B233" s="2" t="n">
@@ -9180,7 +9180,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9195,7 +9195,7 @@
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr"/>
@@ -9203,7 +9203,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B234" s="2" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9232,7 +9232,7 @@
         <v>0</v>
       </c>
       <c r="I234" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr"/>
@@ -9240,7 +9240,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B235" s="2" t="n">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr"/>
@@ -9277,7 +9277,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B236" s="2" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9306,7 +9306,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J236" t="inlineStr"/>
       <c r="K236" t="inlineStr"/>
@@ -9314,7 +9314,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B237" s="2" t="n">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -9343,7 +9343,7 @@
         <v>0</v>
       </c>
       <c r="I237" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr"/>
@@ -9351,7 +9351,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B238" s="2" t="n">
@@ -9365,7 +9365,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9380,7 +9380,7 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J238" t="inlineStr"/>
       <c r="K238" t="inlineStr"/>
@@ -9388,7 +9388,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B239" s="2" t="n">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -9417,7 +9417,7 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr"/>
@@ -9425,7 +9425,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B240" s="2" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -9451,10 +9451,10 @@
         <v>2</v>
       </c>
       <c r="H240" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="I240" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr"/>
@@ -9462,7 +9462,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B241" s="2" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -9488,10 +9488,10 @@
         <v>3</v>
       </c>
       <c r="H241" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="I241" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr"/>
@@ -9499,7 +9499,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B242" s="2" t="n">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -9525,10 +9525,10 @@
         <v>5</v>
       </c>
       <c r="H242" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="I242" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr"/>
@@ -9536,7 +9536,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B243" s="2" t="n">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -9562,10 +9562,10 @@
         <v>6</v>
       </c>
       <c r="H243" t="n">
-        <v>0.28</v>
+        <v>0.86</v>
       </c>
       <c r="I243" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr"/>
@@ -9573,7 +9573,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B244" s="2" t="n">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -9599,10 +9599,10 @@
         <v>6.5</v>
       </c>
       <c r="H244" t="n">
-        <v>0.31</v>
+        <v>0.93</v>
       </c>
       <c r="I244" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr"/>
@@ -9610,7 +9610,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B245" s="2" t="n">
@@ -9624,7 +9624,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -9636,10 +9636,10 @@
         <v>7</v>
       </c>
       <c r="H245" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr"/>
@@ -9647,7 +9647,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B246" s="2" t="n">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -9673,13 +9673,13 @@
         <v>7</v>
       </c>
       <c r="H246" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="J246" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
@@ -9690,21 +9690,21 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B247" s="2" t="n">
-        <v>44817</v>
+        <v>44088</v>
       </c>
       <c r="C247" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D247" t="n">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr"/>
@@ -9727,21 +9727,21 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B248" s="2" t="n">
-        <v>44823</v>
+        <v>44092</v>
       </c>
       <c r="C248" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D248" t="n">
         <v>262</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -9756,7 +9756,7 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr"/>
@@ -9764,21 +9764,21 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B249" s="2" t="n">
-        <v>44827</v>
+        <v>44095</v>
       </c>
       <c r="C249" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D249" t="n">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -9793,7 +9793,7 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
@@ -9801,21 +9801,21 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B250" s="2" t="n">
-        <v>44832</v>
+        <v>44098</v>
       </c>
       <c r="C250" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D250" t="n">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9830,7 +9830,7 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr"/>
@@ -9838,21 +9838,21 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B251" s="2" t="n">
-        <v>44834</v>
+        <v>44102</v>
       </c>
       <c r="C251" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D251" t="n">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -9861,13 +9861,13 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="I251" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr"/>
@@ -9875,21 +9875,21 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B252" s="2" t="n">
-        <v>44841</v>
+        <v>44104</v>
       </c>
       <c r="C252" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D252" t="n">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -9898,13 +9898,13 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="I252" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr"/>
@@ -9912,21 +9912,21 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B253" s="2" t="n">
-        <v>44844</v>
+        <v>44106</v>
       </c>
       <c r="C253" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D253" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -9935,13 +9935,13 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H253" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="I253" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr"/>
@@ -9949,21 +9949,21 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B254" s="2" t="n">
-        <v>44848</v>
+        <v>44109</v>
       </c>
       <c r="C254" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D254" t="n">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -9972,13 +9972,13 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H254" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="I254" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr"/>
@@ -9986,21 +9986,21 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B255" s="2" t="n">
-        <v>44851</v>
+        <v>44022</v>
       </c>
       <c r="C255" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D255" t="n">
-        <v>290</v>
+        <v>192</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -10009,13 +10009,13 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H255" t="n">
-        <v>0.13</v>
+        <v>0.83</v>
       </c>
       <c r="I255" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr"/>
@@ -10023,21 +10023,21 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B256" s="2" t="n">
-        <v>44854</v>
+        <v>44175</v>
       </c>
       <c r="C256" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D256" t="n">
-        <v>293</v>
+        <v>345</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10046,13 +10046,13 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H256" t="n">
-        <v>0.2</v>
+        <v>0.83</v>
       </c>
       <c r="I256" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr"/>
@@ -10060,21 +10060,21 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B257" s="2" t="n">
-        <v>44859</v>
+        <v>44118</v>
       </c>
       <c r="C257" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D257" t="n">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10083,13 +10083,13 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H257" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="I257" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr"/>
@@ -10097,21 +10097,21 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B258" s="2" t="n">
-        <v>44862</v>
+        <v>44120</v>
       </c>
       <c r="C258" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D258" t="n">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10120,13 +10120,13 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H258" t="n">
-        <v>0.26</v>
+        <v>1</v>
       </c>
       <c r="I258" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr"/>
@@ -10134,21 +10134,21 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B259" s="2" t="n">
-        <v>44866</v>
+        <v>44123</v>
       </c>
       <c r="C259" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D259" t="n">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10157,13 +10157,13 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H259" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I259" t="n">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="J259" t="inlineStr"/>
       <c r="K259" t="inlineStr"/>
@@ -10171,21 +10171,21 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B260" s="2" t="n">
-        <v>44869</v>
+        <v>44127</v>
       </c>
       <c r="C260" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D260" t="n">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -10194,579 +10194,18 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H260" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I260" t="n">
-        <v>290</v>
-      </c>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="n">
-        <v>44872</v>
-      </c>
-      <c r="C261" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D261" t="n">
-        <v>311</v>
-      </c>
-      <c r="E261" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F261" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G261" t="n">
-        <v>5</v>
-      </c>
-      <c r="H261" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I261" t="n">
-        <v>290</v>
-      </c>
-      <c r="J261" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>StartFlowering</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B262" s="2" t="n">
-        <v>44088</v>
-      </c>
-      <c r="C262" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D262" t="n">
-        <v>258</v>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" t="n">
-        <v>274</v>
-      </c>
-      <c r="J262" t="inlineStr"/>
-      <c r="K262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="n">
-        <v>44092</v>
-      </c>
-      <c r="C263" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D263" t="n">
-        <v>262</v>
-      </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F263" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G263" t="n">
-        <v>0</v>
-      </c>
-      <c r="H263" t="n">
-        <v>0</v>
-      </c>
-      <c r="I263" t="n">
-        <v>274</v>
-      </c>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B264" s="2" t="n">
-        <v>44095</v>
-      </c>
-      <c r="C264" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D264" t="n">
-        <v>265</v>
-      </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F264" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G264" t="n">
-        <v>0</v>
-      </c>
-      <c r="H264" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" t="n">
-        <v>274</v>
-      </c>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B265" s="2" t="n">
-        <v>44098</v>
-      </c>
-      <c r="C265" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D265" t="n">
-        <v>268</v>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G265" t="n">
-        <v>0</v>
-      </c>
-      <c r="H265" t="n">
-        <v>0</v>
-      </c>
-      <c r="I265" t="n">
-        <v>274</v>
-      </c>
-      <c r="J265" t="inlineStr"/>
-      <c r="K265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B266" s="2" t="n">
-        <v>44102</v>
-      </c>
-      <c r="C266" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D266" t="n">
-        <v>272</v>
-      </c>
-      <c r="E266" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F266" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G266" t="n">
+        <v>264</v>
+      </c>
+      <c r="J260" t="n">
         <v>1</v>
       </c>
-      <c r="H266" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I266" t="n">
-        <v>274</v>
-      </c>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B267" s="2" t="n">
-        <v>44104</v>
-      </c>
-      <c r="C267" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D267" t="n">
-        <v>274</v>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G267" t="n">
-        <v>2</v>
-      </c>
-      <c r="H267" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I267" t="n">
-        <v>274</v>
-      </c>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B268" s="2" t="n">
-        <v>44106</v>
-      </c>
-      <c r="C268" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D268" t="n">
-        <v>276</v>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G268" t="n">
-        <v>2</v>
-      </c>
-      <c r="H268" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I268" t="n">
-        <v>274</v>
-      </c>
-      <c r="J268" t="inlineStr"/>
-      <c r="K268" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B269" s="2" t="n">
-        <v>44109</v>
-      </c>
-      <c r="C269" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D269" t="n">
-        <v>279</v>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G269" t="n">
-        <v>4</v>
-      </c>
-      <c r="H269" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I269" t="n">
-        <v>274</v>
-      </c>
-      <c r="J269" t="inlineStr"/>
-      <c r="K269" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B270" s="2" t="n">
-        <v>44022</v>
-      </c>
-      <c r="C270" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D270" t="n">
-        <v>192</v>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G270" t="n">
-        <v>5</v>
-      </c>
-      <c r="H270" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I270" t="n">
-        <v>274</v>
-      </c>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B271" s="2" t="n">
-        <v>44175</v>
-      </c>
-      <c r="C271" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D271" t="n">
-        <v>345</v>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G271" t="n">
-        <v>5</v>
-      </c>
-      <c r="H271" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I271" t="n">
-        <v>274</v>
-      </c>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B272" s="2" t="n">
-        <v>44118</v>
-      </c>
-      <c r="C272" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D272" t="n">
-        <v>288</v>
-      </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G272" t="n">
-        <v>5</v>
-      </c>
-      <c r="H272" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="I272" t="n">
-        <v>274</v>
-      </c>
-      <c r="J272" t="inlineStr"/>
-      <c r="K272" t="inlineStr"/>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B273" s="2" t="n">
-        <v>44120</v>
-      </c>
-      <c r="C273" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D273" t="n">
-        <v>290</v>
-      </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G273" t="n">
-        <v>6</v>
-      </c>
-      <c r="H273" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I273" t="n">
-        <v>274</v>
-      </c>
-      <c r="J273" t="inlineStr"/>
-      <c r="K273" t="inlineStr"/>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B274" s="2" t="n">
-        <v>44123</v>
-      </c>
-      <c r="C274" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D274" t="n">
-        <v>293</v>
-      </c>
-      <c r="E274" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G274" t="n">
-        <v>6</v>
-      </c>
-      <c r="H274" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I274" t="n">
-        <v>274</v>
-      </c>
-      <c r="J274" t="inlineStr"/>
-      <c r="K274" t="inlineStr"/>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B275" s="2" t="n">
-        <v>44127</v>
-      </c>
-      <c r="C275" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D275" t="n">
-        <v>297</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G275" t="n">
-        <v>6</v>
-      </c>
-      <c r="H275" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="I275" t="n">
-        <v>274</v>
-      </c>
-      <c r="J275" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="K275" t="inlineStr">
+      <c r="K260" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -10783,7 +10222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H204"/>
+  <dimension ref="A1:I191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10819,10 +10258,15 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>KiwiFruit.Phenology.Flowers</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>KiwiFruit.Phenology.FloweringDOY</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>KiwiFruit.Phenology.CurrentStageName</t>
         </is>
@@ -10854,9 +10298,12 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>335</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>327</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10884,9 +10331,12 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>335</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="H3" t="n">
+        <v>327</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10914,9 +10364,12 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>335</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>2.421052631578947</v>
+      </c>
+      <c r="H4" t="n">
+        <v>327</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10944,9 +10397,12 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>335</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>8.157894736842104</v>
+      </c>
+      <c r="H5" t="n">
+        <v>327</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10974,9 +10430,12 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>335</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>17.94736842105263</v>
+      </c>
+      <c r="H6" t="n">
+        <v>327</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -11004,9 +10463,12 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>335</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>18.52631578947368</v>
+      </c>
+      <c r="H7" t="n">
+        <v>327</v>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11038,9 +10500,12 @@
         </is>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>330</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -11068,9 +10533,12 @@
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>330</v>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -11098,9 +10566,12 @@
         </is>
       </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
         <v>330</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -11128,9 +10599,12 @@
         </is>
       </c>
       <c r="G11" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H11" t="n">
         <v>330</v>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -11158,9 +10632,12 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="H12" t="n">
         <v>330</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -11188,9 +10665,12 @@
         </is>
       </c>
       <c r="G13" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="H13" t="n">
         <v>330</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11222,9 +10702,12 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>327</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>323</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -11252,9 +10735,12 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>327</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>323</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -11282,9 +10768,12 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>327</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>323</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -11312,9 +10801,12 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>327</v>
-      </c>
-      <c r="H17" t="inlineStr"/>
+        <v>0.4</v>
+      </c>
+      <c r="H17" t="n">
+        <v>323</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -11342,9 +10834,12 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>327</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>6.8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>323</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -11372,9 +10867,12 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>327</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>22.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>323</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -11402,9 +10900,12 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>327</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>37.6</v>
+      </c>
+      <c r="H20" t="n">
+        <v>323</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -11432,9 +10933,12 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>327</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>37.6</v>
+      </c>
+      <c r="H21" t="n">
+        <v>323</v>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11466,9 +10970,12 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>327</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>323</v>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -11496,9 +11003,12 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>327</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>323</v>
+      </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -11526,9 +11036,12 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>327</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>323</v>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -11556,9 +11069,12 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>327</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>1.636363636363636</v>
+      </c>
+      <c r="H25" t="n">
+        <v>323</v>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -11586,9 +11102,12 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>327</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>7.818181818181818</v>
+      </c>
+      <c r="H26" t="n">
+        <v>323</v>
+      </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -11616,9 +11135,12 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>327</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
+        <v>18.81818181818182</v>
+      </c>
+      <c r="H27" t="n">
+        <v>323</v>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11646,9 +11168,12 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>327</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>31.18181818181818</v>
+      </c>
+      <c r="H28" t="n">
+        <v>323</v>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -11676,9 +11201,12 @@
         </is>
       </c>
       <c r="G29" t="n">
-        <v>327</v>
-      </c>
-      <c r="H29" t="inlineStr">
+        <v>32</v>
+      </c>
+      <c r="H29" t="n">
+        <v>323</v>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11710,9 +11238,12 @@
         </is>
       </c>
       <c r="G30" t="n">
-        <v>327</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>323</v>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11740,9 +11271,12 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>327</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>323</v>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -11770,9 +11304,12 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>327</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="H32" t="n">
+        <v>323</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -11800,9 +11337,12 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>327</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>2.9</v>
+      </c>
+      <c r="H33" t="n">
+        <v>323</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11830,9 +11370,12 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>327</v>
-      </c>
-      <c r="H34" t="inlineStr"/>
+        <v>6.066666666666666</v>
+      </c>
+      <c r="H34" t="n">
+        <v>323</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -11860,9 +11403,12 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>327</v>
-      </c>
-      <c r="H35" t="inlineStr"/>
+        <v>18.9</v>
+      </c>
+      <c r="H35" t="n">
+        <v>323</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -11890,9 +11436,12 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>327</v>
-      </c>
-      <c r="H36" t="inlineStr"/>
+        <v>19.76666666666667</v>
+      </c>
+      <c r="H36" t="n">
+        <v>323</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -11920,9 +11469,12 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>327</v>
-      </c>
-      <c r="H37" t="inlineStr">
+        <v>20.73333333333333</v>
+      </c>
+      <c r="H37" t="n">
+        <v>323</v>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -11954,9 +11506,12 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>329</v>
-      </c>
-      <c r="H38" t="inlineStr"/>
+        <v>0.59375</v>
+      </c>
+      <c r="H38" t="n">
+        <v>323</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -11984,9 +11539,12 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>329</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="H39" t="n">
+        <v>323</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -12014,9 +11572,12 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>329</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>13.96875</v>
+      </c>
+      <c r="H40" t="n">
+        <v>323</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12044,9 +11605,12 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>329</v>
-      </c>
-      <c r="H41" t="inlineStr">
+        <v>29.671875</v>
+      </c>
+      <c r="H41" t="n">
+        <v>323</v>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12078,9 +11642,12 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>329</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>0.078125</v>
+      </c>
+      <c r="H42" t="n">
+        <v>324</v>
+      </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -12108,9 +11675,12 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>329</v>
-      </c>
-      <c r="H43" t="inlineStr"/>
+        <v>4.234375</v>
+      </c>
+      <c r="H43" t="n">
+        <v>324</v>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -12138,9 +11708,12 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>329</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>16.9375</v>
+      </c>
+      <c r="H44" t="n">
+        <v>324</v>
+      </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -12168,9 +11741,12 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>329</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>19.71875</v>
+      </c>
+      <c r="H45" t="n">
+        <v>324</v>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12198,9 +11774,12 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>329</v>
-      </c>
-      <c r="H46" t="inlineStr">
+        <v>20.171875</v>
+      </c>
+      <c r="H46" t="n">
+        <v>324</v>
+      </c>
+      <c r="I46" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12232,9 +11811,12 @@
         </is>
       </c>
       <c r="G47" t="n">
+        <v>2.53968253968254</v>
+      </c>
+      <c r="H47" t="n">
         <v>320</v>
       </c>
-      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12262,9 +11844,12 @@
         </is>
       </c>
       <c r="G48" t="n">
+        <v>11.28571428571429</v>
+      </c>
+      <c r="H48" t="n">
         <v>320</v>
       </c>
-      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12292,9 +11877,12 @@
         </is>
       </c>
       <c r="G49" t="n">
+        <v>21.73015873015873</v>
+      </c>
+      <c r="H49" t="n">
         <v>320</v>
       </c>
-      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12322,9 +11910,12 @@
         </is>
       </c>
       <c r="G50" t="n">
+        <v>23.09523809523809</v>
+      </c>
+      <c r="H50" t="n">
         <v>320</v>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12356,9 +11947,12 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>324</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>1.703125</v>
+      </c>
+      <c r="H51" t="n">
+        <v>320</v>
+      </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -12386,9 +11980,12 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>324</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>11.1875</v>
+      </c>
+      <c r="H52" t="n">
+        <v>320</v>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -12416,9 +12013,12 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>324</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>21.40625</v>
+      </c>
+      <c r="H53" t="n">
+        <v>320</v>
+      </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -12446,9 +12046,12 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>324</v>
-      </c>
-      <c r="H54" t="inlineStr">
+        <v>23.390625</v>
+      </c>
+      <c r="H54" t="n">
+        <v>320</v>
+      </c>
+      <c r="I54" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12480,9 +12083,12 @@
         </is>
       </c>
       <c r="G55" t="n">
+        <v>2.640625</v>
+      </c>
+      <c r="H55" t="n">
         <v>320</v>
       </c>
-      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -12510,9 +12116,12 @@
         </is>
       </c>
       <c r="G56" t="n">
+        <v>11.484375</v>
+      </c>
+      <c r="H56" t="n">
         <v>320</v>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -12540,9 +12149,12 @@
         </is>
       </c>
       <c r="G57" t="n">
+        <v>21.765625</v>
+      </c>
+      <c r="H57" t="n">
         <v>320</v>
       </c>
-      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -12570,9 +12182,12 @@
         </is>
       </c>
       <c r="G58" t="n">
+        <v>23.109375</v>
+      </c>
+      <c r="H58" t="n">
         <v>320</v>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12604,9 +12219,12 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>329</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>0.234375</v>
+      </c>
+      <c r="H59" t="n">
+        <v>325</v>
+      </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -12634,9 +12252,12 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>329</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>1.15625</v>
+      </c>
+      <c r="H60" t="n">
+        <v>325</v>
+      </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -12664,9 +12285,12 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>329</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>2.84375</v>
+      </c>
+      <c r="H61" t="n">
+        <v>325</v>
+      </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -12694,9 +12318,12 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>329</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>14.734375</v>
+      </c>
+      <c r="H62" t="n">
+        <v>325</v>
+      </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -12724,9 +12351,12 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>329</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>18.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>325</v>
+      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12754,9 +12384,12 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>329</v>
-      </c>
-      <c r="H64" t="inlineStr">
+        <v>20.28125</v>
+      </c>
+      <c r="H64" t="n">
+        <v>325</v>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12788,9 +12421,12 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>334</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>0.90625</v>
+      </c>
+      <c r="H65" t="n">
+        <v>329</v>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -12818,9 +12454,12 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>334</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>4.890625</v>
+      </c>
+      <c r="H66" t="n">
+        <v>329</v>
+      </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -12848,9 +12487,12 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>334</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>12.125</v>
+      </c>
+      <c r="H67" t="n">
+        <v>329</v>
+      </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -12878,9 +12520,12 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>334</v>
-      </c>
-      <c r="H68" t="inlineStr">
+        <v>13.421875</v>
+      </c>
+      <c r="H68" t="n">
+        <v>329</v>
+      </c>
+      <c r="I68" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -12912,9 +12557,12 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>342</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>0.015625</v>
+      </c>
+      <c r="H69" t="n">
+        <v>320</v>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -12942,9 +12590,12 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>342</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>0.09375</v>
+      </c>
+      <c r="H70" t="n">
+        <v>320</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -12972,9 +12623,12 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>342</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>0.4375</v>
+      </c>
+      <c r="H71" t="n">
+        <v>320</v>
+      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -13002,9 +12656,12 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>342</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>2.828125</v>
+      </c>
+      <c r="H72" t="n">
+        <v>320</v>
+      </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13032,9 +12689,12 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>342</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>10.28125</v>
+      </c>
+      <c r="H73" t="n">
+        <v>320</v>
+      </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -13062,9 +12722,12 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>342</v>
-      </c>
-      <c r="H74" t="inlineStr">
+        <v>12.5625</v>
+      </c>
+      <c r="H74" t="n">
+        <v>320</v>
+      </c>
+      <c r="I74" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13096,9 +12759,12 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>329</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>324</v>
+      </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -13126,9 +12792,12 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>329</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>0.3191489361702128</v>
+      </c>
+      <c r="H76" t="n">
+        <v>324</v>
+      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -13156,9 +12825,12 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>329</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>1.276595744680851</v>
+      </c>
+      <c r="H77" t="n">
+        <v>324</v>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -13186,9 +12858,12 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>329</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>5.978723404255319</v>
+      </c>
+      <c r="H78" t="n">
+        <v>324</v>
+      </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -13216,9 +12891,12 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>329</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>17.19148936170213</v>
+      </c>
+      <c r="H79" t="n">
+        <v>324</v>
+      </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -13246,9 +12924,12 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>329</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>22.17021276595745</v>
+      </c>
+      <c r="H80" t="n">
+        <v>324</v>
+      </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -13276,9 +12957,12 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>329</v>
-      </c>
-      <c r="H81" t="inlineStr">
+        <v>23.31914893617021</v>
+      </c>
+      <c r="H81" t="n">
+        <v>324</v>
+      </c>
+      <c r="I81" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13310,9 +12994,12 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>329</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>0.125</v>
+      </c>
+      <c r="H82" t="n">
+        <v>318</v>
+      </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -13340,9 +13027,12 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>329</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="H83" t="n">
+        <v>318</v>
+      </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -13370,9 +13060,12 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>329</v>
-      </c>
-      <c r="H84" t="inlineStr"/>
+        <v>0.375</v>
+      </c>
+      <c r="H84" t="n">
+        <v>318</v>
+      </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -13400,9 +13093,12 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>329</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>0.675</v>
+      </c>
+      <c r="H85" t="n">
+        <v>318</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -13430,9 +13126,12 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>329</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>1.075</v>
+      </c>
+      <c r="H86" t="n">
+        <v>318</v>
+      </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -13460,9 +13159,12 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>329</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>4.65</v>
+      </c>
+      <c r="H87" t="n">
+        <v>318</v>
+      </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -13490,9 +13192,12 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>329</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H88" t="n">
+        <v>318</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -13520,9 +13225,12 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>329</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>11.275</v>
+      </c>
+      <c r="H89" t="n">
+        <v>318</v>
+      </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -13550,9 +13258,12 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>329</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>13.725</v>
+      </c>
+      <c r="H90" t="n">
+        <v>318</v>
+      </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13580,9 +13291,12 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>329</v>
-      </c>
-      <c r="H91" t="inlineStr">
+        <v>13.875</v>
+      </c>
+      <c r="H91" t="n">
+        <v>318</v>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13614,9 +13328,12 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>324</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>317</v>
+      </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13644,9 +13361,12 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>324</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="H93" t="n">
+        <v>317</v>
+      </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13674,9 +13394,12 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>324</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>0.575</v>
+      </c>
+      <c r="H94" t="n">
+        <v>317</v>
+      </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13704,9 +13427,12 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>324</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="H95" t="n">
+        <v>317</v>
+      </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13734,9 +13460,12 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>324</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>7.725</v>
+      </c>
+      <c r="H96" t="n">
+        <v>317</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13764,9 +13493,12 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>324</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
+        <v>10.025</v>
+      </c>
+      <c r="H97" t="n">
+        <v>317</v>
+      </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13794,9 +13526,12 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>324</v>
-      </c>
-      <c r="H98" t="inlineStr">
+        <v>10.025</v>
+      </c>
+      <c r="H98" t="n">
+        <v>317</v>
+      </c>
+      <c r="I98" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -13828,9 +13563,12 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>330</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>319</v>
+      </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13858,9 +13596,12 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>330</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>319</v>
+      </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13888,9 +13629,12 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>330</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>319</v>
+      </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13918,9 +13662,12 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>330</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>319</v>
+      </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13948,9 +13695,12 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>330</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>319</v>
+      </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13978,9 +13728,12 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>330</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>319</v>
+      </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14008,9 +13761,12 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>330</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>319</v>
+      </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14038,9 +13794,12 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>330</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>0.3</v>
+      </c>
+      <c r="H106" t="n">
+        <v>319</v>
+      </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -14068,9 +13827,12 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>330</v>
-      </c>
-      <c r="H107" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="H107" t="n">
+        <v>319</v>
+      </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -14098,9 +13860,12 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>330</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>0.9</v>
+      </c>
+      <c r="H108" t="n">
+        <v>319</v>
+      </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14128,9 +13893,12 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>330</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>1.05</v>
+      </c>
+      <c r="H109" t="n">
+        <v>319</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14158,9 +13926,12 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>330</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>1.45</v>
+      </c>
+      <c r="H110" t="n">
+        <v>319</v>
+      </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14188,9 +13959,12 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>330</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="H111" t="n">
+        <v>319</v>
+      </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14218,9 +13992,12 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>330</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="H112" t="n">
+        <v>319</v>
+      </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14248,9 +14025,12 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>330</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
+        <v>4.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>319</v>
+      </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14278,9 +14058,12 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>330</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>6.2</v>
+      </c>
+      <c r="H114" t="n">
+        <v>319</v>
+      </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14308,9 +14091,12 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>330</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
+        <v>6.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>319</v>
+      </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14338,9 +14124,12 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>330</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="H116" t="n">
+        <v>319</v>
+      </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14368,9 +14157,12 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>330</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
+        <v>6.75</v>
+      </c>
+      <c r="H117" t="n">
+        <v>319</v>
+      </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14398,9 +14190,12 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>330</v>
-      </c>
-      <c r="H118" t="inlineStr">
+        <v>6.85</v>
+      </c>
+      <c r="H118" t="n">
+        <v>319</v>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -14432,9 +14227,12 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>329</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="H119" t="n">
+        <v>317</v>
+      </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14462,9 +14260,12 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>329</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>0.02564102564102564</v>
+      </c>
+      <c r="H120" t="n">
+        <v>317</v>
+      </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14492,9 +14293,12 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>329</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="H121" t="n">
+        <v>317</v>
+      </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14522,9 +14326,12 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>329</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="H122" t="n">
+        <v>317</v>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14552,9 +14359,12 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>329</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
+        <v>1.333333333333333</v>
+      </c>
+      <c r="H123" t="n">
+        <v>317</v>
+      </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14582,9 +14392,12 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>329</v>
-      </c>
-      <c r="H124" t="inlineStr"/>
+        <v>1.512820512820513</v>
+      </c>
+      <c r="H124" t="n">
+        <v>317</v>
+      </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14612,9 +14425,12 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>329</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
+        <v>2.102564102564103</v>
+      </c>
+      <c r="H125" t="n">
+        <v>317</v>
+      </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14642,9 +14458,12 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>329</v>
-      </c>
-      <c r="H126" t="inlineStr"/>
+        <v>2.538461538461538</v>
+      </c>
+      <c r="H126" t="n">
+        <v>317</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14672,9 +14491,12 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>329</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>2.974358974358974</v>
+      </c>
+      <c r="H127" t="n">
+        <v>317</v>
+      </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -14702,9 +14524,12 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>329</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>3.256410256410256</v>
+      </c>
+      <c r="H128" t="n">
+        <v>317</v>
+      </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -14732,9 +14557,12 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>329</v>
-      </c>
-      <c r="H129" t="inlineStr"/>
+        <v>3.358974358974359</v>
+      </c>
+      <c r="H129" t="n">
+        <v>317</v>
+      </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -14762,9 +14590,12 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>329</v>
-      </c>
-      <c r="H130" t="inlineStr">
+        <v>3.358974358974359</v>
+      </c>
+      <c r="H130" t="n">
+        <v>317</v>
+      </c>
+      <c r="I130" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -14796,9 +14627,12 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>337</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>318</v>
+      </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -14826,9 +14660,12 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>337</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>318</v>
+      </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14856,9 +14693,12 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>337</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>318</v>
+      </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -14886,9 +14726,12 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>337</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
+        <v>0.06779661016949153</v>
+      </c>
+      <c r="H134" t="n">
+        <v>318</v>
+      </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -14916,9 +14759,12 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>337</v>
-      </c>
-      <c r="H135" t="inlineStr"/>
+        <v>0.1694915254237288</v>
+      </c>
+      <c r="H135" t="n">
+        <v>318</v>
+      </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -14946,9 +14792,12 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>337</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>0.1864406779661017</v>
+      </c>
+      <c r="H136" t="n">
+        <v>318</v>
+      </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14976,9 +14825,12 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>337</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>0.3728813559322034</v>
+      </c>
+      <c r="H137" t="n">
+        <v>318</v>
+      </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -15006,9 +14858,12 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>337</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
+        <v>0.5084745762711864</v>
+      </c>
+      <c r="H138" t="n">
+        <v>318</v>
+      </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -15036,9 +14891,12 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>337</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
+        <v>0.8135593220338984</v>
+      </c>
+      <c r="H139" t="n">
+        <v>318</v>
+      </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -15066,9 +14924,12 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>337</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
+        <v>1.169491525423729</v>
+      </c>
+      <c r="H140" t="n">
+        <v>318</v>
+      </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -15096,9 +14957,12 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>337</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
+        <v>1.491525423728814</v>
+      </c>
+      <c r="H141" t="n">
+        <v>318</v>
+      </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -15126,9 +14990,12 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>337</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
+        <v>1.88135593220339</v>
+      </c>
+      <c r="H142" t="n">
+        <v>318</v>
+      </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -15156,9 +15023,12 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>337</v>
-      </c>
-      <c r="H143" t="inlineStr"/>
+        <v>2.203389830508474</v>
+      </c>
+      <c r="H143" t="n">
+        <v>318</v>
+      </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -15186,9 +15056,12 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>337</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>2.372881355932203</v>
+      </c>
+      <c r="H144" t="n">
+        <v>318</v>
+      </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -15216,9 +15089,12 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>337</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>2.559322033898305</v>
+      </c>
+      <c r="H145" t="n">
+        <v>318</v>
+      </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -15246,9 +15122,12 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>337</v>
-      </c>
-      <c r="H146" t="inlineStr">
+        <v>2.76271186440678</v>
+      </c>
+      <c r="H146" t="n">
+        <v>318</v>
+      </c>
+      <c r="I146" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -15280,9 +15159,12 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>314</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H147" t="n">
+        <v>315</v>
+      </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15310,9 +15192,12 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>314</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
+        <v>0.1025641025641026</v>
+      </c>
+      <c r="H148" t="n">
+        <v>315</v>
+      </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15340,9 +15225,12 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>314</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
+        <v>0.1282051282051282</v>
+      </c>
+      <c r="H149" t="n">
+        <v>315</v>
+      </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15370,9 +15258,12 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>314</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="H150" t="n">
+        <v>315</v>
+      </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15400,9 +15291,12 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>314</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
+        <v>0.9743589743589743</v>
+      </c>
+      <c r="H151" t="n">
+        <v>315</v>
+      </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15430,9 +15324,12 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>314</v>
-      </c>
-      <c r="H152" t="inlineStr"/>
+        <v>1.41025641025641</v>
+      </c>
+      <c r="H152" t="n">
+        <v>315</v>
+      </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15460,9 +15357,12 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>314</v>
-      </c>
-      <c r="H153" t="inlineStr"/>
+        <v>1.897435897435897</v>
+      </c>
+      <c r="H153" t="n">
+        <v>315</v>
+      </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15490,9 +15390,12 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>314</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
+        <v>2.153846153846154</v>
+      </c>
+      <c r="H154" t="n">
+        <v>315</v>
+      </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15520,9 +15423,12 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>314</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
+        <v>2.512820512820513</v>
+      </c>
+      <c r="H155" t="n">
+        <v>315</v>
+      </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15550,9 +15456,12 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>314</v>
-      </c>
-      <c r="H156" t="inlineStr"/>
+        <v>2.794871794871795</v>
+      </c>
+      <c r="H156" t="n">
+        <v>315</v>
+      </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -15580,9 +15489,12 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>314</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
+        <v>2.974358974358974</v>
+      </c>
+      <c r="H157" t="n">
+        <v>315</v>
+      </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -15610,9 +15522,12 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>314</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
+        <v>3.205128205128205</v>
+      </c>
+      <c r="H158" t="n">
+        <v>315</v>
+      </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -15640,9 +15555,12 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>314</v>
-      </c>
-      <c r="H159" t="inlineStr"/>
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H159" t="n">
+        <v>315</v>
+      </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -15670,9 +15588,12 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>314</v>
-      </c>
-      <c r="H160" t="inlineStr"/>
+        <v>3.41025641025641</v>
+      </c>
+      <c r="H160" t="n">
+        <v>315</v>
+      </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -15700,9 +15621,12 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>314</v>
-      </c>
-      <c r="H161" t="inlineStr"/>
+        <v>3.41025641025641</v>
+      </c>
+      <c r="H161" t="n">
+        <v>315</v>
+      </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -15730,9 +15654,12 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>314</v>
-      </c>
-      <c r="H162" t="inlineStr">
+        <v>3.41025641025641</v>
+      </c>
+      <c r="H162" t="n">
+        <v>315</v>
+      </c>
+      <c r="I162" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -15741,7 +15668,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B163" s="2" t="n">
@@ -15755,7 +15682,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -15764,14 +15691,17 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>328</v>
-      </c>
-      <c r="H163" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>314</v>
+      </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B164" s="2" t="n">
@@ -15785,7 +15715,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -15794,14 +15724,17 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>328</v>
-      </c>
-      <c r="H164" t="inlineStr"/>
+        <v>0.01666666666666667</v>
+      </c>
+      <c r="H164" t="n">
+        <v>314</v>
+      </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B165" s="2" t="n">
@@ -15815,7 +15748,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -15824,14 +15757,17 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>328</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
+        <v>0.15</v>
+      </c>
+      <c r="H165" t="n">
+        <v>314</v>
+      </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B166" s="2" t="n">
@@ -15845,7 +15781,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -15854,14 +15790,17 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>328</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
+        <v>0.1833333333333333</v>
+      </c>
+      <c r="H166" t="n">
+        <v>314</v>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B167" s="2" t="n">
@@ -15875,7 +15814,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -15884,14 +15823,17 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>328</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="H167" t="n">
+        <v>314</v>
+      </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B168" s="2" t="n">
@@ -15905,7 +15847,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -15914,14 +15856,17 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>328</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
+        <v>1.066666666666667</v>
+      </c>
+      <c r="H168" t="n">
+        <v>314</v>
+      </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B169" s="2" t="n">
@@ -15935,7 +15880,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -15944,14 +15889,17 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>328</v>
-      </c>
-      <c r="H169" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="H169" t="n">
+        <v>314</v>
+      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B170" s="2" t="n">
@@ -15965,7 +15913,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -15974,14 +15922,17 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>328</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
+        <v>7.933333333333334</v>
+      </c>
+      <c r="H170" t="n">
+        <v>314</v>
+      </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B171" s="2" t="n">
@@ -15995,7 +15946,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -16004,14 +15955,17 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>328</v>
-      </c>
-      <c r="H171" t="inlineStr"/>
+        <v>11.38333333333333</v>
+      </c>
+      <c r="H171" t="n">
+        <v>314</v>
+      </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B172" s="2" t="n">
@@ -16025,7 +15979,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -16034,14 +15988,17 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>328</v>
-      </c>
-      <c r="H172" t="inlineStr"/>
+        <v>11.85</v>
+      </c>
+      <c r="H172" t="n">
+        <v>314</v>
+      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B173" s="2" t="n">
@@ -16055,7 +16012,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -16064,14 +16021,17 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>328</v>
-      </c>
-      <c r="H173" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="H173" t="n">
+        <v>314</v>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B174" s="2" t="n">
@@ -16085,7 +16045,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -16094,14 +16054,17 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>328</v>
-      </c>
-      <c r="H174" t="inlineStr"/>
+        <v>12.05</v>
+      </c>
+      <c r="H174" t="n">
+        <v>314</v>
+      </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HW-Budbreak2020Control</t>
+          <t>HW-BudbreakTP2020Control</t>
         </is>
       </c>
       <c r="B175" s="2" t="n">
@@ -16115,7 +16078,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -16124,9 +16087,12 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>328</v>
-      </c>
-      <c r="H175" t="inlineStr">
+        <v>12.05</v>
+      </c>
+      <c r="H175" t="n">
+        <v>314</v>
+      </c>
+      <c r="I175" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -16135,7 +16101,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B176" s="2" t="n">
@@ -16149,7 +16115,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -16158,14 +16124,17 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>327</v>
-      </c>
-      <c r="H176" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>320</v>
+      </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B177" s="2" t="n">
@@ -16179,7 +16148,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -16188,14 +16157,17 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>327</v>
-      </c>
-      <c r="H177" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>320</v>
+      </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B178" s="2" t="n">
@@ -16209,7 +16181,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -16218,14 +16190,17 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>327</v>
-      </c>
-      <c r="H178" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>320</v>
+      </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B179" s="2" t="n">
@@ -16239,7 +16214,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -16248,14 +16223,17 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>327</v>
-      </c>
-      <c r="H179" t="inlineStr"/>
+        <v>0.2</v>
+      </c>
+      <c r="H179" t="n">
+        <v>320</v>
+      </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B180" s="2" t="n">
@@ -16269,7 +16247,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -16278,14 +16256,17 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>327</v>
-      </c>
-      <c r="H180" t="inlineStr"/>
+        <v>1.17</v>
+      </c>
+      <c r="H180" t="n">
+        <v>320</v>
+      </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B181" s="2" t="n">
@@ -16299,7 +16280,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -16308,14 +16289,17 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>327</v>
-      </c>
-      <c r="H181" t="inlineStr"/>
+        <v>8.83</v>
+      </c>
+      <c r="H181" t="n">
+        <v>320</v>
+      </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B182" s="2" t="n">
@@ -16329,7 +16313,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -16338,14 +16322,17 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>327</v>
-      </c>
-      <c r="H182" t="inlineStr"/>
+        <v>15.42</v>
+      </c>
+      <c r="H182" t="n">
+        <v>320</v>
+      </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B183" s="2" t="n">
@@ -16359,7 +16346,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -16368,14 +16355,17 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>327</v>
-      </c>
-      <c r="H183" t="inlineStr"/>
+        <v>20.11</v>
+      </c>
+      <c r="H183" t="n">
+        <v>320</v>
+      </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>HWBBRawKK2021Control</t>
+          <t>HWBBRawTP2021Control</t>
         </is>
       </c>
       <c r="B184" s="2" t="n">
@@ -16389,7 +16379,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -16398,9 +16388,12 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>327</v>
-      </c>
-      <c r="H184" t="inlineStr">
+        <v>20.32</v>
+      </c>
+      <c r="H184" t="n">
+        <v>320</v>
+      </c>
+      <c r="I184" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>
@@ -16409,21 +16402,21 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B185" s="2" t="n">
-        <v>44879</v>
+        <v>44147</v>
       </c>
       <c r="C185" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D185" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -16432,28 +16425,31 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>332</v>
-      </c>
-      <c r="H185" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>322</v>
+      </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B186" s="2" t="n">
-        <v>44881</v>
+        <v>44151</v>
       </c>
       <c r="C186" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D186" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -16462,58 +16458,64 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>332</v>
-      </c>
-      <c r="H186" t="inlineStr"/>
+        <v>0.1180555555555556</v>
+      </c>
+      <c r="H186" t="n">
+        <v>322</v>
+      </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B187" s="2" t="n">
-        <v>44883</v>
+        <v>44154</v>
       </c>
       <c r="C187" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D187" t="n">
+        <v>324</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Te Puke</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="H187" t="n">
         <v>322</v>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G187" t="n">
-        <v>332</v>
-      </c>
-      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B188" s="2" t="n">
-        <v>44886</v>
+        <v>44159</v>
       </c>
       <c r="C188" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D188" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -16522,28 +16524,31 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>332</v>
-      </c>
-      <c r="H188" t="inlineStr"/>
+        <v>3.604166666666667</v>
+      </c>
+      <c r="H188" t="n">
+        <v>322</v>
+      </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B189" s="2" t="n">
-        <v>44888</v>
+        <v>44162</v>
       </c>
       <c r="C189" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D189" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -16552,28 +16557,31 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>332</v>
-      </c>
-      <c r="H189" t="inlineStr"/>
+        <v>5.847222222222222</v>
+      </c>
+      <c r="H189" t="n">
+        <v>322</v>
+      </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B190" s="2" t="n">
-        <v>44890</v>
+        <v>44166</v>
       </c>
       <c r="C190" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D190" t="n">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -16582,28 +16590,31 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>332</v>
-      </c>
-      <c r="H190" t="inlineStr"/>
+        <v>6.958333333333333</v>
+      </c>
+      <c r="H190" t="n">
+        <v>322</v>
+      </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>HWBBRawKK2022Control</t>
+          <t>HW-Budbreak-TP2020Control</t>
         </is>
       </c>
       <c r="B191" s="2" t="n">
-        <v>44893</v>
+        <v>44169</v>
       </c>
       <c r="C191" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D191" t="n">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Kerikeri</t>
+          <t>Te Puke</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -16612,403 +16623,12 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>332</v>
-      </c>
-      <c r="H191" t="inlineStr"/>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B192" s="2" t="n">
-        <v>44896</v>
-      </c>
-      <c r="C192" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D192" t="n">
-        <v>335</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G192" t="n">
-        <v>332</v>
-      </c>
-      <c r="H192" t="inlineStr"/>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B193" s="2" t="n">
-        <v>44900</v>
-      </c>
-      <c r="C193" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D193" t="n">
-        <v>339</v>
-      </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G193" t="n">
-        <v>332</v>
-      </c>
-      <c r="H193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B194" s="2" t="n">
-        <v>44902</v>
-      </c>
-      <c r="C194" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D194" t="n">
-        <v>341</v>
-      </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G194" t="n">
-        <v>332</v>
-      </c>
-      <c r="H194" t="inlineStr"/>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B195" s="2" t="n">
-        <v>44904</v>
-      </c>
-      <c r="C195" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D195" t="n">
-        <v>343</v>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G195" t="n">
-        <v>332</v>
-      </c>
-      <c r="H195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="n">
-        <v>44907</v>
-      </c>
-      <c r="C196" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D196" t="n">
-        <v>346</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G196" t="n">
-        <v>332</v>
-      </c>
-      <c r="H196" t="inlineStr"/>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>HWBBRawKK2022Control</t>
-        </is>
-      </c>
-      <c r="B197" s="2" t="n">
-        <v>44909</v>
-      </c>
-      <c r="C197" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D197" t="n">
-        <v>348</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G197" t="n">
-        <v>332</v>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>StartFlowering</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B198" s="2" t="n">
-        <v>44147</v>
-      </c>
-      <c r="C198" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D198" t="n">
-        <v>317</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G198" t="n">
-        <v>321</v>
-      </c>
-      <c r="H198" t="inlineStr"/>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B199" s="2" t="n">
-        <v>44151</v>
-      </c>
-      <c r="C199" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D199" t="n">
-        <v>321</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G199" t="n">
-        <v>321</v>
-      </c>
-      <c r="H199" t="inlineStr"/>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="n">
-        <v>44154</v>
-      </c>
-      <c r="C200" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D200" t="n">
-        <v>324</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G200" t="n">
-        <v>321</v>
-      </c>
-      <c r="H200" t="inlineStr"/>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="n">
-        <v>44159</v>
-      </c>
-      <c r="C201" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D201" t="n">
-        <v>329</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G201" t="n">
-        <v>321</v>
-      </c>
-      <c r="H201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B202" s="2" t="n">
-        <v>44162</v>
-      </c>
-      <c r="C202" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D202" t="n">
-        <v>332</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G202" t="n">
-        <v>321</v>
-      </c>
-      <c r="H202" t="inlineStr"/>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B203" s="2" t="n">
-        <v>44166</v>
-      </c>
-      <c r="C203" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D203" t="n">
-        <v>336</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G203" t="n">
-        <v>321</v>
-      </c>
-      <c r="H203" t="inlineStr"/>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>HW-Budbreak-KK2020Control</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="n">
-        <v>44169</v>
-      </c>
-      <c r="C204" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D204" t="n">
-        <v>339</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>Kerikeri</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="G204" t="n">
-        <v>321</v>
-      </c>
-      <c r="H204" t="inlineStr">
+        <v>6.645833333333333</v>
+      </c>
+      <c r="H191" t="n">
+        <v>322</v>
+      </c>
+      <c r="I191" t="inlineStr">
         <is>
           <t>StartFlowering</t>
         </is>

--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -1,30 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1FF85C-97E5-492A-B967-4E2E633E5492}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB9C4B2-238F-4981-AB2F-079FB455457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BB" sheetId="1" r:id="rId1"/>
-    <sheet name="Flwr" sheetId="2" r:id="rId2"/>
+    <sheet name="FlwrDOY" sheetId="2" r:id="rId2"/>
+    <sheet name="Flwrs" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">BB!$E$1:$E$252</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1368" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="47">
   <si>
     <t>SimulationName</t>
   </si>
@@ -157,6 +171,15 @@
   <si>
     <t>KiwiFruit.Phenology.MaxBBP</t>
   </si>
+  <si>
+    <t>EndFlowering</t>
+  </si>
+  <si>
+    <t>KiwiFruit.Phenology.MaxFlowers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
 </sst>
 </file>
 
@@ -165,7 +188,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,6 +200,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,12 +245,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -522,17 +554,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J252"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="56.33203125" customWidth="1"/>
-    <col min="2" max="2" width="39.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="29.109375" customWidth="1"/>
+    <col min="1" max="1" width="56.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" customWidth="1"/>
+    <col min="7" max="7" width="40.85546875" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -564,7 +595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -590,7 +621,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -616,7 +647,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -642,7 +673,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -668,7 +699,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -694,7 +725,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -720,7 +751,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -746,7 +777,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -778,7 +809,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -804,7 +835,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -830,7 +861,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -856,7 +887,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -882,7 +913,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -908,7 +939,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -934,7 +965,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -960,7 +991,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -992,7 +1023,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1049,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1044,7 +1075,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1070,7 +1101,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1096,7 +1127,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1122,7 +1153,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1148,7 +1179,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1174,7 +1205,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1206,7 +1237,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1232,7 +1263,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1258,7 +1289,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1284,7 +1315,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1310,7 +1341,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1336,7 +1367,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1362,7 +1393,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1388,7 +1419,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1414,7 +1445,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1440,7 +1471,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1466,7 +1497,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1492,7 +1523,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1518,7 +1549,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1544,7 +1575,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1570,7 +1601,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -1602,7 +1633,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1628,7 +1659,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -1654,7 +1685,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -1680,7 +1711,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -1706,7 +1737,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1732,7 +1763,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -1790,7 +1821,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -1816,7 +1847,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -1842,7 +1873,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -1868,7 +1899,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -1894,7 +1925,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -1926,7 +1957,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -1952,7 +1983,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -1978,7 +2009,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -2004,7 +2035,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -2030,7 +2061,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -2056,7 +2087,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -2082,7 +2113,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -2108,7 +2139,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -2140,7 +2171,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -2166,7 +2197,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -2192,7 +2223,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -2218,7 +2249,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -2244,7 +2275,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -2270,7 +2301,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -2296,7 +2327,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -2322,7 +2353,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>23</v>
       </c>
@@ -2354,7 +2385,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -2380,7 +2411,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -2406,7 +2437,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -2432,7 +2463,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -2458,7 +2489,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>24</v>
       </c>
@@ -2484,7 +2515,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>24</v>
       </c>
@@ -2510,7 +2541,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>24</v>
       </c>
@@ -2536,7 +2567,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -2562,7 +2593,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>24</v>
       </c>
@@ -2588,7 +2619,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -2614,7 +2645,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>24</v>
       </c>
@@ -2634,7 +2665,7 @@
         <v>11</v>
       </c>
       <c r="G79">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H79">
         <v>0.45</v>
@@ -2646,7 +2677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -2672,7 +2703,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -2698,7 +2729,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -2724,7 +2755,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -2750,7 +2781,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -2776,7 +2807,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -2802,7 +2833,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -2828,7 +2859,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -2854,7 +2885,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -2880,7 +2911,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -2906,7 +2937,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -2932,7 +2963,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -2964,7 +2995,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -2990,7 +3021,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -3016,7 +3047,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -3042,7 +3073,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -3068,7 +3099,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -3094,7 +3125,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -3120,7 +3151,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -3146,7 +3177,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -3172,7 +3203,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -3198,7 +3229,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -3224,7 +3255,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -3250,7 +3281,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3282,7 +3313,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -3308,7 +3339,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>27</v>
       </c>
@@ -3334,7 +3365,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>27</v>
       </c>
@@ -3360,7 +3391,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>27</v>
       </c>
@@ -3386,7 +3417,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>27</v>
       </c>
@@ -3412,7 +3443,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>27</v>
       </c>
@@ -3438,7 +3469,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>27</v>
       </c>
@@ -3470,7 +3501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>28</v>
       </c>
@@ -3496,7 +3527,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>28</v>
       </c>
@@ -3522,7 +3553,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>28</v>
       </c>
@@ -3548,7 +3579,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>28</v>
       </c>
@@ -3574,7 +3605,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>28</v>
       </c>
@@ -3600,7 +3631,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>28</v>
       </c>
@@ -3626,7 +3657,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>28</v>
       </c>
@@ -3652,7 +3683,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>28</v>
       </c>
@@ -3678,7 +3709,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>28</v>
       </c>
@@ -3710,7 +3741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -3736,7 +3767,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -3762,7 +3793,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -3788,7 +3819,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -3814,7 +3845,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -3840,7 +3871,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>30</v>
       </c>
@@ -3866,7 +3897,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>30</v>
       </c>
@@ -3892,7 +3923,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>30</v>
       </c>
@@ -3918,7 +3949,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -3944,7 +3975,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -3970,7 +4001,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -3996,7 +4027,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>30</v>
       </c>
@@ -4028,7 +4059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>31</v>
       </c>
@@ -4054,7 +4085,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>31</v>
       </c>
@@ -4080,7 +4111,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>31</v>
       </c>
@@ -4106,7 +4137,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>31</v>
       </c>
@@ -4132,7 +4163,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>31</v>
       </c>
@@ -4158,7 +4189,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -4184,7 +4215,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>31</v>
       </c>
@@ -4210,7 +4241,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>31</v>
       </c>
@@ -4242,7 +4273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>32</v>
       </c>
@@ -4268,7 +4299,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>32</v>
       </c>
@@ -4294,7 +4325,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>32</v>
       </c>
@@ -4320,7 +4351,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>32</v>
       </c>
@@ -4346,7 +4377,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>32</v>
       </c>
@@ -4372,7 +4403,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>32</v>
       </c>
@@ -4398,7 +4429,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>32</v>
       </c>
@@ -4424,7 +4455,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>32</v>
       </c>
@@ -4450,7 +4481,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>32</v>
       </c>
@@ -4476,7 +4507,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>32</v>
       </c>
@@ -4502,7 +4533,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>32</v>
       </c>
@@ -4528,7 +4559,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>32</v>
       </c>
@@ -4554,7 +4585,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>32</v>
       </c>
@@ -4580,7 +4611,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>32</v>
       </c>
@@ -4606,7 +4637,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>32</v>
       </c>
@@ -4632,7 +4663,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>32</v>
       </c>
@@ -4664,7 +4695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>34</v>
       </c>
@@ -4690,7 +4721,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>34</v>
       </c>
@@ -4716,7 +4747,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>34</v>
       </c>
@@ -4742,7 +4773,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>34</v>
       </c>
@@ -4768,7 +4799,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>34</v>
       </c>
@@ -4794,7 +4825,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>34</v>
       </c>
@@ -4820,7 +4851,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -4846,7 +4877,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>34</v>
       </c>
@@ -4872,7 +4903,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -4898,7 +4929,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>34</v>
       </c>
@@ -4924,7 +4955,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>34</v>
       </c>
@@ -4950,7 +4981,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>34</v>
       </c>
@@ -4976,7 +5007,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>34</v>
       </c>
@@ -5002,7 +5033,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>34</v>
       </c>
@@ -5028,7 +5059,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>34</v>
       </c>
@@ -5054,7 +5085,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>34</v>
       </c>
@@ -5080,7 +5111,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>34</v>
       </c>
@@ -5106,7 +5137,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>34</v>
       </c>
@@ -5132,7 +5163,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>34</v>
       </c>
@@ -5158,7 +5189,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>34</v>
       </c>
@@ -5190,7 +5221,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>36</v>
       </c>
@@ -5216,7 +5247,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>36</v>
       </c>
@@ -5242,7 +5273,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>36</v>
       </c>
@@ -5268,7 +5299,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>36</v>
       </c>
@@ -5294,7 +5325,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>36</v>
       </c>
@@ -5320,7 +5351,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>36</v>
       </c>
@@ -5346,7 +5377,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>36</v>
       </c>
@@ -5372,7 +5403,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>36</v>
       </c>
@@ -5398,7 +5429,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>36</v>
       </c>
@@ -5424,7 +5455,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -5450,7 +5481,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>36</v>
       </c>
@@ -5476,7 +5507,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>36</v>
       </c>
@@ -5502,7 +5533,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>36</v>
       </c>
@@ -5528,7 +5559,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>36</v>
       </c>
@@ -5554,7 +5585,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>36</v>
       </c>
@@ -5580,7 +5611,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>36</v>
       </c>
@@ -5612,7 +5643,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>37</v>
       </c>
@@ -5638,7 +5669,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>37</v>
       </c>
@@ -5664,7 +5695,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>37</v>
       </c>
@@ -5690,7 +5721,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>37</v>
       </c>
@@ -5716,7 +5747,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>37</v>
       </c>
@@ -5742,7 +5773,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>37</v>
       </c>
@@ -5768,7 +5799,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>37</v>
       </c>
@@ -5794,7 +5825,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>37</v>
       </c>
@@ -5820,7 +5851,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>37</v>
       </c>
@@ -5846,7 +5877,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>37</v>
       </c>
@@ -5872,7 +5903,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>37</v>
       </c>
@@ -5898,7 +5929,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>37</v>
       </c>
@@ -5930,7 +5961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>38</v>
       </c>
@@ -5956,7 +5987,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>38</v>
       </c>
@@ -5982,7 +6013,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>38</v>
       </c>
@@ -6008,7 +6039,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>38</v>
       </c>
@@ -6034,7 +6065,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>38</v>
       </c>
@@ -6060,7 +6091,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>38</v>
       </c>
@@ -6086,7 +6117,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>38</v>
       </c>
@@ -6112,7 +6143,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>38</v>
       </c>
@@ -6138,7 +6169,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>38</v>
       </c>
@@ -6164,7 +6195,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>38</v>
       </c>
@@ -6190,7 +6221,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>38</v>
       </c>
@@ -6216,7 +6247,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>38</v>
       </c>
@@ -6242,7 +6273,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>38</v>
       </c>
@@ -6268,7 +6299,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>38</v>
       </c>
@@ -6294,7 +6325,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>38</v>
       </c>
@@ -6320,7 +6351,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>38</v>
       </c>
@@ -6346,7 +6377,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>38</v>
       </c>
@@ -6372,7 +6403,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>38</v>
       </c>
@@ -6398,7 +6429,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>38</v>
       </c>
@@ -6424,7 +6455,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>38</v>
       </c>
@@ -6456,7 +6487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>39</v>
       </c>
@@ -6482,7 +6513,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>39</v>
       </c>
@@ -6508,7 +6539,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>39</v>
       </c>
@@ -6534,7 +6565,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>39</v>
       </c>
@@ -6560,7 +6591,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>39</v>
       </c>
@@ -6586,7 +6617,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>39</v>
       </c>
@@ -6612,7 +6643,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>39</v>
       </c>
@@ -6638,7 +6669,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>39</v>
       </c>
@@ -6664,7 +6695,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>39</v>
       </c>
@@ -6690,7 +6721,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>39</v>
       </c>
@@ -6716,7 +6747,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>39</v>
       </c>
@@ -6742,7 +6773,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -6768,7 +6799,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>39</v>
       </c>
@@ -6794,7 +6825,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>39</v>
       </c>
@@ -6820,7 +6851,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -6852,7 +6883,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -6878,7 +6909,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -6904,7 +6935,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -6930,7 +6961,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -6956,7 +6987,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -6982,7 +7013,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -7008,7 +7039,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -7034,7 +7065,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -7060,7 +7091,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -7086,7 +7117,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -7112,7 +7143,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -7138,7 +7169,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -7164,7 +7195,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -7190,7 +7221,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -7223,13 +7254,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="E1:E252" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Kerikeri"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="E1:E252" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7237,9 +7262,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I185"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="37.5703125" customWidth="1"/>
+    <col min="8" max="8" width="43.7109375" customWidth="1"/>
+    <col min="9" max="9" width="39" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7268,7 +7300,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7293,8 +7325,11 @@
       <c r="H2">
         <v>328</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7320,7 +7355,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -7346,7 +7381,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -7372,7 +7407,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7398,7 +7433,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7423,11 +7458,8 @@
       <c r="H7">
         <v>328</v>
       </c>
-      <c r="I7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -7452,8 +7484,11 @@
       <c r="H8">
         <v>325</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -7479,7 +7514,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7505,7 +7540,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7531,7 +7566,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -7557,7 +7592,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7583,7 +7618,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -7609,7 +7644,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -7634,11 +7669,8 @@
       <c r="H15">
         <v>325</v>
       </c>
-      <c r="I15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7663,8 +7695,11 @@
       <c r="H16">
         <v>324</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -7690,7 +7725,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -7716,7 +7751,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -7742,7 +7777,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -7768,7 +7803,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -7794,7 +7829,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -7820,7 +7855,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -7845,11 +7880,8 @@
       <c r="H23">
         <v>324</v>
       </c>
-      <c r="I23" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -7874,8 +7906,11 @@
       <c r="H24">
         <v>326</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I24" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -7901,7 +7936,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -7927,7 +7962,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -7953,7 +7988,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -7979,7 +8014,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -8005,7 +8040,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -8031,7 +8066,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -8056,11 +8091,8 @@
       <c r="H31">
         <v>326</v>
       </c>
-      <c r="I31" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -8085,8 +8117,11 @@
       <c r="H32">
         <v>325</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I32" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -8112,7 +8147,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -8138,7 +8173,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -8158,16 +8193,13 @@
         <v>11</v>
       </c>
       <c r="G35">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H35">
         <v>325</v>
       </c>
-      <c r="I35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -8192,8 +8224,11 @@
       <c r="H36">
         <v>327</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -8219,7 +8254,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -8245,7 +8280,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -8271,7 +8306,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -8296,11 +8331,8 @@
       <c r="H40">
         <v>327</v>
       </c>
-      <c r="I40" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -8325,8 +8357,11 @@
       <c r="H41">
         <v>320</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I41" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -8352,7 +8387,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -8372,13 +8407,13 @@
         <v>11</v>
       </c>
       <c r="G43">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H43">
         <v>320</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -8398,16 +8433,13 @@
         <v>11</v>
       </c>
       <c r="G44">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H44">
         <v>320</v>
       </c>
-      <c r="I44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -8432,8 +8464,11 @@
       <c r="H45">
         <v>320</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I45" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -8459,7 +8494,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -8479,13 +8514,13 @@
         <v>11</v>
       </c>
       <c r="G47">
-        <v>21.5</v>
+        <v>15</v>
       </c>
       <c r="H47">
         <v>320</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -8505,16 +8540,13 @@
         <v>11</v>
       </c>
       <c r="G48">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="H48">
         <v>320</v>
       </c>
-      <c r="I48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -8539,8 +8571,11 @@
       <c r="H49">
         <v>320</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I49" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -8566,7 +8601,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -8586,13 +8621,13 @@
         <v>11</v>
       </c>
       <c r="G51">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H51">
         <v>320</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -8612,16 +8647,13 @@
         <v>11</v>
       </c>
       <c r="G52">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H52">
         <v>320</v>
       </c>
-      <c r="I52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -8646,8 +8678,11 @@
       <c r="H53">
         <v>327</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -8673,7 +8708,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -8699,7 +8734,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -8719,13 +8754,13 @@
         <v>11</v>
       </c>
       <c r="G56">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H56">
         <v>327</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -8745,13 +8780,13 @@
         <v>11</v>
       </c>
       <c r="G57">
-        <v>14.5</v>
+        <v>9</v>
       </c>
       <c r="H57">
         <v>327</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -8771,16 +8806,13 @@
         <v>11</v>
       </c>
       <c r="G58">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H58">
         <v>327</v>
       </c>
-      <c r="I58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -8805,8 +8837,11 @@
       <c r="H59">
         <v>329</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I59" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -8832,7 +8867,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -8858,7 +8893,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -8883,11 +8918,8 @@
       <c r="H62">
         <v>329</v>
       </c>
-      <c r="I62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -8912,8 +8944,11 @@
       <c r="H63">
         <v>331</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I63" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>27</v>
       </c>
@@ -8939,7 +8974,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>27</v>
       </c>
@@ -8965,7 +9000,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -8991,7 +9026,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>27</v>
       </c>
@@ -9017,7 +9052,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>27</v>
       </c>
@@ -9037,16 +9072,13 @@
         <v>11</v>
       </c>
       <c r="G68">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H68">
         <v>331</v>
       </c>
-      <c r="I68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -9071,8 +9103,11 @@
       <c r="H69">
         <v>326</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I69" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -9098,7 +9133,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -9124,7 +9159,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -9150,7 +9185,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -9176,7 +9211,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -9202,7 +9237,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -9227,11 +9262,8 @@
       <c r="H75">
         <v>326</v>
       </c>
-      <c r="I75" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>30</v>
       </c>
@@ -9256,8 +9288,11 @@
       <c r="H76">
         <v>322</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I76" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>30</v>
       </c>
@@ -9283,7 +9318,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>30</v>
       </c>
@@ -9309,7 +9344,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -9335,7 +9370,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -9361,7 +9396,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -9387,7 +9422,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -9413,7 +9448,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -9439,7 +9474,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -9465,7 +9500,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -9490,11 +9525,8 @@
       <c r="H85">
         <v>322</v>
       </c>
-      <c r="I85" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>31</v>
       </c>
@@ -9519,8 +9551,11 @@
       <c r="H86">
         <v>320</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -9546,7 +9581,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>31</v>
       </c>
@@ -9572,7 +9607,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -9598,7 +9633,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -9624,7 +9659,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -9650,7 +9685,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -9675,11 +9710,8 @@
       <c r="H92">
         <v>320</v>
       </c>
-      <c r="I92" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -9704,8 +9736,11 @@
       <c r="H93">
         <v>321</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I93" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -9731,7 +9766,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -9757,7 +9792,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -9783,7 +9818,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>32</v>
       </c>
@@ -9809,7 +9844,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>32</v>
       </c>
@@ -9835,7 +9870,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -9861,7 +9896,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>32</v>
       </c>
@@ -9887,7 +9922,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -9913,7 +9948,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -9939,7 +9974,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -9965,7 +10000,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -9991,7 +10026,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -10017,7 +10052,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>32</v>
       </c>
@@ -10043,7 +10078,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>32</v>
       </c>
@@ -10069,7 +10104,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>32</v>
       </c>
@@ -10095,7 +10130,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -10121,7 +10156,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -10147,7 +10182,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -10173,7 +10208,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -10198,11 +10233,8 @@
       <c r="H112">
         <v>321</v>
       </c>
-      <c r="I112" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -10227,8 +10259,11 @@
       <c r="H113">
         <v>315</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I113" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>34</v>
       </c>
@@ -10254,7 +10289,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>34</v>
       </c>
@@ -10280,7 +10315,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -10306,7 +10341,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>34</v>
       </c>
@@ -10332,7 +10367,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>34</v>
       </c>
@@ -10358,7 +10393,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -10384,7 +10419,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -10410,7 +10445,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>34</v>
       </c>
@@ -10436,7 +10471,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -10462,7 +10497,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -10488,7 +10523,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>34</v>
       </c>
@@ -10508,16 +10543,13 @@
         <v>35</v>
       </c>
       <c r="G124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H124">
         <v>315</v>
       </c>
-      <c r="I124" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -10542,8 +10574,11 @@
       <c r="H125">
         <v>317</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I125" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>36</v>
       </c>
@@ -10569,7 +10604,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>36</v>
       </c>
@@ -10595,7 +10630,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>36</v>
       </c>
@@ -10621,7 +10656,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -10647,7 +10682,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>36</v>
       </c>
@@ -10673,7 +10708,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>36</v>
       </c>
@@ -10699,7 +10734,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>36</v>
       </c>
@@ -10725,7 +10760,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>36</v>
       </c>
@@ -10751,7 +10786,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>36</v>
       </c>
@@ -10777,7 +10812,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -10803,7 +10838,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>36</v>
       </c>
@@ -10829,7 +10864,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>36</v>
       </c>
@@ -10855,7 +10890,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>36</v>
       </c>
@@ -10881,7 +10916,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>36</v>
       </c>
@@ -10907,7 +10942,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>36</v>
       </c>
@@ -10932,11 +10967,8 @@
       <c r="H140">
         <v>317</v>
       </c>
-      <c r="I140" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -10961,8 +10993,11 @@
       <c r="H141">
         <v>314</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I141" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -10988,7 +11023,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -11014,7 +11049,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -11040,7 +11075,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>37</v>
       </c>
@@ -11066,7 +11101,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -11092,7 +11127,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>37</v>
       </c>
@@ -11118,7 +11153,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>37</v>
       </c>
@@ -11144,7 +11179,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -11170,7 +11205,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -11196,7 +11231,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -11222,7 +11257,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -11248,7 +11283,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -11274,7 +11309,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -11300,7 +11335,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -11326,7 +11361,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>37</v>
       </c>
@@ -11351,11 +11386,8 @@
       <c r="H156">
         <v>314</v>
       </c>
-      <c r="I156" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>38</v>
       </c>
@@ -11380,8 +11412,11 @@
       <c r="H157">
         <v>322</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I157" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>38</v>
       </c>
@@ -11407,7 +11442,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>38</v>
       </c>
@@ -11433,7 +11468,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>38</v>
       </c>
@@ -11459,7 +11494,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>38</v>
       </c>
@@ -11485,7 +11520,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>38</v>
       </c>
@@ -11511,7 +11546,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>38</v>
       </c>
@@ -11537,7 +11572,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>38</v>
       </c>
@@ -11563,7 +11598,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>38</v>
       </c>
@@ -11589,7 +11624,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>38</v>
       </c>
@@ -11615,7 +11650,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>38</v>
       </c>
@@ -11641,7 +11676,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -11667,7 +11702,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>38</v>
       </c>
@@ -11692,11 +11727,8 @@
       <c r="H169">
         <v>322</v>
       </c>
-      <c r="I169" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -11721,8 +11753,11 @@
       <c r="H170">
         <v>323</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I170" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -11748,7 +11783,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -11774,7 +11809,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -11800,7 +11835,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -11826,7 +11861,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -11852,7 +11887,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -11878,7 +11913,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -11904,7 +11939,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -11929,11 +11964,8 @@
       <c r="H178">
         <v>323</v>
       </c>
-      <c r="I178" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -11958,8 +11990,11 @@
       <c r="H179">
         <v>317</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I179" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -11985,7 +12020,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -12011,7 +12046,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -12037,7 +12072,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -12063,7 +12098,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -12089,7 +12124,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -12109,13 +12144,5033 @@
         <v>19</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H185">
         <v>317</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5082DE-7F0F-42DB-B242-7E2A52480CF2}">
+  <dimension ref="A1:J185"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="7" max="7" width="37.5703125" customWidth="1"/>
+    <col min="8" max="8" width="43.7109375" customWidth="1"/>
+    <col min="9" max="9" width="39" customWidth="1"/>
+    <col min="10" max="10" width="33.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2">
+        <v>42692</v>
+      </c>
+      <c r="C2">
+        <v>2016</v>
+      </c>
+      <c r="D2">
+        <v>323</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>328</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2">
+        <v>42695</v>
+      </c>
+      <c r="C3">
+        <v>2016</v>
+      </c>
+      <c r="D3">
+        <v>326</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>42699</v>
+      </c>
+      <c r="C4">
+        <v>2016</v>
+      </c>
+      <c r="D4">
+        <v>330</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2">
+        <v>42704</v>
+      </c>
+      <c r="C5">
+        <v>2016</v>
+      </c>
+      <c r="D5">
+        <v>335</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>7</v>
+      </c>
+      <c r="H5">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="2">
+        <v>42710</v>
+      </c>
+      <c r="C6">
+        <v>2016</v>
+      </c>
+      <c r="D6">
+        <v>341</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>16</v>
+      </c>
+      <c r="H6">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>42713</v>
+      </c>
+      <c r="C7">
+        <v>2016</v>
+      </c>
+      <c r="D7">
+        <v>344</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>16</v>
+      </c>
+      <c r="H7">
+        <v>328</v>
+      </c>
+      <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2">
+        <v>42318</v>
+      </c>
+      <c r="C8">
+        <v>2015</v>
+      </c>
+      <c r="D8">
+        <v>314</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>325</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="2">
+        <v>42321</v>
+      </c>
+      <c r="C9">
+        <v>2015</v>
+      </c>
+      <c r="D9">
+        <v>317</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="2">
+        <v>42325</v>
+      </c>
+      <c r="C10">
+        <v>2015</v>
+      </c>
+      <c r="D10">
+        <v>321</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="2">
+        <v>42327</v>
+      </c>
+      <c r="C11">
+        <v>2015</v>
+      </c>
+      <c r="D11">
+        <v>323</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>42331</v>
+      </c>
+      <c r="C12">
+        <v>2015</v>
+      </c>
+      <c r="D12">
+        <v>327</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12">
+        <v>5.5</v>
+      </c>
+      <c r="H12">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="2">
+        <v>42334</v>
+      </c>
+      <c r="C13">
+        <v>2015</v>
+      </c>
+      <c r="D13">
+        <v>330</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13">
+        <v>20</v>
+      </c>
+      <c r="H13">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>42339</v>
+      </c>
+      <c r="C14">
+        <v>2015</v>
+      </c>
+      <c r="D14">
+        <v>335</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14">
+        <v>37</v>
+      </c>
+      <c r="H14">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2">
+        <v>42342</v>
+      </c>
+      <c r="C15">
+        <v>2015</v>
+      </c>
+      <c r="D15">
+        <v>338</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15">
+        <v>37</v>
+      </c>
+      <c r="H15">
+        <v>325</v>
+      </c>
+      <c r="I15" t="s">
+        <v>44</v>
+      </c>
+      <c r="J15">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>42318</v>
+      </c>
+      <c r="C16">
+        <v>2015</v>
+      </c>
+      <c r="D16">
+        <v>314</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>324</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
+        <v>42321</v>
+      </c>
+      <c r="C17">
+        <v>2015</v>
+      </c>
+      <c r="D17">
+        <v>317</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" s="2">
+        <v>42325</v>
+      </c>
+      <c r="C18">
+        <v>2015</v>
+      </c>
+      <c r="D18">
+        <v>321</v>
+      </c>
+      <c r="E18" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2">
+        <v>42327</v>
+      </c>
+      <c r="C19">
+        <v>2015</v>
+      </c>
+      <c r="D19">
+        <v>323</v>
+      </c>
+      <c r="E19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2">
+        <v>42331</v>
+      </c>
+      <c r="C20">
+        <v>2015</v>
+      </c>
+      <c r="D20">
+        <v>327</v>
+      </c>
+      <c r="E20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20">
+        <v>4</v>
+      </c>
+      <c r="H20">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="2">
+        <v>42334</v>
+      </c>
+      <c r="C21">
+        <v>2015</v>
+      </c>
+      <c r="D21">
+        <v>330</v>
+      </c>
+      <c r="E21" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G21">
+        <v>19</v>
+      </c>
+      <c r="H21">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="2">
+        <v>42339</v>
+      </c>
+      <c r="C22">
+        <v>2015</v>
+      </c>
+      <c r="D22">
+        <v>335</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22">
+        <v>30</v>
+      </c>
+      <c r="H22">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="2">
+        <v>42342</v>
+      </c>
+      <c r="C23">
+        <v>2015</v>
+      </c>
+      <c r="D23">
+        <v>338</v>
+      </c>
+      <c r="E23" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>324</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="2">
+        <v>42320</v>
+      </c>
+      <c r="C24">
+        <v>2015</v>
+      </c>
+      <c r="D24">
+        <v>316</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>326</v>
+      </c>
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="2">
+        <v>42325</v>
+      </c>
+      <c r="C25">
+        <v>2015</v>
+      </c>
+      <c r="D25">
+        <v>321</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="2">
+        <v>42327</v>
+      </c>
+      <c r="C26">
+        <v>2015</v>
+      </c>
+      <c r="D26">
+        <v>323</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>19</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="2">
+        <v>42331</v>
+      </c>
+      <c r="C27">
+        <v>2015</v>
+      </c>
+      <c r="D27">
+        <v>327</v>
+      </c>
+      <c r="E27" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="2">
+        <v>42334</v>
+      </c>
+      <c r="C28">
+        <v>2015</v>
+      </c>
+      <c r="D28">
+        <v>330</v>
+      </c>
+      <c r="E28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" t="s">
+        <v>19</v>
+      </c>
+      <c r="G28">
+        <v>5.5</v>
+      </c>
+      <c r="H28">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="2">
+        <v>42339</v>
+      </c>
+      <c r="C29">
+        <v>2015</v>
+      </c>
+      <c r="D29">
+        <v>335</v>
+      </c>
+      <c r="E29" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29">
+        <v>18.5</v>
+      </c>
+      <c r="H29">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="2">
+        <v>42341</v>
+      </c>
+      <c r="C30">
+        <v>2015</v>
+      </c>
+      <c r="D30">
+        <v>337</v>
+      </c>
+      <c r="E30" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30">
+        <v>19</v>
+      </c>
+      <c r="H30">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="2">
+        <v>42345</v>
+      </c>
+      <c r="C31">
+        <v>2015</v>
+      </c>
+      <c r="D31">
+        <v>341</v>
+      </c>
+      <c r="E31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31">
+        <v>20</v>
+      </c>
+      <c r="H31">
+        <v>326</v>
+      </c>
+      <c r="I31" t="s">
+        <v>44</v>
+      </c>
+      <c r="J31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" s="2">
+        <v>39769</v>
+      </c>
+      <c r="C32">
+        <v>2008</v>
+      </c>
+      <c r="D32">
+        <v>322</v>
+      </c>
+      <c r="E32" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>325</v>
+      </c>
+      <c r="I32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="2">
+        <v>39772</v>
+      </c>
+      <c r="C33">
+        <v>2008</v>
+      </c>
+      <c r="D33">
+        <v>325</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34" s="2">
+        <v>39776</v>
+      </c>
+      <c r="C34">
+        <v>2008</v>
+      </c>
+      <c r="D34">
+        <v>329</v>
+      </c>
+      <c r="E34" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34">
+        <v>10.5</v>
+      </c>
+      <c r="H34">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="2">
+        <v>39780</v>
+      </c>
+      <c r="C35">
+        <v>2008</v>
+      </c>
+      <c r="D35">
+        <v>333</v>
+      </c>
+      <c r="E35" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35">
+        <v>27</v>
+      </c>
+      <c r="H35">
+        <v>325</v>
+      </c>
+      <c r="I35" t="s">
+        <v>44</v>
+      </c>
+      <c r="J35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="2">
+        <v>39770</v>
+      </c>
+      <c r="C36">
+        <v>2008</v>
+      </c>
+      <c r="D36">
+        <v>323</v>
+      </c>
+      <c r="E36" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>327</v>
+      </c>
+      <c r="I36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="2">
+        <v>39776</v>
+      </c>
+      <c r="C37">
+        <v>2008</v>
+      </c>
+      <c r="D37">
+        <v>329</v>
+      </c>
+      <c r="E37" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="2">
+        <v>39780</v>
+      </c>
+      <c r="C38">
+        <v>2008</v>
+      </c>
+      <c r="D38">
+        <v>333</v>
+      </c>
+      <c r="E38" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38">
+        <v>15</v>
+      </c>
+      <c r="H38">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="2">
+        <v>39783</v>
+      </c>
+      <c r="C39">
+        <v>2008</v>
+      </c>
+      <c r="D39">
+        <v>336</v>
+      </c>
+      <c r="E39" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39">
+        <v>17</v>
+      </c>
+      <c r="H39">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="2">
+        <v>39786</v>
+      </c>
+      <c r="C40">
+        <v>2008</v>
+      </c>
+      <c r="D40">
+        <v>339</v>
+      </c>
+      <c r="E40" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40">
+        <v>18</v>
+      </c>
+      <c r="H40">
+        <v>327</v>
+      </c>
+      <c r="I40" t="s">
+        <v>44</v>
+      </c>
+      <c r="J40">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="2">
+        <v>40133</v>
+      </c>
+      <c r="C41">
+        <v>2009</v>
+      </c>
+      <c r="D41">
+        <v>320</v>
+      </c>
+      <c r="E41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>320</v>
+      </c>
+      <c r="I41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>22</v>
+      </c>
+      <c r="B42" s="2">
+        <v>40137</v>
+      </c>
+      <c r="C42">
+        <v>2009</v>
+      </c>
+      <c r="D42">
+        <v>324</v>
+      </c>
+      <c r="E42" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42">
+        <v>11</v>
+      </c>
+      <c r="H42">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="2">
+        <v>40141</v>
+      </c>
+      <c r="C43">
+        <v>2009</v>
+      </c>
+      <c r="D43">
+        <v>328</v>
+      </c>
+      <c r="E43" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43">
+        <v>18</v>
+      </c>
+      <c r="H43">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="2">
+        <v>40144</v>
+      </c>
+      <c r="C44">
+        <v>2009</v>
+      </c>
+      <c r="D44">
+        <v>331</v>
+      </c>
+      <c r="E44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44">
+        <v>20</v>
+      </c>
+      <c r="H44">
+        <v>320</v>
+      </c>
+      <c r="I44" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="2">
+        <v>40133</v>
+      </c>
+      <c r="C45">
+        <v>2009</v>
+      </c>
+      <c r="D45">
+        <v>320</v>
+      </c>
+      <c r="E45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>320</v>
+      </c>
+      <c r="I45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="2">
+        <v>40137</v>
+      </c>
+      <c r="C46">
+        <v>2009</v>
+      </c>
+      <c r="D46">
+        <v>324</v>
+      </c>
+      <c r="E46" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="2">
+        <v>40141</v>
+      </c>
+      <c r="C47">
+        <v>2009</v>
+      </c>
+      <c r="D47">
+        <v>328</v>
+      </c>
+      <c r="E47" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
+      </c>
+      <c r="H47">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B48" s="2">
+        <v>40144</v>
+      </c>
+      <c r="C48">
+        <v>2009</v>
+      </c>
+      <c r="D48">
+        <v>331</v>
+      </c>
+      <c r="E48" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>17.5</v>
+      </c>
+      <c r="H48">
+        <v>320</v>
+      </c>
+      <c r="I48" t="s">
+        <v>44</v>
+      </c>
+      <c r="J48">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="2">
+        <v>40498</v>
+      </c>
+      <c r="C49">
+        <v>2010</v>
+      </c>
+      <c r="D49">
+        <v>320</v>
+      </c>
+      <c r="E49" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49">
+        <v>320</v>
+      </c>
+      <c r="I49" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="2">
+        <v>40502</v>
+      </c>
+      <c r="C50">
+        <v>2010</v>
+      </c>
+      <c r="D50">
+        <v>324</v>
+      </c>
+      <c r="E50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>11</v>
+      </c>
+      <c r="H50">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="2">
+        <v>40506</v>
+      </c>
+      <c r="C51">
+        <v>2010</v>
+      </c>
+      <c r="D51">
+        <v>328</v>
+      </c>
+      <c r="E51" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>18</v>
+      </c>
+      <c r="H51">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="2">
+        <v>40509</v>
+      </c>
+      <c r="C52">
+        <v>2010</v>
+      </c>
+      <c r="D52">
+        <v>331</v>
+      </c>
+      <c r="E52" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>20</v>
+      </c>
+      <c r="H52">
+        <v>320</v>
+      </c>
+      <c r="I52" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="2">
+        <v>40501</v>
+      </c>
+      <c r="C53">
+        <v>2010</v>
+      </c>
+      <c r="D53">
+        <v>323</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>327</v>
+      </c>
+      <c r="I53" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="2">
+        <v>40504</v>
+      </c>
+      <c r="C54">
+        <v>2010</v>
+      </c>
+      <c r="D54">
+        <v>326</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="2">
+        <v>40507</v>
+      </c>
+      <c r="C55">
+        <v>2010</v>
+      </c>
+      <c r="D55">
+        <v>329</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>0.5</v>
+      </c>
+      <c r="H55">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="2">
+        <v>40511</v>
+      </c>
+      <c r="C56">
+        <v>2010</v>
+      </c>
+      <c r="D56">
+        <v>333</v>
+      </c>
+      <c r="E56" t="s">
+        <v>10</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+      <c r="H56">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="2">
+        <v>40514</v>
+      </c>
+      <c r="C57">
+        <v>2010</v>
+      </c>
+      <c r="D57">
+        <v>336</v>
+      </c>
+      <c r="E57" t="s">
+        <v>10</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57">
+        <v>9</v>
+      </c>
+      <c r="H57">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="2">
+        <v>40519</v>
+      </c>
+      <c r="C58">
+        <v>2010</v>
+      </c>
+      <c r="D58">
+        <v>341</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58">
+        <v>12</v>
+      </c>
+      <c r="H58">
+        <v>327</v>
+      </c>
+      <c r="I58" t="s">
+        <v>44</v>
+      </c>
+      <c r="J58">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="2">
+        <v>40507</v>
+      </c>
+      <c r="C59">
+        <v>2010</v>
+      </c>
+      <c r="D59">
+        <v>329</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>329</v>
+      </c>
+      <c r="I59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>26</v>
+      </c>
+      <c r="B60" s="2">
+        <v>40512</v>
+      </c>
+      <c r="C60">
+        <v>2010</v>
+      </c>
+      <c r="D60">
+        <v>334</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60">
+        <v>2.5</v>
+      </c>
+      <c r="H60">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="2">
+        <v>40519</v>
+      </c>
+      <c r="C61">
+        <v>2010</v>
+      </c>
+      <c r="D61">
+        <v>341</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61">
+        <v>8.5</v>
+      </c>
+      <c r="H61">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>26</v>
+      </c>
+      <c r="B62" s="2">
+        <v>40525</v>
+      </c>
+      <c r="C62">
+        <v>2010</v>
+      </c>
+      <c r="D62">
+        <v>347</v>
+      </c>
+      <c r="E62" t="s">
+        <v>18</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62">
+        <v>10.5</v>
+      </c>
+      <c r="H62">
+        <v>329</v>
+      </c>
+      <c r="I62" t="s">
+        <v>44</v>
+      </c>
+      <c r="J62">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>27</v>
+      </c>
+      <c r="B63" s="2">
+        <v>40861</v>
+      </c>
+      <c r="C63">
+        <v>2011</v>
+      </c>
+      <c r="D63">
+        <v>318</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>331</v>
+      </c>
+      <c r="I63" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="2">
+        <v>40868</v>
+      </c>
+      <c r="C64">
+        <v>2011</v>
+      </c>
+      <c r="D64">
+        <v>325</v>
+      </c>
+      <c r="E64" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>27</v>
+      </c>
+      <c r="B65" s="2">
+        <v>40872</v>
+      </c>
+      <c r="C65">
+        <v>2011</v>
+      </c>
+      <c r="D65">
+        <v>329</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>27</v>
+      </c>
+      <c r="B66" s="2">
+        <v>40878</v>
+      </c>
+      <c r="C66">
+        <v>2011</v>
+      </c>
+      <c r="D66">
+        <v>335</v>
+      </c>
+      <c r="E66" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>27</v>
+      </c>
+      <c r="B67" s="2">
+        <v>40885</v>
+      </c>
+      <c r="C67">
+        <v>2011</v>
+      </c>
+      <c r="D67">
+        <v>342</v>
+      </c>
+      <c r="E67" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67">
+        <v>8.5</v>
+      </c>
+      <c r="H67">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>27</v>
+      </c>
+      <c r="B68" s="2">
+        <v>40891</v>
+      </c>
+      <c r="C68">
+        <v>2011</v>
+      </c>
+      <c r="D68">
+        <v>348</v>
+      </c>
+      <c r="E68" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68">
+        <v>11.5</v>
+      </c>
+      <c r="H68">
+        <v>331</v>
+      </c>
+      <c r="I68" t="s">
+        <v>44</v>
+      </c>
+      <c r="J68">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>28</v>
+      </c>
+      <c r="B69" s="2">
+        <v>41593</v>
+      </c>
+      <c r="C69">
+        <v>2013</v>
+      </c>
+      <c r="D69">
+        <v>319</v>
+      </c>
+      <c r="E69" t="s">
+        <v>10</v>
+      </c>
+      <c r="F69" t="s">
+        <v>29</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>326</v>
+      </c>
+      <c r="I69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>28</v>
+      </c>
+      <c r="B70" s="2">
+        <v>41597</v>
+      </c>
+      <c r="C70">
+        <v>2013</v>
+      </c>
+      <c r="D70">
+        <v>323</v>
+      </c>
+      <c r="E70" t="s">
+        <v>10</v>
+      </c>
+      <c r="F70" t="s">
+        <v>29</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>28</v>
+      </c>
+      <c r="B71" s="2">
+        <v>41600</v>
+      </c>
+      <c r="C71">
+        <v>2013</v>
+      </c>
+      <c r="D71">
+        <v>326</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
+        <v>29</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" s="2">
+        <v>41603</v>
+      </c>
+      <c r="C72">
+        <v>2013</v>
+      </c>
+      <c r="D72">
+        <v>329</v>
+      </c>
+      <c r="E72" t="s">
+        <v>10</v>
+      </c>
+      <c r="F72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72">
+        <v>2</v>
+      </c>
+      <c r="H72">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" s="2">
+        <v>41607</v>
+      </c>
+      <c r="C73">
+        <v>2013</v>
+      </c>
+      <c r="D73">
+        <v>333</v>
+      </c>
+      <c r="E73" t="s">
+        <v>10</v>
+      </c>
+      <c r="F73" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73">
+        <v>14</v>
+      </c>
+      <c r="H73">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="2">
+        <v>41611</v>
+      </c>
+      <c r="C74">
+        <v>2013</v>
+      </c>
+      <c r="D74">
+        <v>337</v>
+      </c>
+      <c r="E74" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74">
+        <v>21</v>
+      </c>
+      <c r="H74">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" s="2">
+        <v>41614</v>
+      </c>
+      <c r="C75">
+        <v>2013</v>
+      </c>
+      <c r="D75">
+        <v>340</v>
+      </c>
+      <c r="E75" t="s">
+        <v>10</v>
+      </c>
+      <c r="F75" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75">
+        <v>22</v>
+      </c>
+      <c r="H75">
+        <v>326</v>
+      </c>
+      <c r="I75" t="s">
+        <v>44</v>
+      </c>
+      <c r="J75">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>30</v>
+      </c>
+      <c r="B76" s="2">
+        <v>41589</v>
+      </c>
+      <c r="C76">
+        <v>2013</v>
+      </c>
+      <c r="D76">
+        <v>315</v>
+      </c>
+      <c r="E76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F76" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>322</v>
+      </c>
+      <c r="I76" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" s="2">
+        <v>41591</v>
+      </c>
+      <c r="C77">
+        <v>2013</v>
+      </c>
+      <c r="D77">
+        <v>317</v>
+      </c>
+      <c r="E77" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>30</v>
+      </c>
+      <c r="B78" s="2">
+        <v>41593</v>
+      </c>
+      <c r="C78">
+        <v>2013</v>
+      </c>
+      <c r="D78">
+        <v>319</v>
+      </c>
+      <c r="E78" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>30</v>
+      </c>
+      <c r="B79" s="2">
+        <v>41596</v>
+      </c>
+      <c r="C79">
+        <v>2013</v>
+      </c>
+      <c r="D79">
+        <v>322</v>
+      </c>
+      <c r="E79" t="s">
+        <v>18</v>
+      </c>
+      <c r="F79" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" s="2">
+        <v>41599</v>
+      </c>
+      <c r="C80">
+        <v>2013</v>
+      </c>
+      <c r="D80">
+        <v>325</v>
+      </c>
+      <c r="E80" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" t="s">
+        <v>29</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" s="2">
+        <v>41603</v>
+      </c>
+      <c r="C81">
+        <v>2013</v>
+      </c>
+      <c r="D81">
+        <v>329</v>
+      </c>
+      <c r="E81" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" t="s">
+        <v>29</v>
+      </c>
+      <c r="G81">
+        <v>4</v>
+      </c>
+      <c r="H81">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" s="2">
+        <v>41606</v>
+      </c>
+      <c r="C82">
+        <v>2013</v>
+      </c>
+      <c r="D82">
+        <v>332</v>
+      </c>
+      <c r="E82" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" t="s">
+        <v>29</v>
+      </c>
+      <c r="G82">
+        <v>5</v>
+      </c>
+      <c r="H82">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" s="2">
+        <v>41610</v>
+      </c>
+      <c r="C83">
+        <v>2013</v>
+      </c>
+      <c r="D83">
+        <v>336</v>
+      </c>
+      <c r="E83" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" t="s">
+        <v>29</v>
+      </c>
+      <c r="G83">
+        <v>8</v>
+      </c>
+      <c r="H83">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" s="2">
+        <v>41614</v>
+      </c>
+      <c r="C84">
+        <v>2013</v>
+      </c>
+      <c r="D84">
+        <v>340</v>
+      </c>
+      <c r="E84" t="s">
+        <v>18</v>
+      </c>
+      <c r="F84" t="s">
+        <v>29</v>
+      </c>
+      <c r="G84">
+        <v>10</v>
+      </c>
+      <c r="H84">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" s="2">
+        <v>41617</v>
+      </c>
+      <c r="C85">
+        <v>2013</v>
+      </c>
+      <c r="D85">
+        <v>343</v>
+      </c>
+      <c r="E85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" t="s">
+        <v>29</v>
+      </c>
+      <c r="G85">
+        <v>10</v>
+      </c>
+      <c r="H85">
+        <v>322</v>
+      </c>
+      <c r="I85" t="s">
+        <v>44</v>
+      </c>
+      <c r="J85">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" s="2">
+        <v>43396</v>
+      </c>
+      <c r="C86">
+        <v>2018</v>
+      </c>
+      <c r="D86">
+        <v>296</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" t="s">
+        <v>19</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>320</v>
+      </c>
+      <c r="I86" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="2">
+        <v>43416</v>
+      </c>
+      <c r="C87">
+        <v>2018</v>
+      </c>
+      <c r="D87">
+        <v>316</v>
+      </c>
+      <c r="E87" t="s">
+        <v>10</v>
+      </c>
+      <c r="F87" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" s="2">
+        <v>43419</v>
+      </c>
+      <c r="C88">
+        <v>2018</v>
+      </c>
+      <c r="D88">
+        <v>319</v>
+      </c>
+      <c r="E88" t="s">
+        <v>10</v>
+      </c>
+      <c r="F88" t="s">
+        <v>19</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" s="2">
+        <v>43424</v>
+      </c>
+      <c r="C89">
+        <v>2018</v>
+      </c>
+      <c r="D89">
+        <v>324</v>
+      </c>
+      <c r="E89" t="s">
+        <v>10</v>
+      </c>
+      <c r="F89" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" s="2">
+        <v>43430</v>
+      </c>
+      <c r="C90">
+        <v>2018</v>
+      </c>
+      <c r="D90">
+        <v>330</v>
+      </c>
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" t="s">
+        <v>19</v>
+      </c>
+      <c r="G90">
+        <v>8</v>
+      </c>
+      <c r="H90">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91" s="2">
+        <v>43437</v>
+      </c>
+      <c r="C91">
+        <v>2018</v>
+      </c>
+      <c r="D91">
+        <v>337</v>
+      </c>
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91">
+        <v>10.5</v>
+      </c>
+      <c r="H91">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>31</v>
+      </c>
+      <c r="B92" s="2">
+        <v>43444</v>
+      </c>
+      <c r="C92">
+        <v>2018</v>
+      </c>
+      <c r="D92">
+        <v>344</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92">
+        <v>10.5</v>
+      </c>
+      <c r="H92">
+        <v>320</v>
+      </c>
+      <c r="I92" t="s">
+        <v>44</v>
+      </c>
+      <c r="J92">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" s="2">
+        <v>43402</v>
+      </c>
+      <c r="C93">
+        <v>2018</v>
+      </c>
+      <c r="D93">
+        <v>302</v>
+      </c>
+      <c r="E93" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" t="s">
+        <v>33</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>321</v>
+      </c>
+      <c r="I93" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" s="2">
+        <v>43404</v>
+      </c>
+      <c r="C94">
+        <v>2018</v>
+      </c>
+      <c r="D94">
+        <v>304</v>
+      </c>
+      <c r="E94" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" t="s">
+        <v>33</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="2">
+        <v>43406</v>
+      </c>
+      <c r="C95">
+        <v>2018</v>
+      </c>
+      <c r="D95">
+        <v>306</v>
+      </c>
+      <c r="E95" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" t="s">
+        <v>33</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="2">
+        <v>43409</v>
+      </c>
+      <c r="C96">
+        <v>2018</v>
+      </c>
+      <c r="D96">
+        <v>309</v>
+      </c>
+      <c r="E96" t="s">
+        <v>18</v>
+      </c>
+      <c r="F96" t="s">
+        <v>33</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" s="2">
+        <v>43411</v>
+      </c>
+      <c r="C97">
+        <v>2018</v>
+      </c>
+      <c r="D97">
+        <v>311</v>
+      </c>
+      <c r="E97" t="s">
+        <v>18</v>
+      </c>
+      <c r="F97" t="s">
+        <v>33</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>32</v>
+      </c>
+      <c r="B98" s="2">
+        <v>43413</v>
+      </c>
+      <c r="C98">
+        <v>2018</v>
+      </c>
+      <c r="D98">
+        <v>313</v>
+      </c>
+      <c r="E98" t="s">
+        <v>18</v>
+      </c>
+      <c r="F98" t="s">
+        <v>33</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>32</v>
+      </c>
+      <c r="B99" s="2">
+        <v>43416</v>
+      </c>
+      <c r="C99">
+        <v>2018</v>
+      </c>
+      <c r="D99">
+        <v>316</v>
+      </c>
+      <c r="E99" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" t="s">
+        <v>33</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>32</v>
+      </c>
+      <c r="B100" s="2">
+        <v>43418</v>
+      </c>
+      <c r="C100">
+        <v>2018</v>
+      </c>
+      <c r="D100">
+        <v>318</v>
+      </c>
+      <c r="E100" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" t="s">
+        <v>33</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>32</v>
+      </c>
+      <c r="B101" s="2">
+        <v>43420</v>
+      </c>
+      <c r="C101">
+        <v>2018</v>
+      </c>
+      <c r="D101">
+        <v>320</v>
+      </c>
+      <c r="E101" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" t="s">
+        <v>33</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>32</v>
+      </c>
+      <c r="B102" s="2">
+        <v>43423</v>
+      </c>
+      <c r="C102">
+        <v>2018</v>
+      </c>
+      <c r="D102">
+        <v>323</v>
+      </c>
+      <c r="E102" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" t="s">
+        <v>33</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="2">
+        <v>43425</v>
+      </c>
+      <c r="C103">
+        <v>2018</v>
+      </c>
+      <c r="D103">
+        <v>325</v>
+      </c>
+      <c r="E103" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" t="s">
+        <v>33</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>32</v>
+      </c>
+      <c r="B104" s="2">
+        <v>43427</v>
+      </c>
+      <c r="C104">
+        <v>2018</v>
+      </c>
+      <c r="D104">
+        <v>327</v>
+      </c>
+      <c r="E104" t="s">
+        <v>18</v>
+      </c>
+      <c r="F104" t="s">
+        <v>33</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>32</v>
+      </c>
+      <c r="B105" s="2">
+        <v>43430</v>
+      </c>
+      <c r="C105">
+        <v>2018</v>
+      </c>
+      <c r="D105">
+        <v>330</v>
+      </c>
+      <c r="E105" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" t="s">
+        <v>33</v>
+      </c>
+      <c r="G105">
+        <v>2.5</v>
+      </c>
+      <c r="H105">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>32</v>
+      </c>
+      <c r="B106" s="2">
+        <v>43432</v>
+      </c>
+      <c r="C106">
+        <v>2018</v>
+      </c>
+      <c r="D106">
+        <v>332</v>
+      </c>
+      <c r="E106" t="s">
+        <v>18</v>
+      </c>
+      <c r="F106" t="s">
+        <v>33</v>
+      </c>
+      <c r="G106">
+        <v>3.5</v>
+      </c>
+      <c r="H106">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>32</v>
+      </c>
+      <c r="B107" s="2">
+        <v>43434</v>
+      </c>
+      <c r="C107">
+        <v>2018</v>
+      </c>
+      <c r="D107">
+        <v>334</v>
+      </c>
+      <c r="E107" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" t="s">
+        <v>33</v>
+      </c>
+      <c r="G107">
+        <v>3.5</v>
+      </c>
+      <c r="H107">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>32</v>
+      </c>
+      <c r="B108" s="2">
+        <v>43437</v>
+      </c>
+      <c r="C108">
+        <v>2018</v>
+      </c>
+      <c r="D108">
+        <v>337</v>
+      </c>
+      <c r="E108" t="s">
+        <v>18</v>
+      </c>
+      <c r="F108" t="s">
+        <v>33</v>
+      </c>
+      <c r="G108">
+        <v>6</v>
+      </c>
+      <c r="H108">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>32</v>
+      </c>
+      <c r="B109" s="2">
+        <v>43439</v>
+      </c>
+      <c r="C109">
+        <v>2018</v>
+      </c>
+      <c r="D109">
+        <v>339</v>
+      </c>
+      <c r="E109" t="s">
+        <v>18</v>
+      </c>
+      <c r="F109" t="s">
+        <v>33</v>
+      </c>
+      <c r="G109">
+        <v>6</v>
+      </c>
+      <c r="H109">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>32</v>
+      </c>
+      <c r="B110" s="2">
+        <v>43441</v>
+      </c>
+      <c r="C110">
+        <v>2018</v>
+      </c>
+      <c r="D110">
+        <v>341</v>
+      </c>
+      <c r="E110" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" t="s">
+        <v>33</v>
+      </c>
+      <c r="G110">
+        <v>6.5</v>
+      </c>
+      <c r="H110">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>32</v>
+      </c>
+      <c r="B111" s="2">
+        <v>43444</v>
+      </c>
+      <c r="C111">
+        <v>2018</v>
+      </c>
+      <c r="D111">
+        <v>344</v>
+      </c>
+      <c r="E111" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" t="s">
+        <v>33</v>
+      </c>
+      <c r="G111">
+        <v>6.5</v>
+      </c>
+      <c r="H111">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B112" s="2">
+        <v>43446</v>
+      </c>
+      <c r="C112">
+        <v>2018</v>
+      </c>
+      <c r="D112">
+        <v>346</v>
+      </c>
+      <c r="E112" t="s">
+        <v>18</v>
+      </c>
+      <c r="F112" t="s">
+        <v>33</v>
+      </c>
+      <c r="G112">
+        <v>6.5</v>
+      </c>
+      <c r="H112">
+        <v>321</v>
+      </c>
+      <c r="I112" t="s">
+        <v>44</v>
+      </c>
+      <c r="J112">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>34</v>
+      </c>
+      <c r="B113" s="2">
+        <v>43780</v>
+      </c>
+      <c r="C113">
+        <v>2019</v>
+      </c>
+      <c r="D113">
+        <v>315</v>
+      </c>
+      <c r="E113" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" t="s">
+        <v>35</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>315</v>
+      </c>
+      <c r="I113" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>34</v>
+      </c>
+      <c r="B114" s="2">
+        <v>43782</v>
+      </c>
+      <c r="C114">
+        <v>2019</v>
+      </c>
+      <c r="D114">
+        <v>317</v>
+      </c>
+      <c r="E114" t="s">
+        <v>18</v>
+      </c>
+      <c r="F114" t="s">
+        <v>35</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>34</v>
+      </c>
+      <c r="B115" s="2">
+        <v>43784</v>
+      </c>
+      <c r="C115">
+        <v>2019</v>
+      </c>
+      <c r="D115">
+        <v>319</v>
+      </c>
+      <c r="E115" t="s">
+        <v>18</v>
+      </c>
+      <c r="F115" t="s">
+        <v>35</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>34</v>
+      </c>
+      <c r="B116" s="2">
+        <v>43787</v>
+      </c>
+      <c r="C116">
+        <v>2019</v>
+      </c>
+      <c r="D116">
+        <v>322</v>
+      </c>
+      <c r="E116" t="s">
+        <v>18</v>
+      </c>
+      <c r="F116" t="s">
+        <v>35</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>34</v>
+      </c>
+      <c r="B117" s="2">
+        <v>43789</v>
+      </c>
+      <c r="C117">
+        <v>2019</v>
+      </c>
+      <c r="D117">
+        <v>324</v>
+      </c>
+      <c r="E117" t="s">
+        <v>18</v>
+      </c>
+      <c r="F117" t="s">
+        <v>35</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>34</v>
+      </c>
+      <c r="B118" s="2">
+        <v>43791</v>
+      </c>
+      <c r="C118">
+        <v>2019</v>
+      </c>
+      <c r="D118">
+        <v>326</v>
+      </c>
+      <c r="E118" t="s">
+        <v>18</v>
+      </c>
+      <c r="F118" t="s">
+        <v>35</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" s="2">
+        <v>43794</v>
+      </c>
+      <c r="C119">
+        <v>2019</v>
+      </c>
+      <c r="D119">
+        <v>329</v>
+      </c>
+      <c r="E119" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" t="s">
+        <v>35</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>34</v>
+      </c>
+      <c r="B120" s="2">
+        <v>43796</v>
+      </c>
+      <c r="C120">
+        <v>2019</v>
+      </c>
+      <c r="D120">
+        <v>331</v>
+      </c>
+      <c r="E120" t="s">
+        <v>18</v>
+      </c>
+      <c r="F120" t="s">
+        <v>35</v>
+      </c>
+      <c r="G120">
+        <v>2</v>
+      </c>
+      <c r="H120">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" s="2">
+        <v>43798</v>
+      </c>
+      <c r="C121">
+        <v>2019</v>
+      </c>
+      <c r="D121">
+        <v>333</v>
+      </c>
+      <c r="E121" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" t="s">
+        <v>35</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="H121">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>34</v>
+      </c>
+      <c r="B122" s="2">
+        <v>43801</v>
+      </c>
+      <c r="C122">
+        <v>2019</v>
+      </c>
+      <c r="D122">
+        <v>336</v>
+      </c>
+      <c r="E122" t="s">
+        <v>18</v>
+      </c>
+      <c r="F122" t="s">
+        <v>35</v>
+      </c>
+      <c r="G122">
+        <v>2</v>
+      </c>
+      <c r="H122">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123" s="2">
+        <v>43805</v>
+      </c>
+      <c r="C123">
+        <v>2019</v>
+      </c>
+      <c r="D123">
+        <v>340</v>
+      </c>
+      <c r="E123" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" t="s">
+        <v>35</v>
+      </c>
+      <c r="G123">
+        <v>2</v>
+      </c>
+      <c r="H123">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>34</v>
+      </c>
+      <c r="B124" s="2">
+        <v>43808</v>
+      </c>
+      <c r="C124">
+        <v>2019</v>
+      </c>
+      <c r="D124">
+        <v>343</v>
+      </c>
+      <c r="E124" t="s">
+        <v>18</v>
+      </c>
+      <c r="F124" t="s">
+        <v>35</v>
+      </c>
+      <c r="G124">
+        <v>3</v>
+      </c>
+      <c r="H124">
+        <v>315</v>
+      </c>
+      <c r="I124" t="s">
+        <v>44</v>
+      </c>
+      <c r="J124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>36</v>
+      </c>
+      <c r="B125" s="2">
+        <v>44138</v>
+      </c>
+      <c r="C125">
+        <v>2020</v>
+      </c>
+      <c r="D125">
+        <v>308</v>
+      </c>
+      <c r="E125" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>317</v>
+      </c>
+      <c r="I125" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>36</v>
+      </c>
+      <c r="B126" s="2">
+        <v>44141</v>
+      </c>
+      <c r="C126">
+        <v>2020</v>
+      </c>
+      <c r="D126">
+        <v>311</v>
+      </c>
+      <c r="E126" t="s">
+        <v>18</v>
+      </c>
+      <c r="F126" t="s">
+        <v>19</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>36</v>
+      </c>
+      <c r="B127" s="2">
+        <v>44144</v>
+      </c>
+      <c r="C127">
+        <v>2020</v>
+      </c>
+      <c r="D127">
+        <v>314</v>
+      </c>
+      <c r="E127" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>36</v>
+      </c>
+      <c r="B128" s="2">
+        <v>44146</v>
+      </c>
+      <c r="C128">
+        <v>2020</v>
+      </c>
+      <c r="D128">
+        <v>316</v>
+      </c>
+      <c r="E128" t="s">
+        <v>18</v>
+      </c>
+      <c r="F128" t="s">
+        <v>19</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>36</v>
+      </c>
+      <c r="B129" s="2">
+        <v>44148</v>
+      </c>
+      <c r="C129">
+        <v>2020</v>
+      </c>
+      <c r="D129">
+        <v>318</v>
+      </c>
+      <c r="E129" t="s">
+        <v>18</v>
+      </c>
+      <c r="F129" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>36</v>
+      </c>
+      <c r="B130" s="2">
+        <v>44151</v>
+      </c>
+      <c r="C130">
+        <v>2020</v>
+      </c>
+      <c r="D130">
+        <v>321</v>
+      </c>
+      <c r="E130" t="s">
+        <v>18</v>
+      </c>
+      <c r="F130" t="s">
+        <v>19</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>36</v>
+      </c>
+      <c r="B131" s="2">
+        <v>44153</v>
+      </c>
+      <c r="C131">
+        <v>2020</v>
+      </c>
+      <c r="D131">
+        <v>323</v>
+      </c>
+      <c r="E131" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>36</v>
+      </c>
+      <c r="B132" s="2">
+        <v>44155</v>
+      </c>
+      <c r="C132">
+        <v>2020</v>
+      </c>
+      <c r="D132">
+        <v>325</v>
+      </c>
+      <c r="E132" t="s">
+        <v>18</v>
+      </c>
+      <c r="F132" t="s">
+        <v>19</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>36</v>
+      </c>
+      <c r="B133" s="2">
+        <v>44158</v>
+      </c>
+      <c r="C133">
+        <v>2020</v>
+      </c>
+      <c r="D133">
+        <v>328</v>
+      </c>
+      <c r="E133" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>36</v>
+      </c>
+      <c r="B134" s="2">
+        <v>44160</v>
+      </c>
+      <c r="C134">
+        <v>2020</v>
+      </c>
+      <c r="D134">
+        <v>330</v>
+      </c>
+      <c r="E134" t="s">
+        <v>18</v>
+      </c>
+      <c r="F134" t="s">
+        <v>19</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135" s="2">
+        <v>44162</v>
+      </c>
+      <c r="C135">
+        <v>2020</v>
+      </c>
+      <c r="D135">
+        <v>332</v>
+      </c>
+      <c r="E135" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>36</v>
+      </c>
+      <c r="B136" s="2">
+        <v>44165</v>
+      </c>
+      <c r="C136">
+        <v>2020</v>
+      </c>
+      <c r="D136">
+        <v>335</v>
+      </c>
+      <c r="E136" t="s">
+        <v>18</v>
+      </c>
+      <c r="F136" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>36</v>
+      </c>
+      <c r="B137" s="2">
+        <v>44167</v>
+      </c>
+      <c r="C137">
+        <v>2020</v>
+      </c>
+      <c r="D137">
+        <v>337</v>
+      </c>
+      <c r="E137" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137">
+        <v>1</v>
+      </c>
+      <c r="H137">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>36</v>
+      </c>
+      <c r="B138" s="2">
+        <v>44169</v>
+      </c>
+      <c r="C138">
+        <v>2020</v>
+      </c>
+      <c r="D138">
+        <v>339</v>
+      </c>
+      <c r="E138" t="s">
+        <v>18</v>
+      </c>
+      <c r="F138" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138">
+        <v>1</v>
+      </c>
+      <c r="H138">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>36</v>
+      </c>
+      <c r="B139" s="2">
+        <v>44172</v>
+      </c>
+      <c r="C139">
+        <v>2020</v>
+      </c>
+      <c r="D139">
+        <v>342</v>
+      </c>
+      <c r="E139" t="s">
+        <v>18</v>
+      </c>
+      <c r="F139" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139">
+        <v>2</v>
+      </c>
+      <c r="H139">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>36</v>
+      </c>
+      <c r="B140" s="2">
+        <v>44174</v>
+      </c>
+      <c r="C140">
+        <v>2020</v>
+      </c>
+      <c r="D140">
+        <v>344</v>
+      </c>
+      <c r="E140" t="s">
+        <v>18</v>
+      </c>
+      <c r="F140" t="s">
+        <v>19</v>
+      </c>
+      <c r="G140">
+        <v>2</v>
+      </c>
+      <c r="H140">
+        <v>317</v>
+      </c>
+      <c r="I140" t="s">
+        <v>44</v>
+      </c>
+      <c r="J140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>37</v>
+      </c>
+      <c r="B141" s="2">
+        <v>44144</v>
+      </c>
+      <c r="C141">
+        <v>2020</v>
+      </c>
+      <c r="D141">
+        <v>314</v>
+      </c>
+      <c r="E141" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141" t="s">
+        <v>35</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>314</v>
+      </c>
+      <c r="I141" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>37</v>
+      </c>
+      <c r="B142" s="2">
+        <v>44146</v>
+      </c>
+      <c r="C142">
+        <v>2020</v>
+      </c>
+      <c r="D142">
+        <v>316</v>
+      </c>
+      <c r="E142" t="s">
+        <v>18</v>
+      </c>
+      <c r="F142" t="s">
+        <v>35</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>37</v>
+      </c>
+      <c r="B143" s="2">
+        <v>44148</v>
+      </c>
+      <c r="C143">
+        <v>2020</v>
+      </c>
+      <c r="D143">
+        <v>318</v>
+      </c>
+      <c r="E143" t="s">
+        <v>18</v>
+      </c>
+      <c r="F143" t="s">
+        <v>35</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>37</v>
+      </c>
+      <c r="B144" s="2">
+        <v>44151</v>
+      </c>
+      <c r="C144">
+        <v>2020</v>
+      </c>
+      <c r="D144">
+        <v>321</v>
+      </c>
+      <c r="E144" t="s">
+        <v>18</v>
+      </c>
+      <c r="F144" t="s">
+        <v>35</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>37</v>
+      </c>
+      <c r="B145" s="2">
+        <v>44153</v>
+      </c>
+      <c r="C145">
+        <v>2020</v>
+      </c>
+      <c r="D145">
+        <v>323</v>
+      </c>
+      <c r="E145" t="s">
+        <v>18</v>
+      </c>
+      <c r="F145" t="s">
+        <v>35</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>37</v>
+      </c>
+      <c r="B146" s="2">
+        <v>44155</v>
+      </c>
+      <c r="C146">
+        <v>2020</v>
+      </c>
+      <c r="D146">
+        <v>325</v>
+      </c>
+      <c r="E146" t="s">
+        <v>18</v>
+      </c>
+      <c r="F146" t="s">
+        <v>35</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>37</v>
+      </c>
+      <c r="B147" s="2">
+        <v>44158</v>
+      </c>
+      <c r="C147">
+        <v>2020</v>
+      </c>
+      <c r="D147">
+        <v>328</v>
+      </c>
+      <c r="E147" t="s">
+        <v>18</v>
+      </c>
+      <c r="F147" t="s">
+        <v>35</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>37</v>
+      </c>
+      <c r="B148" s="2">
+        <v>44160</v>
+      </c>
+      <c r="C148">
+        <v>2020</v>
+      </c>
+      <c r="D148">
+        <v>330</v>
+      </c>
+      <c r="E148" t="s">
+        <v>18</v>
+      </c>
+      <c r="F148" t="s">
+        <v>35</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>37</v>
+      </c>
+      <c r="B149" s="2">
+        <v>44162</v>
+      </c>
+      <c r="C149">
+        <v>2020</v>
+      </c>
+      <c r="D149">
+        <v>332</v>
+      </c>
+      <c r="E149" t="s">
+        <v>18</v>
+      </c>
+      <c r="F149" t="s">
+        <v>35</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>37</v>
+      </c>
+      <c r="B150" s="2">
+        <v>44165</v>
+      </c>
+      <c r="C150">
+        <v>2020</v>
+      </c>
+      <c r="D150">
+        <v>335</v>
+      </c>
+      <c r="E150" t="s">
+        <v>18</v>
+      </c>
+      <c r="F150" t="s">
+        <v>35</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>37</v>
+      </c>
+      <c r="B151" s="2">
+        <v>44167</v>
+      </c>
+      <c r="C151">
+        <v>2020</v>
+      </c>
+      <c r="D151">
+        <v>337</v>
+      </c>
+      <c r="E151" t="s">
+        <v>18</v>
+      </c>
+      <c r="F151" t="s">
+        <v>35</v>
+      </c>
+      <c r="G151">
+        <v>1</v>
+      </c>
+      <c r="H151">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>37</v>
+      </c>
+      <c r="B152" s="2">
+        <v>44169</v>
+      </c>
+      <c r="C152">
+        <v>2020</v>
+      </c>
+      <c r="D152">
+        <v>339</v>
+      </c>
+      <c r="E152" t="s">
+        <v>18</v>
+      </c>
+      <c r="F152" t="s">
+        <v>35</v>
+      </c>
+      <c r="G152">
+        <v>2</v>
+      </c>
+      <c r="H152">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>37</v>
+      </c>
+      <c r="B153" s="2">
+        <v>44172</v>
+      </c>
+      <c r="C153">
+        <v>2020</v>
+      </c>
+      <c r="D153">
+        <v>342</v>
+      </c>
+      <c r="E153" t="s">
+        <v>18</v>
+      </c>
+      <c r="F153" t="s">
+        <v>35</v>
+      </c>
+      <c r="G153">
+        <v>2</v>
+      </c>
+      <c r="H153">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>37</v>
+      </c>
+      <c r="B154" s="2">
+        <v>44174</v>
+      </c>
+      <c r="C154">
+        <v>2020</v>
+      </c>
+      <c r="D154">
+        <v>344</v>
+      </c>
+      <c r="E154" t="s">
+        <v>18</v>
+      </c>
+      <c r="F154" t="s">
+        <v>35</v>
+      </c>
+      <c r="G154">
+        <v>2</v>
+      </c>
+      <c r="H154">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>37</v>
+      </c>
+      <c r="B155" s="2">
+        <v>44176</v>
+      </c>
+      <c r="C155">
+        <v>2020</v>
+      </c>
+      <c r="D155">
+        <v>346</v>
+      </c>
+      <c r="E155" t="s">
+        <v>18</v>
+      </c>
+      <c r="F155" t="s">
+        <v>35</v>
+      </c>
+      <c r="G155">
+        <v>2</v>
+      </c>
+      <c r="H155">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>37</v>
+      </c>
+      <c r="B156" s="2">
+        <v>44179</v>
+      </c>
+      <c r="C156">
+        <v>2020</v>
+      </c>
+      <c r="D156">
+        <v>349</v>
+      </c>
+      <c r="E156" t="s">
+        <v>18</v>
+      </c>
+      <c r="F156" t="s">
+        <v>35</v>
+      </c>
+      <c r="G156">
+        <v>2</v>
+      </c>
+      <c r="H156">
+        <v>314</v>
+      </c>
+      <c r="I156" t="s">
+        <v>44</v>
+      </c>
+      <c r="J156">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" s="2">
+        <v>44138</v>
+      </c>
+      <c r="C157">
+        <v>2020</v>
+      </c>
+      <c r="D157">
+        <v>308</v>
+      </c>
+      <c r="E157" t="s">
+        <v>10</v>
+      </c>
+      <c r="F157" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>38</v>
+      </c>
+      <c r="B158" s="2">
+        <v>44141</v>
+      </c>
+      <c r="C158">
+        <v>2020</v>
+      </c>
+      <c r="D158">
+        <v>311</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" t="s">
+        <v>19</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>38</v>
+      </c>
+      <c r="B159" s="2">
+        <v>44144</v>
+      </c>
+      <c r="C159">
+        <v>2020</v>
+      </c>
+      <c r="D159">
+        <v>314</v>
+      </c>
+      <c r="E159" t="s">
+        <v>10</v>
+      </c>
+      <c r="F159" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>38</v>
+      </c>
+      <c r="B160" s="2">
+        <v>44147</v>
+      </c>
+      <c r="C160">
+        <v>2020</v>
+      </c>
+      <c r="D160">
+        <v>317</v>
+      </c>
+      <c r="E160" t="s">
+        <v>10</v>
+      </c>
+      <c r="F160" t="s">
+        <v>19</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>38</v>
+      </c>
+      <c r="B161" s="2">
+        <v>44151</v>
+      </c>
+      <c r="C161">
+        <v>2020</v>
+      </c>
+      <c r="D161">
+        <v>321</v>
+      </c>
+      <c r="E161" t="s">
+        <v>10</v>
+      </c>
+      <c r="F161" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>38</v>
+      </c>
+      <c r="B162" s="2">
+        <v>44154</v>
+      </c>
+      <c r="C162">
+        <v>2020</v>
+      </c>
+      <c r="D162">
+        <v>324</v>
+      </c>
+      <c r="E162" t="s">
+        <v>10</v>
+      </c>
+      <c r="F162" t="s">
+        <v>19</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>38</v>
+      </c>
+      <c r="B163" s="2">
+        <v>44158</v>
+      </c>
+      <c r="C163">
+        <v>2020</v>
+      </c>
+      <c r="D163">
+        <v>328</v>
+      </c>
+      <c r="E163" t="s">
+        <v>10</v>
+      </c>
+      <c r="F163" t="s">
+        <v>19</v>
+      </c>
+      <c r="G163">
+        <v>3</v>
+      </c>
+      <c r="H163">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>38</v>
+      </c>
+      <c r="B164" s="2">
+        <v>44162</v>
+      </c>
+      <c r="C164">
+        <v>2020</v>
+      </c>
+      <c r="D164">
+        <v>332</v>
+      </c>
+      <c r="E164" t="s">
+        <v>10</v>
+      </c>
+      <c r="F164" t="s">
+        <v>19</v>
+      </c>
+      <c r="G164">
+        <v>7</v>
+      </c>
+      <c r="H164">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>38</v>
+      </c>
+      <c r="B165" s="2">
+        <v>44166</v>
+      </c>
+      <c r="C165">
+        <v>2020</v>
+      </c>
+      <c r="D165">
+        <v>336</v>
+      </c>
+      <c r="E165" t="s">
+        <v>10</v>
+      </c>
+      <c r="F165" t="s">
+        <v>19</v>
+      </c>
+      <c r="G165">
+        <v>10</v>
+      </c>
+      <c r="H165">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>38</v>
+      </c>
+      <c r="B166" s="2">
+        <v>44169</v>
+      </c>
+      <c r="C166">
+        <v>2020</v>
+      </c>
+      <c r="D166">
+        <v>339</v>
+      </c>
+      <c r="E166" t="s">
+        <v>10</v>
+      </c>
+      <c r="F166" t="s">
+        <v>19</v>
+      </c>
+      <c r="G166">
+        <v>11</v>
+      </c>
+      <c r="H166">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>38</v>
+      </c>
+      <c r="B167" s="2">
+        <v>44172</v>
+      </c>
+      <c r="C167">
+        <v>2020</v>
+      </c>
+      <c r="D167">
+        <v>342</v>
+      </c>
+      <c r="E167" t="s">
+        <v>10</v>
+      </c>
+      <c r="F167" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167">
+        <v>11</v>
+      </c>
+      <c r="H167">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>38</v>
+      </c>
+      <c r="B168" s="2">
+        <v>44175</v>
+      </c>
+      <c r="C168">
+        <v>2020</v>
+      </c>
+      <c r="D168">
+        <v>345</v>
+      </c>
+      <c r="E168" t="s">
+        <v>10</v>
+      </c>
+      <c r="F168" t="s">
+        <v>19</v>
+      </c>
+      <c r="G168">
+        <v>11</v>
+      </c>
+      <c r="H168">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>38</v>
+      </c>
+      <c r="B169" s="2">
+        <v>44176</v>
+      </c>
+      <c r="C169">
+        <v>2020</v>
+      </c>
+      <c r="D169">
+        <v>346</v>
+      </c>
+      <c r="E169" t="s">
+        <v>10</v>
+      </c>
+      <c r="F169" t="s">
+        <v>19</v>
+      </c>
+      <c r="G169">
+        <v>11</v>
+      </c>
+      <c r="H169">
+        <v>322</v>
+      </c>
+      <c r="I169" t="s">
+        <v>44</v>
+      </c>
+      <c r="J169">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>39</v>
+      </c>
+      <c r="B170" s="2">
+        <v>44508</v>
+      </c>
+      <c r="C170">
+        <v>2021</v>
+      </c>
+      <c r="D170">
+        <v>312</v>
+      </c>
+      <c r="E170" t="s">
+        <v>10</v>
+      </c>
+      <c r="F170" t="s">
+        <v>19</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>39</v>
+      </c>
+      <c r="B171" s="2">
+        <v>44509</v>
+      </c>
+      <c r="C171">
+        <v>2021</v>
+      </c>
+      <c r="D171">
+        <v>313</v>
+      </c>
+      <c r="E171" t="s">
+        <v>10</v>
+      </c>
+      <c r="F171" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>39</v>
+      </c>
+      <c r="B172" s="2">
+        <v>44512</v>
+      </c>
+      <c r="C172">
+        <v>2021</v>
+      </c>
+      <c r="D172">
+        <v>316</v>
+      </c>
+      <c r="E172" t="s">
+        <v>10</v>
+      </c>
+      <c r="F172" t="s">
+        <v>19</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>39</v>
+      </c>
+      <c r="B173" s="2">
+        <v>44516</v>
+      </c>
+      <c r="C173">
+        <v>2021</v>
+      </c>
+      <c r="D173">
+        <v>320</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" t="s">
+        <v>19</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>39</v>
+      </c>
+      <c r="B174" s="2">
+        <v>44519</v>
+      </c>
+      <c r="C174">
+        <v>2021</v>
+      </c>
+      <c r="D174">
+        <v>323</v>
+      </c>
+      <c r="E174" t="s">
+        <v>10</v>
+      </c>
+      <c r="F174" t="s">
+        <v>19</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>39</v>
+      </c>
+      <c r="B175" s="2">
+        <v>44523</v>
+      </c>
+      <c r="C175">
+        <v>2021</v>
+      </c>
+      <c r="D175">
+        <v>327</v>
+      </c>
+      <c r="E175" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175">
+        <v>7.5</v>
+      </c>
+      <c r="H175">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>39</v>
+      </c>
+      <c r="B176" s="2">
+        <v>44526</v>
+      </c>
+      <c r="C176">
+        <v>2021</v>
+      </c>
+      <c r="D176">
+        <v>330</v>
+      </c>
+      <c r="E176" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" t="s">
+        <v>19</v>
+      </c>
+      <c r="G176">
+        <v>14</v>
+      </c>
+      <c r="H176">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>39</v>
+      </c>
+      <c r="B177" s="2">
+        <v>44530</v>
+      </c>
+      <c r="C177">
+        <v>2021</v>
+      </c>
+      <c r="D177">
+        <v>334</v>
+      </c>
+      <c r="E177" t="s">
+        <v>10</v>
+      </c>
+      <c r="F177" t="s">
+        <v>19</v>
+      </c>
+      <c r="G177">
+        <v>19.5</v>
+      </c>
+      <c r="H177">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>39</v>
+      </c>
+      <c r="B178" s="2">
+        <v>44533</v>
+      </c>
+      <c r="C178">
+        <v>2021</v>
+      </c>
+      <c r="D178">
+        <v>337</v>
+      </c>
+      <c r="E178" t="s">
+        <v>10</v>
+      </c>
+      <c r="F178" t="s">
+        <v>19</v>
+      </c>
+      <c r="G178">
+        <v>20</v>
+      </c>
+      <c r="H178">
+        <v>323</v>
+      </c>
+      <c r="I178" t="s">
+        <v>44</v>
+      </c>
+      <c r="J178">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>40</v>
+      </c>
+      <c r="B179" s="2">
+        <v>44147</v>
+      </c>
+      <c r="C179">
+        <v>2020</v>
+      </c>
+      <c r="D179">
+        <v>317</v>
+      </c>
+      <c r="E179" t="s">
+        <v>10</v>
+      </c>
+      <c r="F179" t="s">
+        <v>19</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>40</v>
+      </c>
+      <c r="B180" s="2">
+        <v>44151</v>
+      </c>
+      <c r="C180">
+        <v>2020</v>
+      </c>
+      <c r="D180">
+        <v>321</v>
+      </c>
+      <c r="E180" t="s">
+        <v>10</v>
+      </c>
+      <c r="F180" t="s">
+        <v>19</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>40</v>
+      </c>
+      <c r="B181" s="2">
+        <v>44154</v>
+      </c>
+      <c r="C181">
+        <v>2020</v>
+      </c>
+      <c r="D181">
+        <v>324</v>
+      </c>
+      <c r="E181" t="s">
+        <v>10</v>
+      </c>
+      <c r="F181" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>40</v>
+      </c>
+      <c r="B182" s="2">
+        <v>44159</v>
+      </c>
+      <c r="C182">
+        <v>2020</v>
+      </c>
+      <c r="D182">
+        <v>329</v>
+      </c>
+      <c r="E182" t="s">
+        <v>10</v>
+      </c>
+      <c r="F182" t="s">
+        <v>19</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>40</v>
+      </c>
+      <c r="B183" s="2">
+        <v>44162</v>
+      </c>
+      <c r="C183">
+        <v>2020</v>
+      </c>
+      <c r="D183">
+        <v>332</v>
+      </c>
+      <c r="E183" t="s">
+        <v>10</v>
+      </c>
+      <c r="F183" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>40</v>
+      </c>
+      <c r="B184" s="2">
+        <v>44166</v>
+      </c>
+      <c r="C184">
+        <v>2020</v>
+      </c>
+      <c r="D184">
+        <v>336</v>
+      </c>
+      <c r="E184" t="s">
+        <v>10</v>
+      </c>
+      <c r="F184" t="s">
+        <v>19</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>40</v>
+      </c>
+      <c r="B185" s="2">
+        <v>44169</v>
+      </c>
+      <c r="C185">
+        <v>2020</v>
+      </c>
+      <c r="D185">
+        <v>339</v>
+      </c>
+      <c r="E185" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185">
+        <v>20</v>
+      </c>
+      <c r="H185">
+        <v>317</v>
+      </c>
       <c r="I185" t="s">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="J185">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB9C4B2-238F-4981-AB2F-079FB455457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4CF5DC-2D3E-41B3-8A5B-996FD1B9D1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BB" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="49">
   <si>
     <t>SimulationName</t>
   </si>
@@ -180,6 +180,12 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>TPHWControl1996_1999</t>
+  </si>
+  <si>
+    <t>1997-09-31</t>
+  </si>
 </sst>
 </file>
 
@@ -188,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -209,13 +215,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -245,13 +262,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,13 +578,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J252"/>
+  <dimension ref="A1:J256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.28515625" customWidth="1"/>
     <col min="2" max="2" width="39.7109375" customWidth="1"/>
     <col min="7" max="7" width="40.85546875" customWidth="1"/>
     <col min="8" max="8" width="29.140625" customWidth="1"/>
+    <col min="9" max="9" width="39.42578125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -800,7 +826,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I9">
         <v>275</v>
@@ -1014,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I17">
         <v>271</v>
@@ -1228,7 +1254,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I25">
         <v>270</v>
@@ -1624,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="H40">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I40">
         <v>275</v>
@@ -1786,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="H46">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I46">
         <v>262</v>
@@ -1948,7 +1974,7 @@
         <v>6</v>
       </c>
       <c r="H52">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I52">
         <v>266</v>
@@ -2162,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="H60">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I60">
         <v>252</v>
@@ -2376,7 +2402,7 @@
         <v>6</v>
       </c>
       <c r="H68">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I68">
         <v>253</v>
@@ -2668,7 +2694,7 @@
         <v>5</v>
       </c>
       <c r="H79">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I79">
         <v>271</v>
@@ -2986,7 +3012,7 @@
         <v>5</v>
       </c>
       <c r="H91">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I91">
         <v>270</v>
@@ -3304,7 +3330,7 @@
         <v>7</v>
       </c>
       <c r="H103">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I103">
         <v>284</v>
@@ -3492,7 +3518,7 @@
         <v>5</v>
       </c>
       <c r="H110">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I110">
         <v>289</v>
@@ -3732,7 +3758,7 @@
         <v>7</v>
       </c>
       <c r="H119">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I119">
         <v>272</v>
@@ -4050,7 +4076,7 @@
         <v>5</v>
       </c>
       <c r="H131">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I131">
         <v>277</v>
@@ -4264,7 +4290,7 @@
         <v>5</v>
       </c>
       <c r="H139">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I139">
         <v>265</v>
@@ -4686,7 +4712,7 @@
         <v>4</v>
       </c>
       <c r="H155">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I155">
         <v>275</v>
@@ -5212,7 +5238,7 @@
         <v>7</v>
       </c>
       <c r="H175">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I175">
         <v>277</v>
@@ -5634,7 +5660,7 @@
         <v>3</v>
       </c>
       <c r="H191">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I191">
         <v>293</v>
@@ -5952,7 +5978,7 @@
         <v>3</v>
       </c>
       <c r="H203">
-        <v>0.35</v>
+        <v>0.32</v>
       </c>
       <c r="I203">
         <v>289</v>
@@ -6478,7 +6504,7 @@
         <v>5</v>
       </c>
       <c r="H223">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I223">
         <v>271</v>
@@ -6874,7 +6900,7 @@
         <v>7</v>
       </c>
       <c r="H238">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I238">
         <v>273</v>
@@ -7244,12 +7270,128 @@
         <v>6</v>
       </c>
       <c r="H252">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="I252">
         <v>269</v>
       </c>
       <c r="J252" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B253" s="2">
+        <v>35329</v>
+      </c>
+      <c r="C253" s="5">
+        <v>1996</v>
+      </c>
+      <c r="D253" s="5"/>
+      <c r="E253" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G253" s="5"/>
+      <c r="H253" s="5">
+        <v>0.46</v>
+      </c>
+      <c r="I253" s="5">
+        <f>DATE(C253,9,16)-DATE(C253,1,0)</f>
+        <v>260</v>
+      </c>
+      <c r="J253" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C254" s="5">
+        <v>1997</v>
+      </c>
+      <c r="D254" s="5"/>
+      <c r="E254" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F254" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G254" s="5"/>
+      <c r="H254" s="5">
+        <v>0.44</v>
+      </c>
+      <c r="I254" s="5">
+        <f>DATE(C254,9,16)-DATE(C254,1,0)</f>
+        <v>259</v>
+      </c>
+      <c r="J254" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B255" s="2">
+        <v>36059</v>
+      </c>
+      <c r="C255" s="5">
+        <v>1998</v>
+      </c>
+      <c r="D255" s="5"/>
+      <c r="E255" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G255" s="5"/>
+      <c r="H255" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I255" s="5">
+        <f>DATE(C255,9,21)-DATE(C255,1,0)</f>
+        <v>264</v>
+      </c>
+      <c r="J255" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B256" s="2">
+        <v>36438</v>
+      </c>
+      <c r="C256" s="5">
+        <v>1999</v>
+      </c>
+      <c r="D256" s="5"/>
+      <c r="E256" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F256" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G256" s="5"/>
+      <c r="H256" s="5">
+        <v>0.45</v>
+      </c>
+      <c r="I256" s="5">
+        <f>DATE(C256,9,12)-DATE(C256,1,0)</f>
+        <v>255</v>
+      </c>
+      <c r="J256" s="5" t="s">
         <v>12</v>
       </c>
     </row>

--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4CF5DC-2D3E-41B3-8A5B-996FD1B9D1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A40F87-1C43-48BF-9170-12917ACFF8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BB" sheetId="1" r:id="rId1"/>
@@ -206,6 +206,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -12303,7 +12304,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="2" max="3" width="22.140625" customWidth="1"/>
     <col min="7" max="7" width="37.5703125" customWidth="1"/>
     <col min="8" max="8" width="43.7109375" customWidth="1"/>
     <col min="9" max="9" width="39" customWidth="1"/>
@@ -12721,7 +12722,7 @@
         <v>44</v>
       </c>
       <c r="J15">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -12938,7 +12939,7 @@
         <v>44</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">

--- a/Prototypes/KiwiFruit/ObservAll.xlsx
+++ b/Prototypes/KiwiFruit/ObservAll.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub repos\APSIMX\Prototypes\KiwiFruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9A40F87-1C43-48BF-9170-12917ACFF8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACDE5A7-77ED-4825-8E10-DB0F81880DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BB" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="50">
   <si>
     <t>SimulationName</t>
   </si>
@@ -186,13 +186,17 @@
   <si>
     <t>1997-09-31</t>
   </si>
+  <si>
+    <t>HWTP2005Control</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -263,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -277,6 +281,8 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,17 +586,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J256"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.28515625" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
-    <col min="7" max="7" width="40.85546875" customWidth="1"/>
-    <col min="8" max="8" width="29.140625" customWidth="1"/>
-    <col min="9" max="9" width="39.42578125" customWidth="1"/>
+    <col min="1" max="1" width="56.33203125" customWidth="1"/>
+    <col min="2" max="2" width="39.6640625" customWidth="1"/>
+    <col min="7" max="7" width="40.88671875" customWidth="1"/>
+    <col min="8" max="8" width="29.109375" customWidth="1"/>
+    <col min="9" max="9" width="39.44140625" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,7 +628,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -648,7 +654,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -674,7 +680,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -700,7 +706,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -726,7 +732,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -752,7 +758,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -778,7 +784,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -804,7 +810,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -836,7 +842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -862,7 +868,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -888,7 +894,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -914,7 +920,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -940,7 +946,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -966,7 +972,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -992,7 +998,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1018,7 +1024,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1076,7 +1082,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1102,7 +1108,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1154,7 +1160,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -1206,7 +1212,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1232,7 +1238,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -1264,7 +1270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -1290,7 +1296,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -1342,7 +1348,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -1368,7 +1374,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -1394,7 +1400,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -1420,7 +1426,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -1446,7 +1452,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1478,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>17</v>
       </c>
@@ -1498,7 +1504,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>17</v>
       </c>
@@ -1524,7 +1530,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -1550,7 +1556,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>17</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>17</v>
       </c>
@@ -1602,7 +1608,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>17</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>17</v>
       </c>
@@ -1660,7 +1666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>20</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>20</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>20</v>
       </c>
@@ -1738,7 +1744,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -1790,7 +1796,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>20</v>
       </c>
@@ -1822,7 +1828,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -1848,7 +1854,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>21</v>
       </c>
@@ -1874,7 +1880,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>21</v>
       </c>
@@ -1900,7 +1906,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -1926,7 +1932,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>21</v>
       </c>
@@ -1952,7 +1958,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>21</v>
       </c>
@@ -1984,7 +1990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -2010,7 +2016,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -2036,7 +2042,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -2062,7 +2068,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -2088,7 +2094,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -2140,7 +2146,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -2166,7 +2172,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -2198,7 +2204,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>23</v>
       </c>
@@ -2224,7 +2230,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>23</v>
       </c>
@@ -2250,7 +2256,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>23</v>
       </c>
@@ -2276,7 +2282,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>23</v>
       </c>
@@ -2302,7 +2308,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>23</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>23</v>
       </c>
@@ -2354,7 +2360,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>23</v>
       </c>
@@ -2380,7 +2386,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>23</v>
       </c>
@@ -2412,7 +2418,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>24</v>
       </c>
@@ -2438,7 +2444,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>24</v>
       </c>
@@ -2464,7 +2470,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>24</v>
       </c>
@@ -2490,7 +2496,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>24</v>
       </c>
@@ -2516,7 +2522,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>24</v>
       </c>
@@ -2542,7 +2548,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>24</v>
       </c>
@@ -2568,7 +2574,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>24</v>
       </c>
@@ -2594,7 +2600,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>24</v>
       </c>
@@ -2620,7 +2626,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>24</v>
       </c>
@@ -2646,7 +2652,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>24</v>
       </c>
@@ -2672,7 +2678,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>24</v>
       </c>
@@ -2704,7 +2710,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>25</v>
       </c>
@@ -2730,7 +2736,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>25</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>25</v>
       </c>
@@ -2782,7 +2788,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -2808,7 +2814,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>25</v>
       </c>
@@ -2834,7 +2840,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>25</v>
       </c>
@@ -2860,7 +2866,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>25</v>
       </c>
@@ -2886,7 +2892,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>25</v>
       </c>
@@ -2912,7 +2918,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>25</v>
       </c>
@@ -2938,7 +2944,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>25</v>
       </c>
@@ -2964,7 +2970,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>25</v>
       </c>
@@ -2990,7 +2996,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>25</v>
       </c>
@@ -3022,7 +3028,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>26</v>
       </c>
@@ -3048,7 +3054,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>26</v>
       </c>
@@ -3074,7 +3080,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3106,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -3126,7 +3132,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -3152,7 +3158,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -3178,7 +3184,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>26</v>
       </c>
@@ -3204,7 +3210,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>26</v>
       </c>
@@ -3230,7 +3236,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>26</v>
       </c>
@@ -3256,7 +3262,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>26</v>
       </c>
@@ -3282,7 +3288,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>26</v>
       </c>
@@ -3308,7 +3314,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>26</v>
       </c>
@@ -3340,7 +3346,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>27</v>
       </c>
@@ -3366,7 +3372,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>27</v>
       </c>
@@ -3392,7 +3398,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>27</v>
       </c>
@@ -3418,7 +3424,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>27</v>
       </c>
@@ -3444,7 +3450,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>27</v>
       </c>
@@ -3470,7 +3476,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>27</v>
       </c>
@@ -3496,7 +3502,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>27</v>
       </c>
@@ -3528,7 +3534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>28</v>
       </c>
@@ -3554,7 +3560,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>28</v>
       </c>
@@ -3580,7 +3586,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>28</v>
       </c>
@@ -3606,7 +3612,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>28</v>
       </c>
@@ -3632,7 +3638,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>28</v>
       </c>
@@ -3658,7 +3664,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>28</v>
       </c>
@@ -3684,7 +3690,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>28</v>
       </c>
@@ -3710,7 +3716,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>28</v>
       </c>
@@ -3736,7 +3742,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>28</v>
       </c>
@@ -3768,7 +3774,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -3794,7 +3800,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -3820,7 +3826,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -3846,7 +3852,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -3872,7 +3878,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -3898,7 +3904,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>30</v>
       </c>
@@ -3924,7 +3930,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>30</v>
       </c>
@@ -3950,7 +3956,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>30</v>
       </c>
@@ -3976,7 +3982,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -4002,7 +4008,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -4028,7 +4034,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>30</v>
       </c>
@@ -4054,7 +4060,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>30</v>
       </c>
@@ -4086,7 +4092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>31</v>
       </c>
@@ -4112,7 +4118,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>31</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>31</v>
       </c>
@@ -4164,7 +4170,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>31</v>
       </c>
@@ -4190,7 +4196,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>31</v>
       </c>
@@ -4216,7 +4222,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>31</v>
       </c>
@@ -4242,7 +4248,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>31</v>
       </c>
@@ -4268,7 +4274,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>31</v>
       </c>
@@ -4300,7 +4306,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>32</v>
       </c>
@@ -4326,7 +4332,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>32</v>
       </c>
@@ -4352,7 +4358,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>32</v>
       </c>
@@ -4378,7 +4384,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>32</v>
       </c>
@@ -4404,7 +4410,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>32</v>
       </c>
@@ -4430,7 +4436,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>32</v>
       </c>
@@ -4456,7 +4462,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>32</v>
       </c>
@@ -4482,7 +4488,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>32</v>
       </c>
@@ -4508,7 +4514,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>32</v>
       </c>
@@ -4534,7 +4540,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>32</v>
       </c>
@@ -4560,7 +4566,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>32</v>
       </c>
@@ -4586,7 +4592,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>32</v>
       </c>
@@ -4612,7 +4618,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>32</v>
       </c>
@@ -4638,7 +4644,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>32</v>
       </c>
@@ -4664,7 +4670,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>32</v>
       </c>
@@ -4690,7 +4696,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>32</v>
       </c>
@@ -4722,7 +4728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>34</v>
       </c>
@@ -4748,7 +4754,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>34</v>
       </c>
@@ -4774,7 +4780,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>34</v>
       </c>
@@ -4800,7 +4806,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>34</v>
       </c>
@@ -4826,7 +4832,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>34</v>
       </c>
@@ -4852,7 +4858,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>34</v>
       </c>
@@ -4878,7 +4884,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>34</v>
       </c>
@@ -4904,7 +4910,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>34</v>
       </c>
@@ -4930,7 +4936,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>34</v>
       </c>
@@ -4956,7 +4962,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>34</v>
       </c>
@@ -4982,7 +4988,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>34</v>
       </c>
@@ -5008,7 +5014,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>34</v>
       </c>
@@ -5034,7 +5040,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>34</v>
       </c>
@@ -5060,7 +5066,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>34</v>
       </c>
@@ -5086,7 +5092,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>34</v>
       </c>
@@ -5112,7 +5118,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>34</v>
       </c>
@@ -5138,7 +5144,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>34</v>
       </c>
@@ -5164,7 +5170,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>34</v>
       </c>
@@ -5190,7 +5196,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>34</v>
       </c>
@@ -5216,7 +5222,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>34</v>
       </c>
@@ -5248,7 +5254,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>36</v>
       </c>
@@ -5274,7 +5280,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>36</v>
       </c>
@@ -5300,7 +5306,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>36</v>
       </c>
@@ -5326,7 +5332,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>36</v>
       </c>
@@ -5352,7 +5358,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>36</v>
       </c>
@@ -5378,7 +5384,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>36</v>
       </c>
@@ -5404,7 +5410,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>36</v>
       </c>
@@ -5430,7 +5436,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>36</v>
       </c>
@@ -5456,7 +5462,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>36</v>
       </c>
@@ -5482,7 +5488,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>36</v>
       </c>
@@ -5508,7 +5514,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>36</v>
       </c>
@@ -5534,7 +5540,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>36</v>
       </c>
@@ -5560,7 +5566,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>36</v>
       </c>
@@ -5586,7 +5592,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>36</v>
       </c>
@@ -5612,7 +5618,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>36</v>
       </c>
@@ -5638,7 +5644,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>36</v>
       </c>
@@ -5670,7 +5676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>37</v>
       </c>
@@ -5696,7 +5702,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>37</v>
       </c>
@@ -5722,7 +5728,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>37</v>
       </c>
@@ -5748,7 +5754,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>37</v>
       </c>
@@ -5774,7 +5780,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>37</v>
       </c>
@@ -5800,7 +5806,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>37</v>
       </c>
@@ -5826,7 +5832,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>37</v>
       </c>
@@ -5852,7 +5858,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>37</v>
       </c>
@@ -5878,7 +5884,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>37</v>
       </c>
@@ -5904,7 +5910,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>37</v>
       </c>
@@ -5930,7 +5936,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>37</v>
       </c>
@@ -5956,7 +5962,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>37</v>
       </c>
@@ -5988,7 +5994,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>38</v>
       </c>
@@ -6014,7 +6020,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>38</v>
       </c>
@@ -6040,7 +6046,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>38</v>
       </c>
@@ -6066,7 +6072,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>38</v>
       </c>
@@ -6092,7 +6098,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>38</v>
       </c>
@@ -6118,7 +6124,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>38</v>
       </c>
@@ -6144,7 +6150,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>38</v>
       </c>
@@ -6170,7 +6176,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>38</v>
       </c>
@@ -6196,7 +6202,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>38</v>
       </c>
@@ -6222,7 +6228,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>38</v>
       </c>
@@ -6248,7 +6254,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>38</v>
       </c>
@@ -6274,7 +6280,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>38</v>
       </c>
@@ -6300,7 +6306,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>38</v>
       </c>
@@ -6326,7 +6332,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>38</v>
       </c>
@@ -6352,7 +6358,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>38</v>
       </c>
@@ -6378,7 +6384,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>38</v>
       </c>
@@ -6404,7 +6410,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>38</v>
       </c>
@@ -6430,7 +6436,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>38</v>
       </c>
@@ -6456,7 +6462,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>38</v>
       </c>
@@ -6482,7 +6488,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>38</v>
       </c>
@@ -6514,7 +6520,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>39</v>
       </c>
@@ -6540,7 +6546,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>39</v>
       </c>
@@ -6566,7 +6572,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>39</v>
       </c>
@@ -6592,7 +6598,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>39</v>
       </c>
@@ -6618,7 +6624,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>39</v>
       </c>
@@ -6644,7 +6650,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>39</v>
       </c>
@@ -6670,7 +6676,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>39</v>
       </c>
@@ -6696,7 +6702,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>39</v>
       </c>
@@ -6722,7 +6728,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>39</v>
       </c>
@@ -6748,7 +6754,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>39</v>
       </c>
@@ -6774,7 +6780,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>39</v>
       </c>
@@ -6800,7 +6806,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -6826,7 +6832,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>39</v>
       </c>
@@ -6852,7 +6858,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>39</v>
       </c>
@@ -6878,7 +6884,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -6910,7 +6916,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>40</v>
       </c>
@@ -6936,7 +6942,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>40</v>
       </c>
@@ -6962,7 +6968,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>40</v>
       </c>
@@ -6988,7 +6994,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>40</v>
       </c>
@@ -7014,7 +7020,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>40</v>
       </c>
@@ -7040,7 +7046,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>40</v>
       </c>
@@ -7066,7 +7072,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>40</v>
       </c>
@@ -7092,7 +7098,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>40</v>
       </c>
@@ -7118,7 +7124,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>40</v>
       </c>
@@ -7144,7 +7150,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>40</v>
       </c>
@@ -7170,7 +7176,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>40</v>
       </c>
@@ -7196,7 +7202,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>40</v>
       </c>
@@ -7222,7 +7228,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>40</v>
       </c>
@@ -7248,7 +7254,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>40</v>
       </c>
@@ -7280,7 +7286,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="4" t="s">
         <v>47</v>
       </c>
@@ -7309,7 +7315,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="4" t="s">
         <v>47</v>
       </c>
@@ -7338,7 +7344,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="4" t="s">
         <v>47</v>
       </c>
@@ -7367,7 +7373,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="4" t="s">
         <v>47</v>
       </c>
@@ -7404,17 +7410,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I186"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="7" max="7" width="37.5703125" customWidth="1"/>
-    <col min="8" max="8" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.44140625" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" customWidth="1"/>
+    <col min="7" max="7" width="37.5546875" customWidth="1"/>
+    <col min="8" max="8" width="43.6640625" customWidth="1"/>
     <col min="9" max="9" width="39" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7443,7 +7449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -7472,7 +7478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -7498,7 +7504,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -7524,7 +7530,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -7550,7 +7556,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -7576,7 +7582,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -7602,7 +7608,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -7631,7 +7637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -7657,7 +7663,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -7683,7 +7689,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -7709,7 +7715,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -7735,7 +7741,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -7761,7 +7767,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -7787,7 +7793,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -7813,7 +7819,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -7842,7 +7848,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -7868,7 +7874,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -7894,7 +7900,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -7920,7 +7926,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -7946,7 +7952,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -7972,7 +7978,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -7998,7 +8004,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -8024,7 +8030,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -8053,7 +8059,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -8079,7 +8085,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -8105,7 +8111,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -8131,7 +8137,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -8157,7 +8163,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -8183,7 +8189,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -8209,7 +8215,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -8235,7 +8241,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -8264,7 +8270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -8290,7 +8296,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -8316,7 +8322,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -8342,7 +8348,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -8371,7 +8377,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -8397,7 +8403,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -8423,7 +8429,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -8449,7 +8455,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -8475,7 +8481,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -8504,7 +8510,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -8530,7 +8536,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -8556,7 +8562,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -8582,7 +8588,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -8611,7 +8617,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -8637,7 +8643,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -8663,7 +8669,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -8689,7 +8695,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -8718,7 +8724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -8744,7 +8750,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -8770,7 +8776,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -8796,7 +8802,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -8819,13 +8825,13 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I53" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -8848,10 +8854,10 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -8874,10 +8880,10 @@
         <v>0.5</v>
       </c>
       <c r="H55">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -8900,10 +8906,10 @@
         <v>5</v>
       </c>
       <c r="H56">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -8926,10 +8932,10 @@
         <v>9</v>
       </c>
       <c r="H57">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -8952,10 +8958,10 @@
         <v>12</v>
       </c>
       <c r="H58">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -8984,7 +8990,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -9010,7 +9016,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -9036,7 +9042,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -9062,7 +9068,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -9091,7 +9097,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>27</v>
       </c>
@@ -9117,7 +9123,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>27</v>
       </c>
@@ -9143,7 +9149,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -9169,7 +9175,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>27</v>
       </c>
@@ -9195,7 +9201,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>27</v>
       </c>
@@ -9221,7 +9227,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -9250,7 +9256,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -9276,7 +9282,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -9302,7 +9308,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -9328,7 +9334,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -9354,7 +9360,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -9380,7 +9386,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -9406,7 +9412,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>30</v>
       </c>
@@ -9435,7 +9441,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>30</v>
       </c>
@@ -9461,7 +9467,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>30</v>
       </c>
@@ -9487,7 +9493,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -9513,7 +9519,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -9539,7 +9545,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -9565,7 +9571,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -9591,7 +9597,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -9617,7 +9623,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -9643,7 +9649,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -9669,7 +9675,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>31</v>
       </c>
@@ -9692,13 +9698,13 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I86" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -9721,10 +9727,10 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>31</v>
       </c>
@@ -9747,10 +9753,10 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -9773,10 +9779,10 @@
         <v>1</v>
       </c>
       <c r="H89">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -9799,10 +9805,10 @@
         <v>8</v>
       </c>
       <c r="H90">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -9825,10 +9831,10 @@
         <v>10.5</v>
       </c>
       <c r="H91">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -9851,10 +9857,10 @@
         <v>10.5</v>
       </c>
       <c r="H92">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -9877,13 +9883,13 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I93" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -9906,10 +9912,10 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -9932,10 +9938,10 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -9958,10 +9964,10 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>32</v>
       </c>
@@ -9984,10 +9990,10 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>32</v>
       </c>
@@ -10010,10 +10016,10 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -10036,10 +10042,10 @@
         <v>0</v>
       </c>
       <c r="H99">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>32</v>
       </c>
@@ -10062,10 +10068,10 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -10088,10 +10094,10 @@
         <v>0</v>
       </c>
       <c r="H101">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -10114,10 +10120,10 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -10140,10 +10146,10 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -10166,10 +10172,10 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -10192,10 +10198,10 @@
         <v>2.5</v>
       </c>
       <c r="H105">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>32</v>
       </c>
@@ -10218,10 +10224,10 @@
         <v>3.5</v>
       </c>
       <c r="H106">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>32</v>
       </c>
@@ -10244,10 +10250,10 @@
         <v>3.5</v>
       </c>
       <c r="H107">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>32</v>
       </c>
@@ -10270,10 +10276,10 @@
         <v>6</v>
       </c>
       <c r="H108">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -10296,10 +10302,10 @@
         <v>6</v>
       </c>
       <c r="H109">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -10319,13 +10325,13 @@
         <v>33</v>
       </c>
       <c r="G110">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H110">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -10345,13 +10351,13 @@
         <v>33</v>
       </c>
       <c r="G111">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H111">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -10371,13 +10377,13 @@
         <v>33</v>
       </c>
       <c r="G112">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H112">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -10400,13 +10406,13 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I113" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>34</v>
       </c>
@@ -10429,10 +10435,10 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>34</v>
       </c>
@@ -10455,10 +10461,10 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -10481,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>34</v>
       </c>
@@ -10504,13 +10510,13 @@
         <v>35</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>34</v>
       </c>
@@ -10530,13 +10536,13 @@
         <v>35</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -10556,13 +10562,13 @@
         <v>35</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H119">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -10582,13 +10588,13 @@
         <v>35</v>
       </c>
       <c r="G120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H120">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>34</v>
       </c>
@@ -10608,13 +10614,13 @@
         <v>35</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H121">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -10634,13 +10640,13 @@
         <v>35</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -10660,13 +10666,13 @@
         <v>35</v>
       </c>
       <c r="G123">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H123">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>34</v>
       </c>
@@ -10686,13 +10692,13 @@
         <v>35</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H124">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -10715,13 +10721,13 @@
         <v>0</v>
       </c>
       <c r="H125">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="I125" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>36</v>
       </c>
@@ -10744,10 +10750,10 @@
         <v>0</v>
       </c>
       <c r="H126">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>36</v>
       </c>
@@ -10770,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="H127">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>36</v>
       </c>
@@ -10796,10 +10802,10 @@
         <v>0</v>
       </c>
       <c r="H128">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -10822,10 +10828,10 @@
         <v>0</v>
       </c>
       <c r="H129">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>36</v>
       </c>
@@ -10848,10 +10854,10 @@
         <v>0</v>
       </c>
       <c r="H130">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>36</v>
       </c>
@@ -10874,10 +10880,10 @@
         <v>0</v>
       </c>
       <c r="H131">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>36</v>
       </c>
@@ -10900,10 +10906,10 @@
         <v>0</v>
       </c>
       <c r="H132">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>36</v>
       </c>
@@ -10926,10 +10932,10 @@
         <v>0</v>
       </c>
       <c r="H133">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>36</v>
       </c>
@@ -10952,10 +10958,10 @@
         <v>0</v>
       </c>
       <c r="H134">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -10975,13 +10981,13 @@
         <v>19</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>36</v>
       </c>
@@ -11001,13 +11007,13 @@
         <v>19</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H136">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>36</v>
       </c>
@@ -11027,13 +11033,13 @@
         <v>19</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H137">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>36</v>
       </c>
@@ -11053,13 +11059,13 @@
         <v>19</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H138">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>36</v>
       </c>
@@ -11079,13 +11085,13 @@
         <v>19</v>
       </c>
       <c r="G139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H139">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>36</v>
       </c>
@@ -11105,13 +11111,13 @@
         <v>19</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H140">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -11134,13 +11140,13 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="I141" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -11163,10 +11169,10 @@
         <v>0</v>
       </c>
       <c r="H142">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -11189,10 +11195,10 @@
         <v>0</v>
       </c>
       <c r="H143">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -11215,10 +11221,10 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>37</v>
       </c>
@@ -11241,10 +11247,10 @@
         <v>0</v>
       </c>
       <c r="H145">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -11267,10 +11273,10 @@
         <v>0</v>
       </c>
       <c r="H146">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>37</v>
       </c>
@@ -11293,10 +11299,10 @@
         <v>0</v>
       </c>
       <c r="H147">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>37</v>
       </c>
@@ -11316,13 +11322,13 @@
         <v>35</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -11342,13 +11348,13 @@
         <v>35</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H149">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -11368,13 +11374,13 @@
         <v>35</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H150">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -11394,13 +11400,13 @@
         <v>35</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H151">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -11420,13 +11426,13 @@
         <v>35</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H152">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -11446,13 +11452,13 @@
         <v>35</v>
       </c>
       <c r="G153">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H153">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -11472,13 +11478,13 @@
         <v>35</v>
       </c>
       <c r="G154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H154">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -11498,13 +11504,13 @@
         <v>35</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H155">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>37</v>
       </c>
@@ -11524,13 +11530,13 @@
         <v>35</v>
       </c>
       <c r="G156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H156">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>38</v>
       </c>
@@ -11559,7 +11565,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>38</v>
       </c>
@@ -11585,7 +11591,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>38</v>
       </c>
@@ -11611,7 +11617,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>38</v>
       </c>
@@ -11637,7 +11643,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>38</v>
       </c>
@@ -11663,7 +11669,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>38</v>
       </c>
@@ -11689,7 +11695,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>38</v>
       </c>
@@ -11715,7 +11721,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>38</v>
       </c>
@@ -11741,7 +11747,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>38</v>
       </c>
@@ -11767,7 +11773,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>38</v>
       </c>
@@ -11793,7 +11799,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>38</v>
       </c>
@@ -11819,7 +11825,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -11845,7 +11851,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>38</v>
       </c>
@@ -11871,7 +11877,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -11900,7 +11906,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -11926,7 +11932,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -11952,7 +11958,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -11978,7 +11984,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -12004,7 +12010,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -12030,7 +12036,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -12056,7 +12062,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -12082,7 +12088,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -12108,7 +12114,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -12137,7 +12143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -12163,7 +12169,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -12189,7 +12195,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -12215,7 +12221,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -12241,7 +12247,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -12267,7 +12273,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>40</v>
       </c>
@@ -12291,6 +12297,30 @@
       </c>
       <c r="H185">
         <v>317</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A186" t="s">
+        <v>49</v>
+      </c>
+      <c r="B186" s="7">
+        <v>38676</v>
+      </c>
+      <c r="C186">
+        <v>2005</v>
+      </c>
+      <c r="E186" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" t="s">
+        <v>19</v>
+      </c>
+      <c r="H186" s="8">
+        <f>B186 - DATE(YEAR(B186),1,0)</f>
+        <v>324</v>
+      </c>
+      <c r="I186" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -12301,17 +12331,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A5082DE-7F0F-42DB-B242-7E2A52480CF2}">
   <dimension ref="A1:J185"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="3" width="22.140625" customWidth="1"/>
-    <col min="7" max="7" width="37.5703125" customWidth="1"/>
-    <col min="8" max="8" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.44140625" customWidth="1"/>
+    <col min="2" max="3" width="22.109375" customWidth="1"/>
+    <col min="7" max="7" width="37.5546875" customWidth="1"/>
+    <col min="8" max="8" width="43.6640625" customWidth="1"/>
     <col min="9" max="9" width="39" customWidth="1"/>
-    <col min="10" max="10" width="33.7109375" customWidth="1"/>
+    <col min="10" max="10" width="33.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12343,7 +12373,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -12372,7 +12402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -12398,7 +12428,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -12424,7 +12454,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -12450,7 +12480,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -12476,7 +12506,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -12508,7 +12538,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -12537,7 +12567,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -12563,7 +12593,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -12589,7 +12619,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -12615,7 +12645,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -12641,7 +12671,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -12667,7 +12697,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -12693,7 +12723,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -12725,7 +12755,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -12754,7 +12784,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -12780,7 +12810,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -12806,7 +12836,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -12832,7 +12862,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -12858,7 +12888,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -12884,7 +12914,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -12910,7 +12940,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -12942,7 +12972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -12971,7 +13001,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -12997,7 +13027,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>17</v>
       </c>
@@ -13023,7 +13053,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -13049,7 +13079,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>17</v>
       </c>
@@ -13075,7 +13105,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>17</v>
       </c>
@@ -13101,7 +13131,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -13127,7 +13157,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>17</v>
       </c>
@@ -13159,7 +13189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>20</v>
       </c>
@@ -13188,7 +13218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -13214,7 +13244,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>20</v>
       </c>
@@ -13240,7 +13270,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>20</v>
       </c>
@@ -13272,7 +13302,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -13301,7 +13331,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -13327,7 +13357,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -13353,7 +13383,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -13379,7 +13409,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -13411,7 +13441,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -13440,7 +13470,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -13466,7 +13496,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -13492,7 +13522,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -13524,7 +13554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -13553,7 +13583,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -13579,7 +13609,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -13605,7 +13635,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>23</v>
       </c>
@@ -13637,7 +13667,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>24</v>
       </c>
@@ -13666,7 +13696,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>24</v>
       </c>
@@ -13692,7 +13722,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>24</v>
       </c>
@@ -13718,7 +13748,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -13750,7 +13780,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -13773,13 +13803,13 @@
         <v>0</v>
       </c>
       <c r="H53">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I53" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>25</v>
       </c>
@@ -13802,10 +13832,10 @@
         <v>0</v>
       </c>
       <c r="H54">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>25</v>
       </c>
@@ -13828,10 +13858,10 @@
         <v>0.5</v>
       </c>
       <c r="H55">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>25</v>
       </c>
@@ -13854,10 +13884,10 @@
         <v>5</v>
       </c>
       <c r="H56">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>25</v>
       </c>
@@ -13880,10 +13910,10 @@
         <v>9</v>
       </c>
       <c r="H57">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>25</v>
       </c>
@@ -13906,7 +13936,7 @@
         <v>12</v>
       </c>
       <c r="H58">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="I58" t="s">
         <v>44</v>
@@ -13915,7 +13945,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>26</v>
       </c>
@@ -13944,7 +13974,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>26</v>
       </c>
@@ -13970,7 +14000,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -13996,7 +14026,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>26</v>
       </c>
@@ -14028,7 +14058,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>27</v>
       </c>
@@ -14057,7 +14087,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>27</v>
       </c>
@@ -14083,7 +14113,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>27</v>
       </c>
@@ -14109,7 +14139,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -14135,7 +14165,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>27</v>
       </c>
@@ -14161,7 +14191,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>27</v>
       </c>
@@ -14193,7 +14223,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -14222,7 +14252,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>28</v>
       </c>
@@ -14248,7 +14278,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>28</v>
       </c>
@@ -14274,7 +14304,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>28</v>
       </c>
@@ -14300,7 +14330,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>28</v>
       </c>
@@ -14326,7 +14356,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>28</v>
       </c>
@@ -14352,7 +14382,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>28</v>
       </c>
@@ -14384,7 +14414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>30</v>
       </c>
@@ -14413,7 +14443,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>30</v>
       </c>
@@ -14439,7 +14469,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>30</v>
       </c>
@@ -14465,7 +14495,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -14491,7 +14521,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -14517,7 +14547,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -14543,7 +14573,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -14569,7 +14599,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -14595,7 +14625,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -14621,7 +14651,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -14653,7 +14683,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>31</v>
       </c>
@@ -14676,13 +14706,13 @@
         <v>0</v>
       </c>
       <c r="H86">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I86" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>31</v>
       </c>
@@ -14705,10 +14735,10 @@
         <v>0</v>
       </c>
       <c r="H87">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>31</v>
       </c>
@@ -14731,10 +14761,10 @@
         <v>0</v>
       </c>
       <c r="H88">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -14757,10 +14787,10 @@
         <v>1</v>
       </c>
       <c r="H89">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>31</v>
       </c>
@@ -14783,10 +14813,10 @@
         <v>8</v>
       </c>
       <c r="H90">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>31</v>
       </c>
@@ -14809,10 +14839,10 @@
         <v>10.5</v>
       </c>
       <c r="H91">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>31</v>
       </c>
@@ -14835,7 +14865,7 @@
         <v>10.5</v>
       </c>
       <c r="H92">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="I92" t="s">
         <v>44</v>
@@ -14844,7 +14874,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -14867,13 +14897,13 @@
         <v>0</v>
       </c>
       <c r="H93">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I93" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -14896,10 +14926,10 @@
         <v>0</v>
       </c>
       <c r="H94">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -14922,10 +14952,10 @@
         <v>0</v>
       </c>
       <c r="H95">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -14948,10 +14978,10 @@
         <v>0</v>
       </c>
       <c r="H96">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>32</v>
       </c>
@@ -14974,10 +15004,10 @@
         <v>0</v>
       </c>
       <c r="H97">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>32</v>
       </c>
@@ -15000,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="H98">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -15026,10 +15056,10 @@
         <v>0</v>
       </c>
       <c r="H99">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>32</v>
       </c>
@@ -15052,10 +15082,10 @@
         <v>0</v>
       </c>
       <c r="H100">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -15078,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="H101">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -15104,10 +15134,10 @@
         <v>0</v>
       </c>
       <c r="H102">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -15130,10 +15160,10 @@
         <v>0</v>
       </c>
       <c r="H103">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -15156,10 +15186,10 @@
         <v>0</v>
       </c>
       <c r="H104">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -15182,10 +15212,10 @@
         <v>2.5</v>
       </c>
       <c r="H105">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>32</v>
       </c>
@@ -15208,10 +15238,10 @@
         <v>3.5</v>
       </c>
       <c r="H106">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>32</v>
       </c>
@@ -15234,10 +15264,10 @@
         <v>3.5</v>
       </c>
       <c r="H107">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>32</v>
       </c>
@@ -15260,10 +15290,10 @@
         <v>6</v>
       </c>
       <c r="H108">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -15286,10 +15316,10 @@
         <v>6</v>
       </c>
       <c r="H109">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -15309,13 +15339,13 @@
         <v>33</v>
       </c>
       <c r="G110">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H110">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -15335,13 +15365,13 @@
         <v>33</v>
       </c>
       <c r="G111">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H111">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -15361,10 +15391,10 @@
         <v>33</v>
       </c>
       <c r="G112">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H112">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="I112" t="s">
         <v>44</v>
@@ -15373,7 +15403,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>34</v>
       </c>
@@ -15396,13 +15426,13 @@
         <v>0</v>
       </c>
       <c r="H113">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I113" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>34</v>
       </c>
@@ -15425,10 +15455,10 @@
         <v>0</v>
       </c>
       <c r="H114">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>34</v>
       </c>
@@ -15451,10 +15481,10 @@
         <v>0</v>
       </c>
       <c r="H115">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>34</v>
       </c>
@@ -15477,10 +15507,10 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>34</v>
       </c>
@@ -15500,13 +15530,13 @@
         <v>35</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>34</v>
       </c>
@@ -15526,13 +15556,13 @@
         <v>35</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>34</v>
       </c>
@@ -15552,13 +15582,13 @@
         <v>35</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H119">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>34</v>
       </c>
@@ -15578,13 +15608,13 @@
         <v>35</v>
       </c>
       <c r="G120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H120">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>34</v>
       </c>
@@ -15604,13 +15634,13 @@
         <v>35</v>
       </c>
       <c r="G121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H121">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>34</v>
       </c>
@@ -15630,13 +15660,13 @@
         <v>35</v>
       </c>
       <c r="G122">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H122">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>34</v>
       </c>
@@ -15656,13 +15686,13 @@
         <v>35</v>
       </c>
       <c r="G123">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H123">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>34</v>
       </c>
@@ -15682,19 +15712,20 @@
         <v>35</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H124">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="I124" t="s">
         <v>44</v>
       </c>
       <c r="J124">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+        <f>G124</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -15717,13 +15748,13 @@
         <v>0</v>
       </c>
       <c r="H125">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="I125" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>36</v>
       </c>
@@ -15746,10 +15777,10 @@
         <v>0</v>
       </c>
       <c r="H126">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>36</v>
       </c>
@@ -15772,10 +15803,10 @@
         <v>0</v>
       </c>
       <c r="H127">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>36</v>
       </c>
@@ -15798,10 +15829,10 @@
         <v>0</v>
       </c>
       <c r="H128">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>36</v>
       </c>
@@ -15824,10 +15855,10 @@
         <v>0</v>
       </c>
       <c r="H129">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>36</v>
       </c>
@@ -15850,10 +15881,10 @@
         <v>0</v>
       </c>
       <c r="H130">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>36</v>
       </c>
@@ -15876,10 +15907,10 @@
         <v>0</v>
       </c>
       <c r="H131">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>36</v>
       </c>
@@ -15902,10 +15933,10 @@
         <v>0</v>
       </c>
       <c r="H132">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>36</v>
       </c>
@@ -15928,10 +15959,10 @@
         <v>0</v>
       </c>
       <c r="H133">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>36</v>
       </c>
@@ -15954,10 +15985,10 @@
         <v>0</v>
       </c>
       <c r="H134">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>36</v>
       </c>
@@ -15977,13 +16008,13 @@
         <v>19</v>
       </c>
       <c r="G135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H135">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>36</v>
       </c>
@@ -16003,13 +16034,13 @@
         <v>19</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H136">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>36</v>
       </c>
@@ -16029,13 +16060,13 @@
         <v>19</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H137">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>36</v>
       </c>
@@ -16055,13 +16086,13 @@
         <v>19</v>
       </c>
       <c r="G138">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H138">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>36</v>
       </c>
@@ -16081,13 +16112,13 @@
         <v>19</v>
       </c>
       <c r="G139">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H139">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>36</v>
       </c>
@@ -16107,19 +16138,20 @@
         <v>19</v>
       </c>
       <c r="G140">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H140">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="I140" t="s">
         <v>44</v>
       </c>
       <c r="J140">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+        <f>G140</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -16142,13 +16174,13 @@
         <v>0</v>
       </c>
       <c r="H141">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="I141" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>37</v>
       </c>
@@ -16171,10 +16203,10 @@
         <v>0</v>
       </c>
       <c r="H142">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>37</v>
       </c>
@@ -16197,10 +16229,10 @@
         <v>0</v>
       </c>
       <c r="H143">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>37</v>
       </c>
@@ -16223,10 +16255,10 @@
         <v>0</v>
       </c>
       <c r="H144">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>37</v>
       </c>
@@ -16249,10 +16281,10 @@
         <v>0</v>
       </c>
       <c r="H145">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>37</v>
       </c>
@@ -16275,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="H146">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>37</v>
       </c>
@@ -16301,10 +16333,10 @@
         <v>0</v>
       </c>
       <c r="H147">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>37</v>
       </c>
@@ -16324,13 +16356,13 @@
         <v>35</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>37</v>
       </c>
@@ -16350,13 +16382,13 @@
         <v>35</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H149">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>37</v>
       </c>
@@ -16376,13 +16408,13 @@
         <v>35</v>
       </c>
       <c r="G150">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H150">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>37</v>
       </c>
@@ -16402,13 +16434,13 @@
         <v>35</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H151">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>37</v>
       </c>
@@ -16428,13 +16460,13 @@
         <v>35</v>
       </c>
       <c r="G152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H152">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>37</v>
       </c>
@@ -16454,13 +16486,13 @@
         <v>35</v>
       </c>
       <c r="G153">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H153">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>37</v>
       </c>
@@ -16480,13 +16512,13 @@
         <v>35</v>
       </c>
       <c r="G154">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H154">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>37</v>
       </c>
@@ -16506,13 +16538,13 @@
         <v>35</v>
       </c>
       <c r="G155">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H155">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>37</v>
       </c>
@@ -16532,19 +16564,19 @@
         <v>35</v>
       </c>
       <c r="G156">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H156">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="I156" t="s">
         <v>44</v>
       </c>
       <c r="J156">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>38</v>
       </c>
@@ -16570,7 +16602,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>38</v>
       </c>
@@ -16596,7 +16628,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>38</v>
       </c>
@@ -16622,7 +16654,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>38</v>
       </c>
@@ -16648,7 +16680,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>38</v>
       </c>
@@ -16674,7 +16706,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>38</v>
       </c>
@@ -16700,7 +16732,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>38</v>
       </c>
@@ -16726,7 +16758,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>38</v>
       </c>
@@ -16752,7 +16784,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>38</v>
       </c>
@@ -16778,7 +16810,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>38</v>
       </c>
@@ -16804,7 +16836,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>38</v>
       </c>
@@ -16830,7 +16862,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>38</v>
       </c>
@@ -16856,7 +16888,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>38</v>
       </c>
@@ -16888,7 +16920,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -16914,7 +16946,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -16940,7 +16972,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -16966,7 +16998,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -16992,7 +17024,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -17018,7 +17050,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -17044,7 +17076,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -17070,7 +17102,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -17096,7 +17128,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -17128,7 +17160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>40</v>
       </c>
@@ -17154,7 +17186,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>40</v>
       </c>
@@ -17180,7 +17212,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>40</v>
       </c>
@@ -17206,7 +17238,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>40</v>
       </c>
@@ -17232,7 +17264,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>40</v>
       </c>
@@ -17258,7 +17290,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>40</v>
       </c>
@@ -17284,7 +17316,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>40</v>
       </c>
